--- a/Tables/MAIHDA.xlsx
+++ b/Tables/MAIHDA.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38b97e870d12de33/Documents/UAH/PhD Documents/INEdatos/Analysis/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{980E5B5A-75EE-4430-85D2-0D88ED2233B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C3DFA13-7A7B-47D9-BAE2-828DB4EFF82F}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{980E5B5A-75EE-4430-85D2-0D88ED2233B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0FCB3D0-F854-4808-B0F0-93B503ECB1CF}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1572" yWindow="3804" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{F53BC189-169C-4D5A-95F0-57F331A1907F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F53BC189-169C-4D5A-95F0-57F331A1907F}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIHDA-0412" sheetId="1" r:id="rId1"/>
-    <sheet name="MAIHDA (2)" sheetId="2" r:id="rId2"/>
-    <sheet name="MAIHDA" sheetId="3" r:id="rId3"/>
+    <sheet name="MAIHDA (2)" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="MAIHDA" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1312,57 +1312,6 @@
     <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1378,6 +1327,57 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1669,14 +1669,17 @@
     <col min="4" max="4" width="15.5546875" style="1" customWidth="1"/>
     <col min="5" max="6" width="9.109375" style="1"/>
     <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
-    <col min="8" max="9" width="9.109375" style="1"/>
+    <col min="8" max="8" width="6.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" style="1"/>
     <col min="10" max="10" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="9.109375" style="1"/>
-    <col min="15" max="15" width="11.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12" style="1" customWidth="1"/>
     <col min="17" max="17" width="10" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="1" customWidth="1"/>
     <col min="20" max="21" width="9.109375" style="1"/>
     <col min="22" max="22" width="29.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -1747,18 +1750,18 @@
     </row>
     <row r="9" spans="1:11" ht="28.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="50" t="s">
+      <c r="H9" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
     </row>
     <row r="10" spans="1:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -1819,12 +1822,12 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
       <c r="G12" s="6" t="s">
         <v>19</v>
       </c>
@@ -1845,11 +1848,11 @@
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="41">
         <v>3.29</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
       <c r="G13" s="6" t="s">
         <v>22</v>
       </c>
@@ -1870,11 +1873,11 @@
       <c r="A14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="41">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
       <c r="G14" s="6" t="s">
         <v>25</v>
       </c>
@@ -1895,24 +1898,24 @@
       <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="41">
         <v>0.08</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
       <c r="G15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="38">
+      <c r="H15" s="42">
         <v>0.62</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15" s="42">
         <v>0.04</v>
       </c>
-      <c r="J15" s="38" t="s">
+      <c r="J15" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="51" t="s">
+      <c r="K15" s="43" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1920,28 +1923,28 @@
       <c r="A16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="44">
+      <c r="B16" s="49">
         <v>72</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
       <c r="G16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="51"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="43"/>
     </row>
     <row r="17" spans="1:11" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="45">
+      <c r="B17" s="50">
         <v>19500</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
       <c r="G17" s="6" t="s">
         <v>33</v>
       </c>
@@ -1962,11 +1965,11 @@
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
       <c r="G18" s="6" t="s">
         <v>37</v>
       </c>
@@ -2009,85 +2012,85 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="43" t="s">
+      <c r="G20" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
     </row>
     <row r="21" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="38"/>
+      <c r="A21" s="42"/>
       <c r="G21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="46">
+      <c r="H21" s="41">
         <v>3.29</v>
       </c>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
     </row>
     <row r="22" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="38"/>
+      <c r="A22" s="42"/>
       <c r="G22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H22" s="46">
+      <c r="H22" s="41">
         <v>0.03</v>
       </c>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
     </row>
     <row r="23" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="38"/>
+      <c r="A23" s="42"/>
       <c r="G23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="46">
+      <c r="H23" s="41">
         <v>0.01</v>
       </c>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="44">
+      <c r="H24" s="49">
         <v>72</v>
       </c>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
     </row>
     <row r="25" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="45">
+      <c r="H25" s="50">
         <v>19500</v>
       </c>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
     </row>
     <row r="26" spans="1:11" ht="33.6" x14ac:dyDescent="0.25">
       <c r="G26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H26" s="46" t="s">
+      <c r="H26" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
     </row>
     <row r="27" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G27" s="12" t="s">
@@ -2101,7 +2104,7 @@
       <c r="A28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G28" s="38" t="s">
+      <c r="G28" s="42" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2112,7 +2115,7 @@
       <c r="C29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="38"/>
+      <c r="G29" s="42"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -2124,7 +2127,7 @@
       <c r="C30" s="1">
         <v>8.6</v>
       </c>
-      <c r="G30" s="38"/>
+      <c r="G30" s="42"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -2136,7 +2139,7 @@
       <c r="C31" s="1">
         <v>9.5</v>
       </c>
-      <c r="G31" s="38"/>
+      <c r="G31" s="42"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -2148,7 +2151,7 @@
       <c r="C32" s="1">
         <v>14.1</v>
       </c>
-      <c r="G32" s="38"/>
+      <c r="G32" s="42"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
@@ -2160,7 +2163,7 @@
       <c r="C33" s="1">
         <v>8.1</v>
       </c>
-      <c r="G33" s="38"/>
+      <c r="G33" s="42"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
@@ -2172,7 +2175,7 @@
       <c r="C34" s="1">
         <v>12.3</v>
       </c>
-      <c r="G34" s="38"/>
+      <c r="G34" s="42"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
@@ -2184,7 +2187,7 @@
       <c r="C35" s="1">
         <v>14</v>
       </c>
-      <c r="G35" s="38"/>
+      <c r="G35" s="42"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
@@ -2196,7 +2199,7 @@
       <c r="C36" s="1">
         <v>8</v>
       </c>
-      <c r="G36" s="38"/>
+      <c r="G36" s="42"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
@@ -2208,7 +2211,7 @@
       <c r="C37" s="1">
         <v>4</v>
       </c>
-      <c r="G37" s="38"/>
+      <c r="G37" s="42"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -2220,7 +2223,7 @@
       <c r="C38" s="1">
         <v>10.1</v>
       </c>
-      <c r="G38" s="38"/>
+      <c r="G38" s="42"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2939,36 +2942,36 @@
       </c>
     </row>
     <row r="106" spans="1:34" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="47" t="s">
+      <c r="A106" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B106" s="47"/>
-      <c r="D106" s="48" t="s">
+      <c r="B106" s="46"/>
+      <c r="D106" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="E106" s="48"/>
-      <c r="F106" s="48"/>
-      <c r="H106" s="49" t="s">
+      <c r="E106" s="47"/>
+      <c r="F106" s="47"/>
+      <c r="H106" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="I106" s="49"/>
-      <c r="J106" s="49"/>
-      <c r="K106" s="49"/>
-      <c r="L106" s="49"/>
-      <c r="M106" s="49"/>
-      <c r="N106" s="49"/>
-      <c r="O106" s="49"/>
-      <c r="P106" s="49"/>
-      <c r="Q106" s="49"/>
-      <c r="R106" s="49"/>
-      <c r="S106" s="49"/>
-      <c r="V106" s="41" t="s">
+      <c r="I106" s="48"/>
+      <c r="J106" s="48"/>
+      <c r="K106" s="48"/>
+      <c r="L106" s="48"/>
+      <c r="M106" s="48"/>
+      <c r="N106" s="48"/>
+      <c r="O106" s="48"/>
+      <c r="P106" s="48"/>
+      <c r="Q106" s="48"/>
+      <c r="R106" s="48"/>
+      <c r="S106" s="48"/>
+      <c r="V106" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="W106" s="41"/>
-      <c r="X106" s="41"/>
-      <c r="Y106" s="41"/>
-      <c r="Z106" s="41"/>
+      <c r="W106" s="51"/>
+      <c r="X106" s="51"/>
+      <c r="Y106" s="51"/>
+      <c r="Z106" s="51"/>
       <c r="AB106" s="2" t="s">
         <v>58</v>
       </c>
@@ -2992,10 +2995,10 @@
       </c>
     </row>
     <row r="107" spans="1:34" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="42" t="s">
+      <c r="A107" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="B107" s="42"/>
+      <c r="B107" s="52"/>
       <c r="D107" s="17" t="s">
         <v>66</v>
       </c>
@@ -3738,13 +3741,13 @@
       <c r="T116" s="1">
         <v>0.118312327125455</v>
       </c>
-      <c r="V116" s="43" t="s">
+      <c r="V116" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="W116" s="43"/>
-      <c r="X116" s="43"/>
-      <c r="Y116" s="43"/>
-      <c r="Z116" s="43"/>
+      <c r="W116" s="45"/>
+      <c r="X116" s="45"/>
+      <c r="Y116" s="45"/>
+      <c r="Z116" s="45"/>
       <c r="AB116" s="1">
         <v>72</v>
       </c>
@@ -3816,14 +3819,14 @@
       <c r="V117" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W117" s="38">
+      <c r="W117" s="42">
         <v>3.29</v>
       </c>
-      <c r="X117" s="38"/>
-      <c r="Y117" s="38">
+      <c r="X117" s="42"/>
+      <c r="Y117" s="42">
         <v>3.29</v>
       </c>
-      <c r="Z117" s="38"/>
+      <c r="Z117" s="42"/>
       <c r="AB117" s="1">
         <v>71</v>
       </c>
@@ -3895,14 +3898,14 @@
       <c r="V118" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="W118" s="38" t="s">
+      <c r="W118" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="X118" s="38"/>
-      <c r="Y118" s="38" t="s">
+      <c r="X118" s="42"/>
+      <c r="Y118" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="Z118" s="38"/>
+      <c r="Z118" s="42"/>
       <c r="AB118" s="1">
         <v>70</v>
       </c>
@@ -3974,14 +3977,14 @@
       <c r="V119" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="W119" s="38">
+      <c r="W119" s="42">
         <v>0.08</v>
       </c>
-      <c r="X119" s="38"/>
-      <c r="Y119" s="38">
+      <c r="X119" s="42"/>
+      <c r="Y119" s="42">
         <v>0.01</v>
       </c>
-      <c r="Z119" s="38"/>
+      <c r="Z119" s="42"/>
       <c r="AB119" s="1">
         <v>64</v>
       </c>
@@ -4051,14 +4054,14 @@
       <c r="V120" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="W120" s="39" t="s">
+      <c r="W120" s="56" t="s">
         <v>130</v>
       </c>
-      <c r="X120" s="39"/>
-      <c r="Y120" s="39" t="s">
+      <c r="X120" s="56"/>
+      <c r="Y120" s="56" t="s">
         <v>130</v>
       </c>
-      <c r="Z120" s="39"/>
+      <c r="Z120" s="56"/>
       <c r="AB120" s="1">
         <v>69</v>
       </c>
@@ -4130,14 +4133,14 @@
       <c r="V121" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="W121" s="40">
+      <c r="W121" s="57">
         <v>19500</v>
       </c>
-      <c r="X121" s="40"/>
-      <c r="Y121" s="40">
+      <c r="X121" s="57"/>
+      <c r="Y121" s="57">
         <v>19500</v>
       </c>
-      <c r="Z121" s="40"/>
+      <c r="Z121" s="57"/>
       <c r="AB121" s="1">
         <v>68</v>
       </c>
@@ -4209,14 +4212,14 @@
       <c r="V122" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="W122" s="35" t="s">
+      <c r="W122" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="X122" s="35"/>
-      <c r="Y122" s="35" t="s">
+      <c r="X122" s="53"/>
+      <c r="Y122" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="Z122" s="35"/>
+      <c r="Z122" s="53"/>
     </row>
     <row r="123" spans="1:34" ht="42" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A123" s="25" t="s">
@@ -4262,13 +4265,13 @@
       <c r="T123" s="1">
         <v>4.6341574791248501E-2</v>
       </c>
-      <c r="V123" s="36" t="s">
+      <c r="V123" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="W123" s="36"/>
-      <c r="X123" s="36"/>
-      <c r="Y123" s="36"/>
-      <c r="Z123" s="36"/>
+      <c r="W123" s="54"/>
+      <c r="X123" s="54"/>
+      <c r="Y123" s="54"/>
+      <c r="Z123" s="54"/>
     </row>
     <row r="124" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="26" t="s">
@@ -4530,10 +4533,10 @@
       <c r="AC128" s="19"/>
     </row>
     <row r="129" spans="1:29" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="A129" s="37" t="s">
+      <c r="A129" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="B129" s="37"/>
+      <c r="B129" s="55"/>
       <c r="H129" s="20" t="s">
         <v>76</v>
       </c>
@@ -6687,16 +6690,26 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="V123:Z123"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="W119:X119"/>
+    <mergeCell ref="Y119:Z119"/>
+    <mergeCell ref="W120:X120"/>
+    <mergeCell ref="Y120:Z120"/>
+    <mergeCell ref="W121:X121"/>
+    <mergeCell ref="Y121:Z121"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="V116:Z116"/>
+    <mergeCell ref="W117:X117"/>
+    <mergeCell ref="Y117:Z117"/>
+    <mergeCell ref="W122:X122"/>
+    <mergeCell ref="Y122:Z122"/>
+    <mergeCell ref="W118:X118"/>
+    <mergeCell ref="Y118:Z118"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="V106:Z106"/>
     <mergeCell ref="G28:G38"/>
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="D106:F106"/>
@@ -6709,26 +6722,16 @@
     <mergeCell ref="H21:K21"/>
     <mergeCell ref="H22:K22"/>
     <mergeCell ref="H23:K23"/>
-    <mergeCell ref="W118:X118"/>
-    <mergeCell ref="Y118:Z118"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="V106:Z106"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="V116:Z116"/>
-    <mergeCell ref="W117:X117"/>
-    <mergeCell ref="Y117:Z117"/>
-    <mergeCell ref="W122:X122"/>
-    <mergeCell ref="Y122:Z122"/>
-    <mergeCell ref="V123:Z123"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="W119:X119"/>
-    <mergeCell ref="Y119:Z119"/>
-    <mergeCell ref="W120:X120"/>
-    <mergeCell ref="Y120:Z120"/>
-    <mergeCell ref="W121:X121"/>
-    <mergeCell ref="Y121:Z121"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6771,31 +6774,31 @@
     </row>
     <row r="3" spans="1:21" ht="28.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
       <c r="L3" s="3"/>
-      <c r="M3" s="50" t="s">
+      <c r="M3" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
       <c r="Q3" s="3"/>
-      <c r="R3" s="50" t="s">
+      <c r="R3" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
     </row>
     <row r="4" spans="1:21" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
@@ -6910,12 +6913,12 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
       <c r="F6" s="6" t="s">
         <v>19</v>
       </c>
@@ -6931,12 +6934,12 @@
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="43" t="s">
+      <c r="L6" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
       <c r="Q6" s="6" t="s">
         <v>19</v>
       </c>
@@ -6957,11 +6960,11 @@
       <c r="A7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="46">
+      <c r="B7" s="41">
         <v>3.29</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
       <c r="F7" s="6" t="s">
         <v>172</v>
       </c>
@@ -6980,11 +6983,11 @@
       <c r="L7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="46">
+      <c r="M7" s="41">
         <v>0.59</v>
       </c>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
       <c r="Q7" s="6" t="s">
         <v>172</v>
       </c>
@@ -7005,11 +7008,11 @@
       <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="46">
+      <c r="B8" s="41">
         <v>0.9</v>
       </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
       <c r="F8" s="6" t="s">
         <v>175</v>
       </c>
@@ -7028,11 +7031,11 @@
       <c r="L8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="46">
+      <c r="M8" s="41">
         <v>0.01</v>
       </c>
-      <c r="N8" s="46"/>
-      <c r="O8" s="46"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
       <c r="Q8" s="6" t="s">
         <v>175</v>
       </c>
@@ -7053,11 +7056,11 @@
       <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="41">
         <v>0.21</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
       <c r="F9" s="6" t="s">
         <v>178</v>
       </c>
@@ -7076,11 +7079,11 @@
       <c r="L9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="M9" s="46">
+      <c r="M9" s="41">
         <v>0.02</v>
       </c>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
       <c r="Q9" s="6" t="s">
         <v>178</v>
       </c>
@@ -7101,11 +7104,11 @@
       <c r="A10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="44">
+      <c r="B10" s="49">
         <v>108</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
       <c r="F10" s="6" t="s">
         <v>181</v>
       </c>
@@ -7124,11 +7127,11 @@
       <c r="L10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="44">
+      <c r="M10" s="49">
         <v>108</v>
       </c>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
       <c r="Q10" s="6" t="s">
         <v>181</v>
       </c>
@@ -7149,11 +7152,11 @@
       <c r="A11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="50">
         <v>29653</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
       <c r="F11" s="6" t="s">
         <v>184</v>
       </c>
@@ -7172,11 +7175,11 @@
       <c r="L11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="45">
+      <c r="M11" s="50">
         <v>29653</v>
       </c>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="50"/>
       <c r="Q11" s="6" t="s">
         <v>184</v>
       </c>
@@ -7197,11 +7200,11 @@
       <c r="A12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
       <c r="F12" s="6" t="s">
         <v>188</v>
       </c>
@@ -7220,11 +7223,11 @@
       <c r="L12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M12" s="46" t="s">
+      <c r="M12" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="N12" s="46"/>
-      <c r="O12" s="46"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
       <c r="Q12" s="6" t="s">
         <v>188</v>
       </c>
@@ -7245,7 +7248,7 @@
       <c r="A13" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="52">
+      <c r="B13" s="35">
         <v>21.405159999999999</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -7266,7 +7269,7 @@
       <c r="L13" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="52">
+      <c r="M13" s="35">
         <v>2.307426</v>
       </c>
       <c r="Q13" s="6" t="s">
@@ -7350,13 +7353,13 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
       <c r="Q16" s="9" t="s">
         <v>18</v>
       </c>
@@ -7369,12 +7372,12 @@
       <c r="F17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="41">
         <v>3.29</v>
       </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
       <c r="Q17" s="6" t="s">
         <v>21</v>
       </c>
@@ -7383,12 +7386,12 @@
       <c r="F18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="41">
         <v>0.02</v>
       </c>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
       <c r="Q18" s="6" t="s">
         <v>24</v>
       </c>
@@ -7403,12 +7406,12 @@
       <c r="F19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="46">
+      <c r="G19" s="41">
         <v>0.01</v>
       </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
       <c r="Q19" s="6" t="s">
         <v>30</v>
       </c>
@@ -7423,12 +7426,12 @@
       <c r="F20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="49">
         <v>108</v>
       </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
       <c r="Q20" s="11" t="s">
         <v>32</v>
       </c>
@@ -7443,16 +7446,16 @@
       <c r="F21" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="45">
+      <c r="G21" s="50">
         <v>29653</v>
       </c>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
       <c r="Q21" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="R21" s="53">
+      <c r="R21" s="36">
         <v>3.6478820000000001E-8</v>
       </c>
     </row>
@@ -7460,23 +7463,41 @@
       <c r="F22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="46" t="s">
+      <c r="G22" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
     </row>
     <row r="23" spans="6:21" x14ac:dyDescent="0.3">
       <c r="F23" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="52">
+      <c r="G23" s="35">
         <v>0.6992389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="M12:O12"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="F16:J16"/>
     <mergeCell ref="G17:J17"/>
@@ -7484,24 +7505,6 @@
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="G21:J21"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="L6:O6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7529,36 +7532,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="X1" s="54" t="s">
+      <c r="X1" s="37" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="L2" s="54" t="s">
+      <c r="L2" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="Q2" s="54" t="s">
+      <c r="Q2" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="X2" s="54" t="s">
+      <c r="X2" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="AC2" s="54" t="s">
+      <c r="AC2" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="AI2" s="54" t="s">
+      <c r="AI2" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="AN2" s="54" t="s">
+      <c r="AN2" s="37" t="s">
         <v>204</v>
       </c>
     </row>
@@ -7578,57 +7581,57 @@
     </row>
     <row r="4" spans="1:44" ht="28.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="L4" s="50" t="s">
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="L4" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="X4" s="50" t="s">
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+      <c r="X4" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
-      <c r="AC4" s="50" t="s">
+      <c r="Y4" s="44"/>
+      <c r="Z4" s="44"/>
+      <c r="AA4" s="44"/>
+      <c r="AC4" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="AD4" s="50"/>
-      <c r="AE4" s="50"/>
-      <c r="AF4" s="50"/>
-      <c r="AG4" s="50"/>
-      <c r="AI4" s="50" t="s">
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="44"/>
+      <c r="AG4" s="44"/>
+      <c r="AI4" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="AJ4" s="50"/>
-      <c r="AK4" s="50"/>
-      <c r="AL4" s="50"/>
-      <c r="AN4" s="50" t="s">
+      <c r="AJ4" s="44"/>
+      <c r="AK4" s="44"/>
+      <c r="AL4" s="44"/>
+      <c r="AN4" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="AO4" s="50"/>
-      <c r="AP4" s="50"/>
-      <c r="AQ4" s="50"/>
-      <c r="AR4" s="50"/>
+      <c r="AO4" s="44"/>
+      <c r="AP4" s="44"/>
+      <c r="AQ4" s="44"/>
+      <c r="AR4" s="44"/>
     </row>
     <row r="5" spans="1:44" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
@@ -7851,12 +7854,12 @@
       </c>
     </row>
     <row r="7" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
       <c r="F7" s="6" t="s">
         <v>19</v>
       </c>
@@ -7872,12 +7875,12 @@
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="43" t="s">
+      <c r="L7" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
       <c r="Q7" s="6" t="s">
         <v>19</v>
       </c>
@@ -7893,12 +7896,12 @@
       <c r="U7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="X7" s="43" t="s">
+      <c r="X7" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="43"/>
-      <c r="AA7" s="43"/>
+      <c r="Y7" s="45"/>
+      <c r="Z7" s="45"/>
+      <c r="AA7" s="45"/>
       <c r="AC7" s="6" t="s">
         <v>19</v>
       </c>
@@ -7914,12 +7917,12 @@
       <c r="AG7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AI7" s="43" t="s">
+      <c r="AI7" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="AJ7" s="43"/>
-      <c r="AK7" s="43"/>
-      <c r="AL7" s="43"/>
+      <c r="AJ7" s="45"/>
+      <c r="AK7" s="45"/>
+      <c r="AL7" s="45"/>
       <c r="AN7" s="6" t="s">
         <v>19</v>
       </c>
@@ -7940,11 +7943,11 @@
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="46">
+      <c r="B8" s="41">
         <v>3.29</v>
       </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
       <c r="F8" s="6" t="s">
         <v>22</v>
       </c>
@@ -7963,11 +7966,11 @@
       <c r="L8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="46">
+      <c r="M8" s="41">
         <v>3.29</v>
       </c>
-      <c r="N8" s="46"/>
-      <c r="O8" s="46"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
       <c r="Q8" s="6" t="s">
         <v>22</v>
       </c>
@@ -7986,11 +7989,11 @@
       <c r="X8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Y8" s="46">
+      <c r="Y8" s="41">
         <v>2.12</v>
       </c>
-      <c r="Z8" s="46"/>
-      <c r="AA8" s="46"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="41"/>
       <c r="AC8" s="6" t="s">
         <v>22</v>
       </c>
@@ -8009,11 +8012,11 @@
       <c r="AI8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AJ8" s="46">
+      <c r="AJ8" s="41">
         <v>2.11</v>
       </c>
-      <c r="AK8" s="46"/>
-      <c r="AL8" s="46"/>
+      <c r="AK8" s="41"/>
+      <c r="AL8" s="41"/>
       <c r="AN8" s="6" t="s">
         <v>22</v>
       </c>
@@ -8034,11 +8037,11 @@
       <c r="A9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="41">
         <v>0.24</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
       <c r="F9" s="6" t="s">
         <v>25</v>
       </c>
@@ -8057,11 +8060,11 @@
       <c r="L9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="46">
+      <c r="M9" s="41">
         <v>0.26</v>
       </c>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
       <c r="Q9" s="6" t="s">
         <v>25</v>
       </c>
@@ -8080,11 +8083,11 @@
       <c r="X9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Y9" s="46">
+      <c r="Y9" s="41">
         <v>0.17</v>
       </c>
-      <c r="Z9" s="46"/>
-      <c r="AA9" s="46"/>
+      <c r="Z9" s="41"/>
+      <c r="AA9" s="41"/>
       <c r="AC9" s="6" t="s">
         <v>25</v>
       </c>
@@ -8103,11 +8106,11 @@
       <c r="AI9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AJ9" s="46">
+      <c r="AJ9" s="41">
         <v>0.18</v>
       </c>
-      <c r="AK9" s="46"/>
-      <c r="AL9" s="46"/>
+      <c r="AK9" s="41"/>
+      <c r="AL9" s="41"/>
       <c r="AN9" s="6" t="s">
         <v>25</v>
       </c>
@@ -8128,11 +8131,11 @@
       <c r="A10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="41">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
       <c r="F10" s="6" t="s">
         <v>224</v>
       </c>
@@ -8151,11 +8154,11 @@
       <c r="L10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="46">
+      <c r="M10" s="41">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N10" s="46"/>
-      <c r="O10" s="46"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
       <c r="Q10" s="6" t="s">
         <v>178</v>
       </c>
@@ -8174,11 +8177,11 @@
       <c r="X10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="Y10" s="46">
+      <c r="Y10" s="41">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="46"/>
+      <c r="Z10" s="41"/>
+      <c r="AA10" s="41"/>
       <c r="AC10" s="6" t="s">
         <v>224</v>
       </c>
@@ -8197,11 +8200,11 @@
       <c r="AI10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AJ10" s="46">
+      <c r="AJ10" s="41">
         <v>0.08</v>
       </c>
-      <c r="AK10" s="46"/>
-      <c r="AL10" s="46"/>
+      <c r="AK10" s="41"/>
+      <c r="AL10" s="41"/>
       <c r="AN10" s="6" t="s">
         <v>178</v>
       </c>
@@ -8222,11 +8225,11 @@
       <c r="A11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="49">
         <v>54</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
       <c r="F11" s="6" t="s">
         <v>229</v>
       </c>
@@ -8245,11 +8248,11 @@
       <c r="L11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M11" s="44">
+      <c r="M11" s="49">
         <v>108</v>
       </c>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="49"/>
       <c r="Q11" s="6" t="s">
         <v>181</v>
       </c>
@@ -8268,11 +8271,11 @@
       <c r="X11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Y11" s="44">
+      <c r="Y11" s="49">
         <v>54</v>
       </c>
-      <c r="Z11" s="44"/>
-      <c r="AA11" s="44"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="49"/>
       <c r="AC11" s="6" t="s">
         <v>229</v>
       </c>
@@ -8291,11 +8294,11 @@
       <c r="AI11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AJ11" s="44">
+      <c r="AJ11" s="49">
         <v>108</v>
       </c>
-      <c r="AK11" s="44"/>
-      <c r="AL11" s="44"/>
+      <c r="AK11" s="49"/>
+      <c r="AL11" s="49"/>
       <c r="AN11" s="6" t="s">
         <v>181</v>
       </c>
@@ -8316,11 +8319,11 @@
       <c r="A12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="50">
         <v>19500</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
       <c r="F12" s="6" t="s">
         <v>33</v>
       </c>
@@ -8339,11 +8342,11 @@
       <c r="L12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="45">
+      <c r="M12" s="50">
         <v>19500</v>
       </c>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
       <c r="Q12" s="6" t="s">
         <v>184</v>
       </c>
@@ -8362,11 +8365,11 @@
       <c r="X12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="Y12" s="45">
+      <c r="Y12" s="50">
         <v>19500</v>
       </c>
-      <c r="Z12" s="45"/>
-      <c r="AA12" s="45"/>
+      <c r="Z12" s="50"/>
+      <c r="AA12" s="50"/>
       <c r="AC12" s="6" t="s">
         <v>33</v>
       </c>
@@ -8385,11 +8388,11 @@
       <c r="AI12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AJ12" s="45">
+      <c r="AJ12" s="50">
         <v>19500</v>
       </c>
-      <c r="AK12" s="45"/>
-      <c r="AL12" s="45"/>
+      <c r="AK12" s="50"/>
+      <c r="AL12" s="50"/>
       <c r="AN12" s="6" t="s">
         <v>184</v>
       </c>
@@ -8410,11 +8413,11 @@
       <c r="A13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
       <c r="F13" s="6" t="s">
         <v>37</v>
       </c>
@@ -8433,11 +8436,11 @@
       <c r="L13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M13" s="46" t="s">
+      <c r="M13" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
       <c r="Q13" s="6" t="s">
         <v>188</v>
       </c>
@@ -8456,11 +8459,11 @@
       <c r="X13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="Y13" s="46" t="s">
+      <c r="Y13" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="Z13" s="46"/>
-      <c r="AA13" s="46"/>
+      <c r="Z13" s="41"/>
+      <c r="AA13" s="41"/>
       <c r="AC13" s="6" t="s">
         <v>37</v>
       </c>
@@ -8479,11 +8482,11 @@
       <c r="AI13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AJ13" s="46" t="s">
+      <c r="AJ13" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="AK13" s="46"/>
-      <c r="AL13" s="46"/>
+      <c r="AK13" s="41"/>
+      <c r="AL13" s="41"/>
       <c r="AN13" s="6" t="s">
         <v>188</v>
       </c>
@@ -8507,15 +8510,15 @@
       <c r="B14" s="13">
         <v>6.678481E-2</v>
       </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="F14" s="43" t="s">
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="F14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
       <c r="L14" s="12" t="s">
         <v>39</v>
       </c>
@@ -8545,17 +8548,17 @@
       </c>
       <c r="Z14" s="14"/>
       <c r="AA14" s="14"/>
-      <c r="AC14" s="43" t="s">
+      <c r="AC14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="AD14" s="43"/>
-      <c r="AE14" s="43"/>
-      <c r="AF14" s="43"/>
-      <c r="AG14" s="43"/>
+      <c r="AD14" s="45"/>
+      <c r="AE14" s="45"/>
+      <c r="AF14" s="45"/>
+      <c r="AG14" s="45"/>
       <c r="AI14" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AJ14" s="56">
+      <c r="AJ14" s="39">
         <v>7.5683070000000005E-2</v>
       </c>
       <c r="AN14" s="6" t="s">
@@ -8575,18 +8578,18 @@
       </c>
     </row>
     <row r="15" spans="1:44" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="42" t="s">
         <v>246</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="41">
         <v>3.29</v>
       </c>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
       <c r="Q15" s="6" t="s">
         <v>33</v>
       </c>
@@ -8605,12 +8608,12 @@
       <c r="AC15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD15" s="46">
+      <c r="AD15" s="41">
         <v>2.12</v>
       </c>
-      <c r="AE15" s="46"/>
-      <c r="AF15" s="46"/>
-      <c r="AG15" s="46"/>
+      <c r="AE15" s="41"/>
+      <c r="AF15" s="41"/>
+      <c r="AG15" s="41"/>
       <c r="AN15" s="6" t="s">
         <v>33</v>
       </c>
@@ -8628,16 +8631,16 @@
       </c>
     </row>
     <row r="16" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="38"/>
+      <c r="A16" s="42"/>
       <c r="F16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="41">
         <v>0.01</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
       <c r="Q16" s="6" t="s">
         <v>37</v>
       </c>
@@ -8656,12 +8659,12 @@
       <c r="AC16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AD16" s="46">
+      <c r="AD16" s="41">
         <v>0</v>
       </c>
-      <c r="AE16" s="46"/>
-      <c r="AF16" s="46"/>
-      <c r="AG16" s="46"/>
+      <c r="AE16" s="41"/>
+      <c r="AF16" s="41"/>
+      <c r="AG16" s="41"/>
       <c r="AN16" s="6" t="s">
         <v>37</v>
       </c>
@@ -8679,154 +8682,154 @@
       </c>
     </row>
     <row r="17" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
+      <c r="A17" s="42"/>
       <c r="F17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="41">
         <v>0</v>
       </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="Q17" s="43" t="s">
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="Q17" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
+      <c r="R17" s="45"/>
+      <c r="S17" s="45"/>
+      <c r="T17" s="45"/>
+      <c r="U17" s="45"/>
       <c r="AC17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AD17" s="46">
+      <c r="AD17" s="41">
         <v>0</v>
       </c>
-      <c r="AE17" s="46"/>
-      <c r="AF17" s="46"/>
-      <c r="AG17" s="46"/>
-      <c r="AN17" s="43" t="s">
+      <c r="AE17" s="41"/>
+      <c r="AF17" s="41"/>
+      <c r="AG17" s="41"/>
+      <c r="AN17" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="AO17" s="43"/>
-      <c r="AP17" s="43"/>
-      <c r="AQ17" s="43"/>
-      <c r="AR17" s="43"/>
+      <c r="AO17" s="45"/>
+      <c r="AP17" s="45"/>
+      <c r="AQ17" s="45"/>
+      <c r="AR17" s="45"/>
     </row>
     <row r="18" spans="1:44" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="38"/>
+      <c r="A18" s="42"/>
       <c r="F18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="49">
         <v>54</v>
       </c>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
       <c r="Q18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="R18" s="46">
+      <c r="R18" s="41">
         <v>3.29</v>
       </c>
-      <c r="S18" s="46"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="46"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="41"/>
       <c r="AC18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AD18" s="44">
+      <c r="AD18" s="49">
         <v>54</v>
       </c>
-      <c r="AE18" s="44"/>
-      <c r="AF18" s="44"/>
-      <c r="AG18" s="44"/>
+      <c r="AE18" s="49"/>
+      <c r="AF18" s="49"/>
+      <c r="AG18" s="49"/>
       <c r="AN18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AO18" s="46">
+      <c r="AO18" s="41">
         <v>2.11</v>
       </c>
-      <c r="AP18" s="46"/>
-      <c r="AQ18" s="46"/>
-      <c r="AR18" s="46"/>
+      <c r="AP18" s="41"/>
+      <c r="AQ18" s="41"/>
+      <c r="AR18" s="41"/>
     </row>
     <row r="19" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="F19" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="50">
         <v>19500</v>
       </c>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
       <c r="Q19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="R19" s="46">
+      <c r="R19" s="41">
         <v>0.01</v>
       </c>
-      <c r="S19" s="46"/>
-      <c r="T19" s="46"/>
-      <c r="U19" s="46"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="41"/>
       <c r="AC19" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AD19" s="45">
+      <c r="AD19" s="50">
         <v>19500</v>
       </c>
-      <c r="AE19" s="45"/>
-      <c r="AF19" s="45"/>
-      <c r="AG19" s="45"/>
+      <c r="AE19" s="50"/>
+      <c r="AF19" s="50"/>
+      <c r="AG19" s="50"/>
       <c r="AN19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AO19" s="46">
+      <c r="AO19" s="41">
         <v>0</v>
       </c>
-      <c r="AP19" s="46"/>
-      <c r="AQ19" s="46"/>
-      <c r="AR19" s="46"/>
+      <c r="AP19" s="41"/>
+      <c r="AQ19" s="41"/>
+      <c r="AR19" s="41"/>
     </row>
     <row r="20" spans="1:44" ht="61.2" x14ac:dyDescent="0.3">
       <c r="F20" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="46" t="s">
+      <c r="G20" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
       <c r="Q20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="R20" s="46">
+      <c r="R20" s="41">
         <v>0</v>
       </c>
-      <c r="S20" s="46"/>
-      <c r="T20" s="46"/>
-      <c r="U20" s="46"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="41"/>
+      <c r="U20" s="41"/>
       <c r="AC20" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AD20" s="46" t="s">
+      <c r="AD20" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="AE20" s="46"/>
-      <c r="AF20" s="46"/>
-      <c r="AG20" s="46"/>
+      <c r="AE20" s="41"/>
+      <c r="AF20" s="41"/>
+      <c r="AG20" s="41"/>
       <c r="AN20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AO20" s="46">
+      <c r="AO20" s="41">
         <v>0</v>
       </c>
-      <c r="AP20" s="46"/>
-      <c r="AQ20" s="46"/>
-      <c r="AR20" s="46"/>
+      <c r="AP20" s="41"/>
+      <c r="AQ20" s="41"/>
+      <c r="AR20" s="41"/>
     </row>
     <row r="21" spans="1:44" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F21" s="12" t="s">
@@ -8838,12 +8841,12 @@
       <c r="Q21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="R21" s="44">
+      <c r="R21" s="49">
         <v>108</v>
       </c>
-      <c r="S21" s="44"/>
-      <c r="T21" s="44"/>
-      <c r="U21" s="44"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49"/>
       <c r="AC21" s="12" t="s">
         <v>244</v>
       </c>
@@ -8853,12 +8856,12 @@
       <c r="AN21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AO21" s="44">
+      <c r="AO21" s="49">
         <v>108</v>
       </c>
-      <c r="AP21" s="44"/>
-      <c r="AQ21" s="44"/>
-      <c r="AR21" s="44"/>
+      <c r="AP21" s="49"/>
+      <c r="AQ21" s="49"/>
+      <c r="AR21" s="49"/>
     </row>
     <row r="22" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F22" s="12" t="s">
@@ -8870,12 +8873,12 @@
       <c r="Q22" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="R22" s="45">
+      <c r="R22" s="50">
         <v>19500</v>
       </c>
-      <c r="S22" s="45"/>
-      <c r="T22" s="45"/>
-      <c r="U22" s="45"/>
+      <c r="S22" s="50"/>
+      <c r="T22" s="50"/>
+      <c r="U22" s="50"/>
       <c r="AC22" s="12" t="s">
         <v>252</v>
       </c>
@@ -8885,44 +8888,44 @@
       <c r="AN22" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AO22" s="45">
+      <c r="AO22" s="50">
         <v>19500</v>
       </c>
-      <c r="AP22" s="45"/>
-      <c r="AQ22" s="45"/>
-      <c r="AR22" s="45"/>
+      <c r="AP22" s="50"/>
+      <c r="AQ22" s="50"/>
+      <c r="AR22" s="50"/>
     </row>
     <row r="23" spans="1:44" ht="33.6" x14ac:dyDescent="0.3">
       <c r="Q23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R23" s="46" t="s">
+      <c r="R23" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="S23" s="46"/>
-      <c r="T23" s="46"/>
-      <c r="U23" s="46"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="41"/>
+      <c r="U23" s="41"/>
       <c r="AN23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AO23" s="46" t="s">
+      <c r="AO23" s="41" t="s">
         <v>254</v>
       </c>
-      <c r="AP23" s="46"/>
-      <c r="AQ23" s="46"/>
-      <c r="AR23" s="46"/>
+      <c r="AP23" s="41"/>
+      <c r="AQ23" s="41"/>
+      <c r="AR23" s="41"/>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="Q24" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="R24" s="56">
+      <c r="R24" s="39">
         <v>2.1294360000000002E-3</v>
       </c>
       <c r="AN24" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AO24" s="57">
+      <c r="AO24" s="40">
         <v>5.6517609999999998E-9</v>
       </c>
     </row>
@@ -8936,65 +8939,12 @@
       <c r="AN25" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AO25" s="57">
+      <c r="AO25" s="40">
         <v>99.999989999999997</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="R22:U22"/>
-    <mergeCell ref="AO22:AR22"/>
-    <mergeCell ref="R23:U23"/>
-    <mergeCell ref="AO23:AR23"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="R20:U20"/>
-    <mergeCell ref="AD20:AG20"/>
-    <mergeCell ref="AO20:AR20"/>
-    <mergeCell ref="R21:U21"/>
-    <mergeCell ref="AO21:AR21"/>
-    <mergeCell ref="AN17:AR17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="R18:U18"/>
-    <mergeCell ref="AD18:AG18"/>
-    <mergeCell ref="AO18:AR18"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="R19:U19"/>
-    <mergeCell ref="AD19:AG19"/>
-    <mergeCell ref="AO19:AR19"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="AC14:AG14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="AD15:AG15"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="AD16:AG16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="Q17:U17"/>
-    <mergeCell ref="AD17:AG17"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="AJ12:AL12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="Y13:AA13"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="Y8:AA8"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AI4:AL4"/>
     <mergeCell ref="AN4:AR4"/>
     <mergeCell ref="A7:D7"/>
@@ -9007,6 +8957,59 @@
     <mergeCell ref="R4:U4"/>
     <mergeCell ref="X4:AA4"/>
     <mergeCell ref="AC4:AG4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AJ12:AL12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="AD15:AG15"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="AD16:AG16"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="Q17:U17"/>
+    <mergeCell ref="AD17:AG17"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="R19:U19"/>
+    <mergeCell ref="AD19:AG19"/>
+    <mergeCell ref="AO19:AR19"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="AC14:AG14"/>
+    <mergeCell ref="AN17:AR17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="R18:U18"/>
+    <mergeCell ref="AD18:AG18"/>
+    <mergeCell ref="AO18:AR18"/>
+    <mergeCell ref="R22:U22"/>
+    <mergeCell ref="AO22:AR22"/>
+    <mergeCell ref="R23:U23"/>
+    <mergeCell ref="AO23:AR23"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="R20:U20"/>
+    <mergeCell ref="AD20:AG20"/>
+    <mergeCell ref="AO20:AR20"/>
+    <mergeCell ref="R21:U21"/>
+    <mergeCell ref="AO21:AR21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tables/MAIHDA.xlsx
+++ b/Tables/MAIHDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38b97e870d12de33/Documents/UAH/PhD Documents/INEdatos/Analysis/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{980E5B5A-75EE-4430-85D2-0D88ED2233B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0FCB3D0-F854-4808-B0F0-93B503ECB1CF}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{980E5B5A-75EE-4430-85D2-0D88ED2233B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCB7C653-12C0-4FF7-A1A2-B6F4823DED3A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F53BC189-169C-4D5A-95F0-57F331A1907F}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{F53BC189-169C-4D5A-95F0-57F331A1907F}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIHDA-0412" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="256">
   <si>
     <t xml:space="preserve">72 strata: </t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>age: 1 = 6-9, 2 = 10-12, 3 = 13-15</t>
-  </si>
-  <si>
-    <t>social class: 1 = Manual workers, 2 = Non-manual workers</t>
   </si>
   <si>
     <t>geographic location: 1 = Rural, 2 = Semi-urban, 3 = Urban</t>
@@ -1031,6 +1028,12 @@
   </si>
   <si>
     <t>0.083 / 0.083</t>
+  </si>
+  <si>
+    <t>social class: 1 = Non-Manual workers, 2 = Manual workers</t>
+  </si>
+  <si>
+    <t>0.12, 0.16</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1219,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1328,20 +1331,41 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1352,37 +1376,19 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1661,38 +1667,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93932417-64A4-4E65-932D-815F1647D6FB}">
   <dimension ref="A1:AH181"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="9.109375" style="1"/>
-    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.109375" style="1"/>
-    <col min="10" max="10" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="9.140625" style="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="7" style="1" customWidth="1"/>
     <col min="13" max="13" width="8" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" style="1" customWidth="1"/>
     <col min="16" max="16" width="12" style="1" customWidth="1"/>
     <col min="17" max="17" width="10" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="1" customWidth="1"/>
-    <col min="20" max="21" width="9.109375" style="1"/>
-    <col min="22" max="22" width="29.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.44140625" style="1" customWidth="1"/>
+    <col min="20" max="21" width="9.140625" style="1"/>
+    <col min="22" max="22" width="29.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" style="1" customWidth="1"/>
     <col min="24" max="24" width="12" style="1" customWidth="1"/>
-    <col min="25" max="25" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="11.88671875" style="1" customWidth="1"/>
-    <col min="28" max="29" width="9.109375" style="1"/>
-    <col min="30" max="30" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.109375" style="1"/>
+    <col min="25" max="25" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="11.85546875" style="1" customWidth="1"/>
+    <col min="28" max="29" width="9.140625" style="1"/>
+    <col min="30" max="30" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1716,97 +1722,97 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:11" ht="28.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="56" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="28.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="44" t="s">
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+    </row>
+    <row r="10" spans="1:11" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="44" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-    </row>
-    <row r="10" spans="1:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="I10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="7">
         <v>0.14000000000000001</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="G11" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H11" s="7">
         <v>0.1</v>
@@ -1815,21 +1821,21 @@
         <v>0.01</v>
       </c>
       <c r="J11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="G12" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="G12" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="H12" s="7">
         <v>1.91</v>
@@ -1838,23 +1844,23 @@
         <v>0.12</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="51">
+        <v>3.29</v>
+      </c>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="G13" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B13" s="41">
-        <v>3.29</v>
-      </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="H13" s="7">
         <v>1.05</v>
@@ -1863,7 +1869,7 @@
         <v>0.08</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K13" s="7">
         <v>0.51600000000000001</v>
@@ -1871,15 +1877,15 @@
     </row>
     <row r="14" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="51">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="G14" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="B14" s="41">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="G14" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="H14" s="7">
         <v>1.64</v>
@@ -1888,40 +1894,40 @@
         <v>0.12</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="51">
+        <v>0.08</v>
+      </c>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="G15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="41">
-        <v>0.08</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="G15" s="6" t="s">
+      <c r="H15" s="43">
+        <v>0.62</v>
+      </c>
+      <c r="I15" s="43">
+        <v>0.04</v>
+      </c>
+      <c r="J15" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="42">
-        <v>0.62</v>
-      </c>
-      <c r="I15" s="42">
-        <v>0.04</v>
-      </c>
-      <c r="J15" s="42" t="s">
+      <c r="K15" s="57" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="K15" s="43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="B16" s="49">
         <v>72</v>
@@ -1929,16 +1935,16 @@
       <c r="C16" s="49"/>
       <c r="D16" s="49"/>
       <c r="G16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="57"/>
+    </row>
+    <row r="17" spans="1:11" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="43"/>
-    </row>
-    <row r="17" spans="1:11" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="B17" s="50">
         <v>19500</v>
@@ -1946,7 +1952,7 @@
       <c r="C17" s="50"/>
       <c r="D17" s="50"/>
       <c r="G17" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H17" s="7">
         <v>1.34</v>
@@ -1955,23 +1961,23 @@
         <v>0.11</v>
       </c>
       <c r="J17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K17" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="B18" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="G18" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="G18" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="H18" s="7">
         <v>1.36</v>
@@ -1980,15 +1986,15 @@
         <v>0.1</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="13">
         <v>7.7593629999999997E-2</v>
@@ -1996,7 +2002,7 @@
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
       <c r="G19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H19" s="7">
         <v>0.76</v>
@@ -2005,63 +2011,63 @@
         <v>0.05</v>
       </c>
       <c r="J19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
+      <c r="G20" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="47"/>
     </row>
     <row r="21" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="42"/>
+      <c r="A21" s="43"/>
       <c r="G21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="41">
+        <v>20</v>
+      </c>
+      <c r="H21" s="51">
         <v>3.29</v>
       </c>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
     </row>
     <row r="22" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="42"/>
+      <c r="A22" s="43"/>
       <c r="G22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="41">
+        <v>23</v>
+      </c>
+      <c r="H22" s="51">
         <v>0.03</v>
       </c>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
-    </row>
-    <row r="23" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="42"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+    </row>
+    <row r="23" spans="1:11" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="43"/>
       <c r="G23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="41">
+        <v>26</v>
+      </c>
+      <c r="H23" s="51">
         <v>0.01</v>
       </c>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G24" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H24" s="49">
         <v>72</v>
@@ -2072,7 +2078,7 @@
     </row>
     <row r="25" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H25" s="50">
         <v>19500</v>
@@ -2081,20 +2087,20 @@
       <c r="J25" s="50"/>
       <c r="K25" s="50"/>
     </row>
-    <row r="26" spans="1:11" ht="33.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="36" x14ac:dyDescent="0.25">
       <c r="G26" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H26" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
+        <v>34</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
     </row>
     <row r="27" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G27" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H27" s="13">
         <v>7.9433160000000006E-3</v>
@@ -2102,997 +2108,997 @@
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="G28" s="42" t="s">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="58" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29" s="42"/>
+      <c r="G29" s="43"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>11111</v>
       </c>
-      <c r="B30" s="1">
-        <v>91.4</v>
-      </c>
-      <c r="C30" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="G30" s="42"/>
+      <c r="B30" s="20">
+        <v>92</v>
+      </c>
+      <c r="C30" s="20">
+        <v>8</v>
+      </c>
+      <c r="G30" s="43"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>11112</v>
       </c>
-      <c r="B31" s="1">
-        <v>90.5</v>
-      </c>
-      <c r="C31" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="G31" s="42"/>
+      <c r="B31" s="20">
+        <v>96</v>
+      </c>
+      <c r="C31" s="20">
+        <v>4</v>
+      </c>
+      <c r="G31" s="43"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>11121</v>
       </c>
-      <c r="B32" s="1">
-        <v>85.9</v>
-      </c>
-      <c r="C32" s="1">
-        <v>14.1</v>
-      </c>
-      <c r="G32" s="42"/>
+      <c r="B32" s="20">
+        <v>89.9</v>
+      </c>
+      <c r="C32" s="20">
+        <v>10.1</v>
+      </c>
+      <c r="G32" s="43"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>11122</v>
       </c>
-      <c r="B33" s="1">
-        <v>91.9</v>
-      </c>
-      <c r="C33" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="G33" s="42"/>
+      <c r="B33" s="20">
+        <v>97.4</v>
+      </c>
+      <c r="C33" s="20">
+        <v>2.6</v>
+      </c>
+      <c r="G33" s="43"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>11131</v>
       </c>
-      <c r="B34" s="1">
-        <v>87.7</v>
-      </c>
-      <c r="C34" s="1">
-        <v>12.3</v>
-      </c>
-      <c r="G34" s="42"/>
+      <c r="B34" s="20">
+        <v>91.3</v>
+      </c>
+      <c r="C34" s="20">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G34" s="43"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>11132</v>
       </c>
-      <c r="B35" s="1">
-        <v>86</v>
-      </c>
-      <c r="C35" s="1">
-        <v>14</v>
-      </c>
-      <c r="G35" s="42"/>
+      <c r="B35" s="20">
+        <v>91.8</v>
+      </c>
+      <c r="C35" s="20">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G35" s="43"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>11211</v>
       </c>
-      <c r="B36" s="1">
-        <v>92</v>
-      </c>
-      <c r="C36" s="1">
-        <v>8</v>
-      </c>
-      <c r="G36" s="42"/>
+      <c r="B36" s="20">
+        <v>91.4</v>
+      </c>
+      <c r="C36" s="20">
+        <v>8.6</v>
+      </c>
+      <c r="G36" s="43"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>11212</v>
       </c>
-      <c r="B37" s="1">
-        <v>96</v>
-      </c>
-      <c r="C37" s="1">
-        <v>4</v>
-      </c>
-      <c r="G37" s="42"/>
+      <c r="B37" s="20">
+        <v>90.5</v>
+      </c>
+      <c r="C37" s="20">
+        <v>9.5</v>
+      </c>
+      <c r="G37" s="43"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>11221</v>
       </c>
-      <c r="B38" s="1">
-        <v>89.9</v>
-      </c>
-      <c r="C38" s="1">
-        <v>10.1</v>
-      </c>
-      <c r="G38" s="42"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="20">
+        <v>85.9</v>
+      </c>
+      <c r="C38" s="20">
+        <v>14.1</v>
+      </c>
+      <c r="G38" s="43"/>
+    </row>
+    <row r="39" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>11222</v>
       </c>
-      <c r="B39" s="1">
-        <v>97.4</v>
-      </c>
-      <c r="C39" s="1">
-        <v>2.6</v>
+      <c r="B39" s="20">
+        <v>91.9</v>
+      </c>
+      <c r="C39" s="20">
+        <v>8.1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H39" s="1">
         <v>90.481650000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>11231</v>
       </c>
-      <c r="B40" s="1">
-        <v>91.3</v>
-      </c>
-      <c r="C40" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="20">
+        <v>87.7</v>
+      </c>
+      <c r="C40" s="20">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>11232</v>
       </c>
-      <c r="B41" s="1">
-        <v>91.8</v>
-      </c>
-      <c r="C41" s="1">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="20">
+        <v>86</v>
+      </c>
+      <c r="C41" s="20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>12111</v>
       </c>
-      <c r="B42" s="1">
-        <v>89.6</v>
-      </c>
-      <c r="C42" s="1">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="20">
+        <v>94.2</v>
+      </c>
+      <c r="C42" s="20">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>12112</v>
       </c>
-      <c r="B43" s="1">
-        <v>91.2</v>
-      </c>
-      <c r="C43" s="1">
-        <v>8.8000000000000007</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="20">
+        <v>95.1</v>
+      </c>
+      <c r="C43" s="20">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>12121</v>
       </c>
-      <c r="B44" s="1">
-        <v>92.6</v>
-      </c>
-      <c r="C44" s="1">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="20">
+        <v>92.2</v>
+      </c>
+      <c r="C44" s="20">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>12122</v>
       </c>
-      <c r="B45" s="1">
-        <v>83.8</v>
-      </c>
-      <c r="C45" s="1">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B45" s="20">
+        <v>92</v>
+      </c>
+      <c r="C45" s="20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>12131</v>
       </c>
-      <c r="B46" s="1">
-        <v>89.4</v>
-      </c>
-      <c r="C46" s="1">
-        <v>10.6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="20">
+        <v>91.9</v>
+      </c>
+      <c r="C46" s="20">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>12132</v>
       </c>
-      <c r="B47" s="1">
-        <v>90.2</v>
-      </c>
-      <c r="C47" s="1">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="20">
+        <v>93.6</v>
+      </c>
+      <c r="C47" s="20">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>12211</v>
       </c>
-      <c r="B48" s="1">
-        <v>94.2</v>
-      </c>
-      <c r="C48" s="1">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="20">
+        <v>89.6</v>
+      </c>
+      <c r="C48" s="20">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>12212</v>
       </c>
-      <c r="B49" s="1">
-        <v>95.1</v>
-      </c>
-      <c r="C49" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="20">
+        <v>91.2</v>
+      </c>
+      <c r="C49" s="20">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>12221</v>
       </c>
-      <c r="B50" s="1">
-        <v>92.2</v>
-      </c>
-      <c r="C50" s="1">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="20">
+        <v>92.6</v>
+      </c>
+      <c r="C50" s="20">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>12222</v>
       </c>
-      <c r="B51" s="1">
-        <v>92</v>
-      </c>
-      <c r="C51" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="20">
+        <v>83.8</v>
+      </c>
+      <c r="C51" s="20">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>12231</v>
       </c>
-      <c r="B52" s="1">
-        <v>91.9</v>
-      </c>
-      <c r="C52" s="1">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="20">
+        <v>89.4</v>
+      </c>
+      <c r="C52" s="20">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>12232</v>
       </c>
-      <c r="B53" s="1">
-        <v>93.6</v>
-      </c>
-      <c r="C53" s="1">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="20">
+        <v>90.2</v>
+      </c>
+      <c r="C53" s="20">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>13111</v>
       </c>
-      <c r="B54" s="1">
-        <v>90.8</v>
-      </c>
-      <c r="C54" s="1">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="20">
+        <v>89.6</v>
+      </c>
+      <c r="C54" s="20">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>13112</v>
       </c>
-      <c r="B55" s="1">
-        <v>93.7</v>
-      </c>
-      <c r="C55" s="1">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="20">
+        <v>96.8</v>
+      </c>
+      <c r="C55" s="20">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>13121</v>
       </c>
-      <c r="B56" s="1">
-        <v>84.1</v>
-      </c>
-      <c r="C56" s="1">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="20">
+        <v>85.7</v>
+      </c>
+      <c r="C56" s="20">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>13122</v>
       </c>
-      <c r="B57" s="1">
-        <v>88</v>
-      </c>
-      <c r="C57" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="20">
+        <v>88.8</v>
+      </c>
+      <c r="C57" s="20">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>13131</v>
       </c>
-      <c r="B58" s="1">
-        <v>83.9</v>
-      </c>
-      <c r="C58" s="1">
-        <v>16.100000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="20">
+        <v>89.5</v>
+      </c>
+      <c r="C58" s="20">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>13132</v>
       </c>
-      <c r="B59" s="1">
-        <v>87.6</v>
-      </c>
-      <c r="C59" s="1">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="20">
+        <v>93.3</v>
+      </c>
+      <c r="C59" s="20">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>13211</v>
       </c>
-      <c r="B60" s="1">
-        <v>89.6</v>
-      </c>
-      <c r="C60" s="1">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="20">
+        <v>90.8</v>
+      </c>
+      <c r="C60" s="20">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>13212</v>
       </c>
-      <c r="B61" s="1">
-        <v>96.8</v>
-      </c>
-      <c r="C61" s="1">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="20">
+        <v>93.7</v>
+      </c>
+      <c r="C61" s="20">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>13221</v>
       </c>
-      <c r="B62" s="1">
-        <v>85.7</v>
-      </c>
-      <c r="C62" s="1">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="20">
+        <v>84.1</v>
+      </c>
+      <c r="C62" s="20">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>13222</v>
       </c>
-      <c r="B63" s="1">
-        <v>88.8</v>
-      </c>
-      <c r="C63" s="1">
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="20">
+        <v>88</v>
+      </c>
+      <c r="C63" s="20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>13231</v>
       </c>
-      <c r="B64" s="1">
-        <v>89.5</v>
-      </c>
-      <c r="C64" s="1">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="20">
+        <v>83.9</v>
+      </c>
+      <c r="C64" s="20">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>13232</v>
       </c>
-      <c r="B65" s="1">
-        <v>93.3</v>
-      </c>
-      <c r="C65" s="1">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="20">
+        <v>87.6</v>
+      </c>
+      <c r="C65" s="20">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>21111</v>
       </c>
-      <c r="B66" s="1">
-        <v>82.8</v>
-      </c>
-      <c r="C66" s="1">
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="20">
+        <v>90</v>
+      </c>
+      <c r="C66" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>21112</v>
       </c>
-      <c r="B67" s="1">
-        <v>90.6</v>
-      </c>
-      <c r="C67" s="1">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="20">
+        <v>95.5</v>
+      </c>
+      <c r="C67" s="20">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>21121</v>
       </c>
-      <c r="B68" s="1">
-        <v>83</v>
-      </c>
-      <c r="C68" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="20">
+        <v>88.3</v>
+      </c>
+      <c r="C68" s="20">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>21122</v>
       </c>
-      <c r="B69" s="1">
-        <v>83.7</v>
-      </c>
-      <c r="C69" s="1">
-        <v>16.3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="20">
+        <v>93.8</v>
+      </c>
+      <c r="C69" s="20">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>21131</v>
       </c>
-      <c r="B70" s="1">
-        <v>80.900000000000006</v>
-      </c>
-      <c r="C70" s="1">
-        <v>19.100000000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="20">
+        <v>90.5</v>
+      </c>
+      <c r="C70" s="20">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>21132</v>
       </c>
-      <c r="B71" s="1">
-        <v>82.4</v>
-      </c>
-      <c r="C71" s="1">
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="20">
+        <v>90.2</v>
+      </c>
+      <c r="C71" s="20">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>21211</v>
       </c>
-      <c r="B72" s="1">
-        <v>90</v>
-      </c>
-      <c r="C72" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="20">
+        <v>82.8</v>
+      </c>
+      <c r="C72" s="20">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>21212</v>
       </c>
-      <c r="B73" s="1">
-        <v>95.5</v>
-      </c>
-      <c r="C73" s="1">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="20">
+        <v>90.6</v>
+      </c>
+      <c r="C73" s="20">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>21221</v>
       </c>
-      <c r="B74" s="1">
-        <v>88.3</v>
-      </c>
-      <c r="C74" s="1">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="20">
+        <v>83</v>
+      </c>
+      <c r="C74" s="20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>21222</v>
       </c>
-      <c r="B75" s="1">
-        <v>93.8</v>
-      </c>
-      <c r="C75" s="1">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="20">
+        <v>83.7</v>
+      </c>
+      <c r="C75" s="20">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>21231</v>
       </c>
-      <c r="B76" s="1">
-        <v>90.5</v>
-      </c>
-      <c r="C76" s="1">
-        <v>9.5</v>
+      <c r="B76" s="20">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="C76" s="20">
+        <v>19.100000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>21232</v>
       </c>
-      <c r="B77" s="1">
-        <v>90.2</v>
-      </c>
-      <c r="C77" s="1">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="20">
+        <v>82.4</v>
+      </c>
+      <c r="C77" s="20">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>22111</v>
       </c>
-      <c r="B78" s="1">
-        <v>84.1</v>
-      </c>
-      <c r="C78" s="1">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="20">
+        <v>86.3</v>
+      </c>
+      <c r="C78" s="20">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>22112</v>
       </c>
-      <c r="B79" s="1">
-        <v>89.6</v>
-      </c>
-      <c r="C79" s="1">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="20">
+        <v>97.4</v>
+      </c>
+      <c r="C79" s="20">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>22121</v>
       </c>
-      <c r="B80" s="1">
-        <v>79.5</v>
-      </c>
-      <c r="C80" s="1">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="20">
+        <v>86.6</v>
+      </c>
+      <c r="C80" s="20">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>22122</v>
       </c>
-      <c r="B81" s="1">
-        <v>78.900000000000006</v>
-      </c>
-      <c r="C81" s="1">
-        <v>21.1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="20">
+        <v>93</v>
+      </c>
+      <c r="C81" s="20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>22131</v>
       </c>
-      <c r="B82" s="1">
-        <v>78.8</v>
-      </c>
-      <c r="C82" s="1">
-        <v>21.2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="20">
+        <v>86.8</v>
+      </c>
+      <c r="C82" s="20">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>22132</v>
       </c>
-      <c r="B83" s="1">
-        <v>77.7</v>
-      </c>
-      <c r="C83" s="1">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B83" s="20">
+        <v>89.8</v>
+      </c>
+      <c r="C83" s="20">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>22211</v>
       </c>
-      <c r="B84" s="1">
-        <v>86.3</v>
-      </c>
-      <c r="C84" s="1">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B84" s="20">
+        <v>84.1</v>
+      </c>
+      <c r="C84" s="20">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>22212</v>
       </c>
-      <c r="B85" s="1">
-        <v>97.4</v>
-      </c>
-      <c r="C85" s="1">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B85" s="20">
+        <v>89.6</v>
+      </c>
+      <c r="C85" s="20">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>22221</v>
       </c>
-      <c r="B86" s="1">
-        <v>86.6</v>
-      </c>
-      <c r="C86" s="1">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B86" s="20">
+        <v>79.5</v>
+      </c>
+      <c r="C86" s="20">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>22222</v>
       </c>
-      <c r="B87" s="1">
-        <v>93</v>
-      </c>
-      <c r="C87" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B87" s="20">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="C87" s="20">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>22231</v>
       </c>
-      <c r="B88" s="1">
-        <v>86.8</v>
-      </c>
-      <c r="C88" s="1">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B88" s="20">
+        <v>78.8</v>
+      </c>
+      <c r="C88" s="20">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>22232</v>
       </c>
-      <c r="B89" s="1">
-        <v>89.8</v>
-      </c>
-      <c r="C89" s="1">
-        <v>10.199999999999999</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B89" s="20">
+        <v>77.7</v>
+      </c>
+      <c r="C89" s="20">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>23111</v>
       </c>
-      <c r="B90" s="1">
-        <v>77.7</v>
-      </c>
-      <c r="C90" s="1">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="20">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="C90" s="20">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>23112</v>
       </c>
-      <c r="B91" s="1">
-        <v>80.8</v>
-      </c>
-      <c r="C91" s="1">
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="20">
+        <v>77.8</v>
+      </c>
+      <c r="C91" s="20">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>23121</v>
       </c>
-      <c r="B92" s="1">
-        <v>67.8</v>
-      </c>
-      <c r="C92" s="1">
-        <v>32.200000000000003</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B92" s="20">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="C92" s="20">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>23122</v>
       </c>
-      <c r="B93" s="1">
-        <v>77.099999999999994</v>
-      </c>
-      <c r="C93" s="1">
-        <v>22.9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="20">
+        <v>87.4</v>
+      </c>
+      <c r="C93" s="20">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>23131</v>
       </c>
-      <c r="B94" s="1">
-        <v>67.599999999999994</v>
-      </c>
-      <c r="C94" s="1">
-        <v>32.4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B94" s="20">
+        <v>76.599999999999994</v>
+      </c>
+      <c r="C94" s="20">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>23132</v>
       </c>
-      <c r="B95" s="1">
-        <v>72.3</v>
-      </c>
-      <c r="C95" s="1">
-        <v>27.7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B95" s="20">
+        <v>86.9</v>
+      </c>
+      <c r="C95" s="20">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>23211</v>
       </c>
-      <c r="B96" s="1">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="C96" s="1">
-        <v>24.1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="B96" s="20">
+        <v>77.7</v>
+      </c>
+      <c r="C96" s="20">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:34" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>23212</v>
       </c>
-      <c r="B97" s="1">
-        <v>77.8</v>
-      </c>
-      <c r="C97" s="1">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="B97" s="20">
+        <v>80.8</v>
+      </c>
+      <c r="C97" s="20">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:34" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>23221</v>
       </c>
-      <c r="B98" s="1">
-        <v>72.400000000000006</v>
-      </c>
-      <c r="C98" s="1">
-        <v>27.6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="B98" s="20">
+        <v>67.8</v>
+      </c>
+      <c r="C98" s="20">
+        <v>32.200000000000003</v>
+      </c>
+    </row>
+    <row r="99" spans="1:34" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>23222</v>
       </c>
-      <c r="B99" s="1">
-        <v>87.4</v>
-      </c>
-      <c r="C99" s="1">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="B99" s="20">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="C99" s="20">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:34" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>23231</v>
       </c>
-      <c r="B100" s="1">
-        <v>76.599999999999994</v>
-      </c>
-      <c r="C100" s="1">
-        <v>23.4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="B100" s="20">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="C100" s="20">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:34" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>23232</v>
       </c>
       <c r="B101" s="1">
-        <v>86.9</v>
+        <v>72.3</v>
       </c>
       <c r="C101" s="1">
-        <v>13.1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:34" x14ac:dyDescent="0.25">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:34" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="H105" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="V105" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="V105" s="2" t="s">
+      <c r="AB105" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AB105" s="2" t="s">
+    </row>
+    <row r="106" spans="1:34" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="53" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="106" spans="1:34" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="46" t="s">
+      <c r="B106" s="53"/>
+      <c r="D106" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="B106" s="46"/>
-      <c r="D106" s="47" t="s">
+      <c r="E106" s="54"/>
+      <c r="F106" s="54"/>
+      <c r="H106" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="E106" s="47"/>
-      <c r="F106" s="47"/>
-      <c r="H106" s="48" t="s">
+      <c r="I106" s="55"/>
+      <c r="J106" s="55"/>
+      <c r="K106" s="55"/>
+      <c r="L106" s="55"/>
+      <c r="M106" s="55"/>
+      <c r="N106" s="55"/>
+      <c r="O106" s="55"/>
+      <c r="P106" s="55"/>
+      <c r="Q106" s="55"/>
+      <c r="R106" s="55"/>
+      <c r="S106" s="55"/>
+      <c r="V106" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="I106" s="48"/>
-      <c r="J106" s="48"/>
-      <c r="K106" s="48"/>
-      <c r="L106" s="48"/>
-      <c r="M106" s="48"/>
-      <c r="N106" s="48"/>
-      <c r="O106" s="48"/>
-      <c r="P106" s="48"/>
-      <c r="Q106" s="48"/>
-      <c r="R106" s="48"/>
-      <c r="S106" s="48"/>
-      <c r="V106" s="51" t="s">
+      <c r="W106" s="52"/>
+      <c r="X106" s="52"/>
+      <c r="Y106" s="52"/>
+      <c r="Z106" s="52"/>
+      <c r="AB106" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="W106" s="51"/>
-      <c r="X106" s="51"/>
-      <c r="Y106" s="51"/>
-      <c r="Z106" s="51"/>
-      <c r="AB106" s="2" t="s">
+      <c r="AC106" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="AC106" s="15" t="s">
+      <c r="AD106" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="AD106" s="15" t="s">
+      <c r="AE106" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="AE106" s="15" t="s">
+      <c r="AF106" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AF106" s="2" t="s">
+      <c r="AG106" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="AG106" s="15" t="s">
+      <c r="AH106" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AH106" s="2" t="s">
+    </row>
+    <row r="107" spans="1:34" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="46" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="107" spans="1:34" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="52" t="s">
+      <c r="B107" s="46"/>
+      <c r="D107" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B107" s="52"/>
-      <c r="D107" s="17" t="s">
+      <c r="E107" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E107" s="17" t="s">
+      <c r="F107" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="F107" s="17" t="s">
+      <c r="H107" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I107" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J107" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K107" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L107" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M107" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N107" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="H107" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="I107" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="J107" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="K107" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="L107" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="M107" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="N107" s="15" t="s">
+      <c r="O107" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="O107" s="15" t="s">
+      <c r="P107" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="P107" s="15" t="s">
+      <c r="Q107" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="Q107" s="15" t="s">
+      <c r="R107" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="R107" s="15" t="s">
+      <c r="S107" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="S107" s="15" t="s">
+      <c r="T107" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T107" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="V107" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="W107" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="W107" s="18" t="s">
+      <c r="X107" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="X107" s="18" t="s">
-        <v>11</v>
-      </c>
       <c r="Y107" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z107" s="18" t="s">
         <v>10</v>
-      </c>
-      <c r="Z107" s="18" t="s">
-        <v>11</v>
       </c>
       <c r="AB107" s="1">
         <v>1</v>
       </c>
       <c r="AC107" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD107" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="AD107" s="20" t="s">
+      <c r="AE107" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AE107" s="1" t="s">
+      <c r="AF107" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AF107" s="1" t="s">
+      <c r="AG107" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="AG107" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="AH107" s="1">
         <v>11212</v>
       </c>
     </row>
-    <row r="108" spans="1:34" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:34" ht="18" x14ac:dyDescent="0.25">
       <c r="A108" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B108" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B108" s="22" t="s">
+      <c r="D108" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="E108" s="1">
         <v>66</v>
@@ -3101,19 +3107,19 @@
         <v>0.91700000000000004</v>
       </c>
       <c r="H108" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I108" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I108" s="20" t="s">
-        <v>77</v>
-      </c>
       <c r="J108" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K108" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L108" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L108" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M108" s="20">
         <v>11111</v>
@@ -3140,49 +3146,49 @@
         <v>8.9762632060429504E-2</v>
       </c>
       <c r="V108" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W108" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="X108" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="W108" s="7" t="s">
+      <c r="Y108" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="X108" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y108" s="7" t="s">
-        <v>87</v>
-      </c>
       <c r="Z108" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB108" s="1">
         <v>2</v>
       </c>
       <c r="AC108" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AD108" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AE108" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF108" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AF108" s="1" t="s">
+      <c r="AG108" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="AG108" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="AH108" s="1">
         <v>12212</v>
       </c>
     </row>
-    <row r="109" spans="1:34" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:34" ht="18" x14ac:dyDescent="0.25">
       <c r="A109" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B109" s="16"/>
       <c r="D109" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E109" s="1">
         <v>72</v>
@@ -3191,19 +3197,19 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="H109" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I109" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I109" s="20" t="s">
-        <v>77</v>
-      </c>
       <c r="J109" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K109" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L109" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="K109" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L109" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="M109" s="20">
         <v>11112</v>
@@ -3230,33 +3236,33 @@
         <v>6.9559306101678195E-2</v>
       </c>
       <c r="V109" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="W109" s="7"/>
       <c r="X109" s="7"/>
       <c r="Y109" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Z109" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB109" s="1">
         <v>4</v>
       </c>
       <c r="AC109" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD109" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="AD109" s="20" t="s">
+      <c r="AE109" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AE109" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="AF109" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG109" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH109" s="1">
         <v>11222</v>
@@ -3264,25 +3270,25 @@
     </row>
     <row r="110" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A110" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B110" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B110" s="16" t="s">
-        <v>94</v>
-      </c>
       <c r="H110" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I110" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I110" s="20" t="s">
+      <c r="J110" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K110" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J110" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="K110" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="L110" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M110" s="27">
         <v>11211</v>
@@ -3309,7 +3315,7 @@
         <v>5.7532332612191997E-2</v>
       </c>
       <c r="V110" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W110" s="7"/>
       <c r="X110" s="7"/>
@@ -3317,51 +3323,51 @@
         <v>1.05</v>
       </c>
       <c r="Z110" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB110" s="1">
         <v>6</v>
       </c>
       <c r="AC110" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AD110" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AE110" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF110" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AF110" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="AG110" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH110" s="1">
         <v>12211</v>
       </c>
     </row>
-    <row r="111" spans="1:34" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:34" ht="18" x14ac:dyDescent="0.25">
       <c r="A111" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B111" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B111" s="16" t="s">
-        <v>97</v>
-      </c>
       <c r="H111" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="I111" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="I111" s="29" t="s">
+      <c r="J111" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="K111" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="J111" s="29" t="s">
+      <c r="L111" s="29" t="s">
         <v>79</v>
-      </c>
-      <c r="K111" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="L111" s="29" t="s">
-        <v>80</v>
       </c>
       <c r="M111" s="29">
         <v>11212</v>
@@ -3388,33 +3394,33 @@
         <v>4.4230740187191302E-2</v>
       </c>
       <c r="V111" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="W111" s="7"/>
       <c r="X111" s="7"/>
       <c r="Y111" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Z111" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB111" s="1">
         <v>8</v>
       </c>
       <c r="AC111" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AD111" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AE111" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AF111" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG111" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH111" s="1">
         <v>12232</v>
@@ -3422,23 +3428,23 @@
     </row>
     <row r="112" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B112" s="16"/>
       <c r="H112" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I112" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I112" s="20" t="s">
-        <v>77</v>
-      </c>
       <c r="J112" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K112" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L112" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L112" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M112" s="20">
         <v>11121</v>
@@ -3465,33 +3471,33 @@
         <v>0.116647799381551</v>
       </c>
       <c r="V112" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W112" s="20"/>
       <c r="X112" s="20"/>
       <c r="Y112" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z112" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB112" s="1">
         <v>3</v>
       </c>
       <c r="AC112" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD112" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="AD112" s="20" t="s">
+      <c r="AE112" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AE112" s="1" t="s">
+      <c r="AF112" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AF112" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="AG112" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH112" s="1">
         <v>11211</v>
@@ -3499,25 +3505,25 @@
     </row>
     <row r="113" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B113" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B113" s="16" t="s">
-        <v>105</v>
-      </c>
       <c r="H113" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I113" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I113" s="20" t="s">
-        <v>77</v>
-      </c>
       <c r="J113" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K113" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L113" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M113" s="20">
         <v>11122</v>
@@ -3544,39 +3550,39 @@
         <v>9.0998242389662198E-2</v>
       </c>
       <c r="V113" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="W113" s="20"/>
       <c r="X113" s="20"/>
       <c r="Y113" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z113" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="Z113" s="20" t="s">
+      <c r="AC113" s="19"/>
+    </row>
+    <row r="114" spans="1:34" ht="18" x14ac:dyDescent="0.25">
+      <c r="A114" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="AC113" s="19"/>
-    </row>
-    <row r="114" spans="1:34" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="A114" s="26" t="s">
+      <c r="B114" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B114" s="16" t="s">
-        <v>110</v>
-      </c>
       <c r="H114" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I114" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I114" s="20" t="s">
+      <c r="J114" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="K114" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J114" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K114" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="L114" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M114" s="20">
         <v>11221</v>
@@ -3603,42 +3609,42 @@
         <v>7.5565474886209599E-2</v>
       </c>
       <c r="V114" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W114" s="7"/>
       <c r="X114" s="7"/>
       <c r="Y114" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z114" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB114" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="Z114" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB114" s="2" t="s">
+      <c r="AC114" s="19"/>
+    </row>
+    <row r="115" spans="1:34" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="AC114" s="19"/>
-    </row>
-    <row r="115" spans="1:34" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A115" s="26" t="s">
+      <c r="B115" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B115" s="16" t="s">
-        <v>115</v>
-      </c>
       <c r="H115" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="I115" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="I115" s="29" t="s">
+      <c r="J115" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="K115" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="J115" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="K115" s="29" t="s">
-        <v>78</v>
-      </c>
       <c r="L115" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M115" s="29">
         <v>11222</v>
@@ -3665,57 +3671,57 @@
         <v>5.8352724703792998E-2</v>
       </c>
       <c r="V115" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W115" s="7"/>
       <c r="X115" s="7"/>
       <c r="Y115" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Z115" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB115" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC115" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="AC115" s="15" t="s">
+      <c r="AD115" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="AD115" s="15" t="s">
+      <c r="AE115" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="AE115" s="15" t="s">
+      <c r="AF115" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AF115" s="2" t="s">
+      <c r="AG115" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="AG115" s="15" t="s">
+      <c r="AH115" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AH115" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:34" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A116" s="25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B116" s="16"/>
       <c r="H116" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I116" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I116" s="20" t="s">
-        <v>77</v>
-      </c>
       <c r="J116" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K116" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L116" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L116" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M116" s="20">
         <v>11131</v>
@@ -3741,56 +3747,56 @@
       <c r="T116" s="1">
         <v>0.118312327125455</v>
       </c>
-      <c r="V116" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="W116" s="45"/>
-      <c r="X116" s="45"/>
-      <c r="Y116" s="45"/>
-      <c r="Z116" s="45"/>
+      <c r="V116" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="W116" s="47"/>
+      <c r="X116" s="47"/>
+      <c r="Y116" s="47"/>
+      <c r="Z116" s="47"/>
       <c r="AB116" s="1">
         <v>72</v>
       </c>
       <c r="AC116" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD116" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AD116" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="AE116" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF116" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG116" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="AF116" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG116" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="AH116" s="1">
         <v>23131</v>
       </c>
     </row>
-    <row r="117" spans="1:34" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:34" ht="18" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B117" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B117" s="16" t="s">
-        <v>121</v>
-      </c>
       <c r="H117" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I117" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I117" s="20" t="s">
-        <v>77</v>
-      </c>
       <c r="J117" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K117" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L117" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M117" s="20">
         <v>11132</v>
@@ -3817,59 +3823,59 @@
         <v>9.2335017357180804E-2</v>
       </c>
       <c r="V117" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="W117" s="42">
+        <v>20</v>
+      </c>
+      <c r="W117" s="43">
         <v>3.29</v>
       </c>
-      <c r="X117" s="42"/>
-      <c r="Y117" s="42">
+      <c r="X117" s="43"/>
+      <c r="Y117" s="43">
         <v>3.29</v>
       </c>
-      <c r="Z117" s="42"/>
+      <c r="Z117" s="43"/>
       <c r="AB117" s="1">
         <v>71</v>
       </c>
       <c r="AC117" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD117" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AD117" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="AE117" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF117" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG117" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="AF117" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG117" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="AH117" s="1">
         <v>23121</v>
       </c>
     </row>
-    <row r="118" spans="1:34" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:34" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A118" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B118" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="B118" s="16" t="s">
-        <v>123</v>
-      </c>
       <c r="H118" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I118" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I118" s="20" t="s">
+      <c r="J118" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="K118" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J118" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K118" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="L118" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M118" s="20">
         <v>11231</v>
@@ -3896,33 +3902,33 @@
         <v>7.6694668669867502E-2</v>
       </c>
       <c r="V118" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="W118" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="W118" s="42" t="s">
+      <c r="X118" s="43"/>
+      <c r="Y118" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="X118" s="42"/>
-      <c r="Y118" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z118" s="42"/>
+      <c r="Z118" s="43"/>
       <c r="AB118" s="1">
         <v>70</v>
       </c>
       <c r="AC118" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD118" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AD118" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="AE118" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF118" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG118" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH118" s="1">
         <v>23132</v>
@@ -3930,25 +3936,25 @@
     </row>
     <row r="119" spans="1:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B119" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B119" s="16" t="s">
-        <v>128</v>
-      </c>
       <c r="H119" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I119" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I119" s="20" t="s">
+      <c r="J119" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="K119" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J119" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K119" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="L119" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M119" s="20">
         <v>11232</v>
@@ -3975,57 +3981,57 @@
         <v>5.9241187311079802E-2</v>
       </c>
       <c r="V119" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="W119" s="42">
+        <v>26</v>
+      </c>
+      <c r="W119" s="43">
         <v>0.08</v>
       </c>
-      <c r="X119" s="42"/>
-      <c r="Y119" s="42">
+      <c r="X119" s="43"/>
+      <c r="Y119" s="43">
         <v>0.01</v>
       </c>
-      <c r="Z119" s="42"/>
+      <c r="Z119" s="43"/>
       <c r="AB119" s="1">
         <v>64</v>
       </c>
       <c r="AC119" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD119" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AD119" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="AE119" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AF119" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG119" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH119" s="1">
         <v>23221</v>
       </c>
     </row>
-    <row r="120" spans="1:34" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:34" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B120" s="16"/>
       <c r="H120" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I120" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J120" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K120" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L120" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L120" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M120" s="20">
         <v>12111</v>
@@ -4052,59 +4058,59 @@
         <v>9.3833068114483498E-2</v>
       </c>
       <c r="V120" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="W120" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="W120" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="X120" s="56"/>
-      <c r="Y120" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z120" s="56"/>
+      <c r="X120" s="44"/>
+      <c r="Y120" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z120" s="44"/>
       <c r="AB120" s="1">
         <v>69</v>
       </c>
       <c r="AC120" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD120" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AD120" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="AE120" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF120" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG120" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH120" s="1">
         <v>23122</v>
       </c>
     </row>
-    <row r="121" spans="1:34" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:34" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B121" s="16" t="s">
-        <v>132</v>
-      </c>
       <c r="H121" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I121" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J121" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K121" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L121" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="K121" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L121" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="M121" s="20">
         <v>12112</v>
@@ -4131,59 +4137,59 @@
         <v>7.2786848618168198E-2</v>
       </c>
       <c r="V121" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="W121" s="57">
+        <v>31</v>
+      </c>
+      <c r="W121" s="45">
         <v>19500</v>
       </c>
-      <c r="X121" s="57"/>
-      <c r="Y121" s="57">
+      <c r="X121" s="45"/>
+      <c r="Y121" s="45">
         <v>19500</v>
       </c>
-      <c r="Z121" s="57"/>
+      <c r="Z121" s="45"/>
       <c r="AB121" s="1">
         <v>68</v>
       </c>
       <c r="AC121" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD121" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AD121" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="AE121" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF121" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG121" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="AF121" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG121" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="AH121" s="1">
         <v>23111</v>
       </c>
     </row>
-    <row r="122" spans="1:34" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:34" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B122" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B122" s="16" t="s">
-        <v>134</v>
-      </c>
       <c r="H122" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I122" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J122" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K122" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L122" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M122" s="27">
         <v>12211</v>
@@ -4210,36 +4216,36 @@
         <v>6.0237954052970701E-2</v>
       </c>
       <c r="V122" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="W122" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="W122" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="X122" s="53"/>
-      <c r="Y122" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z122" s="53"/>
-    </row>
-    <row r="123" spans="1:34" ht="42" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="X122" s="48"/>
+      <c r="Y122" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z122" s="48"/>
+    </row>
+    <row r="123" spans="1:34" ht="43.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A123" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B123" s="16"/>
       <c r="H123" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I123" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J123" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K123" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="L123" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="K123" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="L123" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="M123" s="27">
         <v>12212</v>
@@ -4265,35 +4271,35 @@
       <c r="T123" s="1">
         <v>4.6341574791248501E-2</v>
       </c>
-      <c r="V123" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="W123" s="54"/>
-      <c r="X123" s="54"/>
-      <c r="Y123" s="54"/>
-      <c r="Z123" s="54"/>
+      <c r="V123" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="W123" s="41"/>
+      <c r="X123" s="41"/>
+      <c r="Y123" s="41"/>
+      <c r="Z123" s="41"/>
     </row>
     <row r="124" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B124" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B124" s="16" t="s">
-        <v>138</v>
-      </c>
       <c r="H124" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I124" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J124" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K124" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L124" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L124" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M124" s="20">
         <v>12121</v>
@@ -4320,7 +4326,7 @@
         <v>0.121774286221144</v>
       </c>
       <c r="V124" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="W124" s="1">
         <v>7.7593629999999997E-2</v>
@@ -4328,25 +4334,25 @@
     </row>
     <row r="125" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B125" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B125" s="16" t="s">
-        <v>141</v>
-      </c>
       <c r="H125" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I125" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J125" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K125" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L125" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M125" s="20">
         <v>12122</v>
@@ -4373,31 +4379,31 @@
         <v>9.5118854091113897E-2</v>
       </c>
       <c r="V125" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="W125" s="1">
         <v>7.9433160000000006E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:34" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A126" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B126" s="16"/>
       <c r="H126" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I126" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J126" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K126" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L126" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M126" s="20">
         <v>12221</v>
@@ -4424,7 +4430,7 @@
         <v>7.9048026381755898E-2</v>
       </c>
       <c r="V126" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="W126" s="1">
         <v>90.481650000000002</v>
@@ -4432,25 +4438,25 @@
     </row>
     <row r="127" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B127" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="B127" s="16" t="s">
-        <v>146</v>
-      </c>
       <c r="H127" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I127" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J127" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K127" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L127" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M127" s="20">
         <v>12222</v>
@@ -4480,25 +4486,25 @@
     </row>
     <row r="128" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A128" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B128" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B128" s="16" t="s">
-        <v>148</v>
-      </c>
       <c r="H128" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I128" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J128" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K128" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L128" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L128" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M128" s="20">
         <v>12131</v>
@@ -4525,32 +4531,32 @@
         <v>0.123501739739745</v>
       </c>
       <c r="V128" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W128" s="1">
         <v>0.64980000000000004</v>
       </c>
       <c r="AC128" s="19"/>
     </row>
-    <row r="129" spans="1:29" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="A129" s="55" t="s">
-        <v>150</v>
-      </c>
-      <c r="B129" s="55"/>
+    <row r="129" spans="1:29" ht="18" x14ac:dyDescent="0.25">
+      <c r="A129" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="B129" s="42"/>
       <c r="H129" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I129" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J129" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K129" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L129" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M129" s="20">
         <v>12132</v>
@@ -4577,28 +4583,28 @@
         <v>9.6509734553624299E-2</v>
       </c>
       <c r="V129" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="W129" s="1">
         <v>0.5</v>
       </c>
       <c r="AC129" s="19"/>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H130" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I130" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J130" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K130" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L130" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M130" s="20">
         <v>12231</v>
@@ -4625,31 +4631,31 @@
         <v>8.0224744586154306E-2</v>
       </c>
       <c r="V130" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="W130" s="1">
         <v>0.6452</v>
       </c>
       <c r="AC130" s="19"/>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H131" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I131" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J131" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K131" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L131" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M131" s="27">
         <v>12232</v>
@@ -4676,27 +4682,27 @@
         <v>6.2021883925275002E-2</v>
       </c>
       <c r="V131" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="W131" s="1">
         <v>0.63470000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H132" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I132" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J132" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K132" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L132" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L132" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M132" s="20">
         <v>13111</v>
@@ -4723,21 +4729,21 @@
         <v>0.139391009541528</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H133" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I133" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J133" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K133" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L133" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="K133" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L133" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="M133" s="20">
         <v>13112</v>
@@ -4764,24 +4770,24 @@
         <v>0.10935959759288</v>
       </c>
       <c r="V133" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="134" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H134" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I134" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J134" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K134" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L134" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M134" s="20">
         <v>13211</v>
@@ -4808,24 +4814,24 @@
         <v>9.1125020130950807E-2</v>
       </c>
       <c r="V134" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="135" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H135" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I135" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J135" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="K135" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="L135" s="29" t="s">
         <v>79</v>
-      </c>
-      <c r="K135" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="L135" s="29" t="s">
-        <v>80</v>
       </c>
       <c r="M135" s="29">
         <v>13212</v>
@@ -4852,24 +4858,24 @@
         <v>7.0638851373286904E-2</v>
       </c>
       <c r="V135" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="136" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H136" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I136" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J136" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K136" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L136" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L136" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M136" s="20">
         <v>13121</v>
@@ -4896,21 +4902,21 @@
         <v>0.17823003270863499</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H137" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I137" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J137" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K137" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L137" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M137" s="20">
         <v>13122</v>
@@ -4937,21 +4943,21 @@
         <v>0.14120379374994499</v>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H138" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I138" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J138" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K138" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L138" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M138" s="20">
         <v>13221</v>
@@ -4978,21 +4984,21 @@
         <v>0.11836517933834199</v>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H139" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I139" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J139" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K139" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L139" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M139" s="20">
         <v>13222</v>
@@ -5019,21 +5025,21 @@
         <v>9.2377480891863498E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H140" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I140" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J140" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K140" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L140" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L140" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M140" s="20">
         <v>13131</v>
@@ -5060,21 +5066,21 @@
         <v>0.180593665048114</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H141" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I141" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J141" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K141" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L141" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M141" s="20">
         <v>13132</v>
@@ -5101,21 +5107,21 @@
         <v>0.14316193868868901</v>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H142" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I142" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J142" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K142" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L142" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M142" s="20">
         <v>13231</v>
@@ -5142,21 +5148,21 @@
         <v>0.120050883036739</v>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H143" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I143" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J143" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K143" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L143" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M143" s="20">
         <v>13232</v>
@@ -5184,21 +5190,21 @@
       </c>
       <c r="AC143" s="19"/>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H144" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I144" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J144" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K144" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L144" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L144" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M144" s="20">
         <v>21111</v>
@@ -5226,21 +5232,21 @@
       </c>
       <c r="AC144" s="19"/>
     </row>
-    <row r="145" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="145" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H145" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I145" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J145" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K145" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L145" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="K145" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L145" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="M145" s="20">
         <v>21112</v>
@@ -5268,21 +5274,21 @@
       </c>
       <c r="AC145" s="19"/>
     </row>
-    <row r="146" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="146" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H146" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I146" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J146" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K146" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J146" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="K146" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="L146" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M146" s="20">
         <v>21211</v>
@@ -5310,21 +5316,21 @@
       </c>
       <c r="AC146" s="19"/>
     </row>
-    <row r="147" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="147" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H147" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I147" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="J147" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="K147" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="J147" s="29" t="s">
+      <c r="L147" s="29" t="s">
         <v>79</v>
-      </c>
-      <c r="K147" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="L147" s="29" t="s">
-        <v>80</v>
       </c>
       <c r="M147" s="29">
         <v>21212</v>
@@ -5352,21 +5358,21 @@
       </c>
       <c r="AC147" s="19"/>
     </row>
-    <row r="148" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="148" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H148" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I148" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J148" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K148" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L148" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L148" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M148" s="20">
         <v>21121</v>
@@ -5394,21 +5400,21 @@
       </c>
       <c r="AC148" s="19"/>
     </row>
-    <row r="149" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="149" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H149" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I149" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J149" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K149" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L149" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M149" s="20">
         <v>21122</v>
@@ -5436,21 +5442,21 @@
       </c>
       <c r="AC149" s="19"/>
     </row>
-    <row r="150" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="150" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H150" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I150" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J150" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="K150" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J150" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K150" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="L150" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M150" s="20">
         <v>21221</v>
@@ -5478,21 +5484,21 @@
       </c>
       <c r="AC150" s="19"/>
     </row>
-    <row r="151" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="151" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H151" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I151" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J151" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="K151" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J151" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K151" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="L151" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M151" s="20">
         <v>21222</v>
@@ -5520,21 +5526,21 @@
       </c>
       <c r="AC151" s="19"/>
     </row>
-    <row r="152" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="152" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H152" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I152" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J152" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K152" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L152" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L152" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M152" s="20">
         <v>21131</v>
@@ -5562,21 +5568,21 @@
       </c>
       <c r="AC152" s="19"/>
     </row>
-    <row r="153" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="153" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H153" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I153" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J153" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K153" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L153" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M153" s="20">
         <v>21132</v>
@@ -5604,21 +5610,21 @@
       </c>
       <c r="AC153" s="19"/>
     </row>
-    <row r="154" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="154" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H154" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I154" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J154" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="K154" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J154" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K154" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="L154" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M154" s="20">
         <v>21231</v>
@@ -5646,21 +5652,21 @@
       </c>
       <c r="AC154" s="19"/>
     </row>
-    <row r="155" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="155" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H155" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I155" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J155" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="K155" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="J155" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K155" s="20" t="s">
-        <v>78</v>
-      </c>
       <c r="L155" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M155" s="20">
         <v>21232</v>
@@ -5688,21 +5694,21 @@
       </c>
       <c r="AC155" s="19"/>
     </row>
-    <row r="156" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="156" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H156" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I156" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J156" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K156" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L156" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L156" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M156" s="20">
         <v>22111</v>
@@ -5730,21 +5736,21 @@
       </c>
       <c r="AC156" s="19"/>
     </row>
-    <row r="157" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="157" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H157" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I157" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J157" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K157" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L157" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="K157" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L157" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="M157" s="20">
         <v>22112</v>
@@ -5772,21 +5778,21 @@
       </c>
       <c r="AC157" s="19"/>
     </row>
-    <row r="158" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="158" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H158" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I158" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J158" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K158" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L158" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M158" s="20">
         <v>22211</v>
@@ -5814,21 +5820,21 @@
       </c>
       <c r="AC158" s="19"/>
     </row>
-    <row r="159" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="159" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H159" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I159" s="29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J159" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="K159" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="L159" s="29" t="s">
         <v>79</v>
-      </c>
-      <c r="K159" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="L159" s="29" t="s">
-        <v>80</v>
       </c>
       <c r="M159" s="29">
         <v>22212</v>
@@ -5856,21 +5862,21 @@
       </c>
       <c r="AC159" s="19"/>
     </row>
-    <row r="160" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="160" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H160" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I160" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J160" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K160" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L160" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L160" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M160" s="20">
         <v>22121</v>
@@ -5898,21 +5904,21 @@
       </c>
       <c r="AC160" s="19"/>
     </row>
-    <row r="161" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="161" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H161" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I161" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J161" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K161" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L161" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M161" s="20">
         <v>22122</v>
@@ -5940,21 +5946,21 @@
       </c>
       <c r="AC161" s="19"/>
     </row>
-    <row r="162" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="162" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H162" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I162" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J162" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K162" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L162" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M162" s="20">
         <v>22221</v>
@@ -5982,21 +5988,21 @@
       </c>
       <c r="AC162" s="19"/>
     </row>
-    <row r="163" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="163" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H163" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I163" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J163" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K163" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L163" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M163" s="20">
         <v>22222</v>
@@ -6024,21 +6030,21 @@
       </c>
       <c r="AC163" s="19"/>
     </row>
-    <row r="164" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="164" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H164" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I164" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J164" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K164" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L164" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L164" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M164" s="20">
         <v>22131</v>
@@ -6066,21 +6072,21 @@
       </c>
       <c r="AC164" s="19"/>
     </row>
-    <row r="165" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="165" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H165" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I165" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J165" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K165" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L165" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M165" s="20">
         <v>22132</v>
@@ -6108,21 +6114,21 @@
       </c>
       <c r="AC165" s="19"/>
     </row>
-    <row r="166" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="166" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H166" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I166" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J166" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K166" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L166" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M166" s="20">
         <v>22231</v>
@@ -6150,21 +6156,21 @@
       </c>
       <c r="AC166" s="19"/>
     </row>
-    <row r="167" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="167" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H167" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I167" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J167" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K167" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L167" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M167" s="20">
         <v>22232</v>
@@ -6191,21 +6197,21 @@
         <v>0.111872321786775</v>
       </c>
     </row>
-    <row r="168" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="168" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H168" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="I168" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I168" s="20" t="s">
-        <v>119</v>
-      </c>
       <c r="J168" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K168" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L168" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="L168" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="M168" s="20">
         <v>23111</v>
@@ -6232,21 +6238,21 @@
         <v>0.23579465421854601</v>
       </c>
     </row>
-    <row r="169" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="169" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H169" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="I169" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I169" s="20" t="s">
-        <v>119</v>
-      </c>
       <c r="J169" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K169" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="L169" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="K169" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L169" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="M169" s="20">
         <v>23112</v>
@@ -6273,21 +6279,21 @@
         <v>0.189568375891911</v>
       </c>
     </row>
-    <row r="170" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="170" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H170" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="I170" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="I170" s="33" t="s">
-        <v>119</v>
-      </c>
       <c r="J170" s="33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K170" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L170" s="33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M170" s="33">
         <v>23211</v>
@@ -6314,21 +6320,21 @@
         <v>0.16036792463802099</v>
       </c>
     </row>
-    <row r="171" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="171" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H171" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="I171" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I171" s="20" t="s">
-        <v>119</v>
-      </c>
       <c r="J171" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K171" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="L171" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="K171" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="L171" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="M171" s="20">
         <v>23212</v>
@@ -6355,21 +6361,21 @@
         <v>0.12648130006873501</v>
       </c>
     </row>
-    <row r="172" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="172" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H172" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="I172" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="I172" s="33" t="s">
-        <v>119</v>
-      </c>
       <c r="J172" s="33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K172" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="L172" s="33" t="s">
         <v>84</v>
-      </c>
-      <c r="L172" s="33" t="s">
-        <v>85</v>
       </c>
       <c r="M172" s="33">
         <v>23121</v>
@@ -6396,21 +6402,21 @@
         <v>0.29236954694454897</v>
       </c>
     </row>
-    <row r="173" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="173" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H173" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="I173" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I173" s="20" t="s">
-        <v>119</v>
-      </c>
       <c r="J173" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K173" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L173" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M173" s="20">
         <v>23122</v>
@@ -6437,21 +6443,21 @@
         <v>0.23851370472674199</v>
       </c>
     </row>
-    <row r="174" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H174" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="I174" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="I174" s="33" t="s">
-        <v>119</v>
-      </c>
       <c r="J174" s="33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K174" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L174" s="33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M174" s="33">
         <v>23221</v>
@@ -6478,21 +6484,21 @@
         <v>0.203668595192976</v>
       </c>
     </row>
-    <row r="175" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="175" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H175" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="I175" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I175" s="20" t="s">
-        <v>119</v>
-      </c>
       <c r="J175" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K175" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L175" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M175" s="20">
         <v>23222</v>
@@ -6519,21 +6525,21 @@
         <v>0.162402034247005</v>
       </c>
     </row>
-    <row r="176" spans="8:29" x14ac:dyDescent="0.25">
+    <row r="176" spans="8:29" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H176" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="I176" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="I176" s="33" t="s">
-        <v>119</v>
-      </c>
       <c r="J176" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K176" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="L176" s="33" t="s">
         <v>84</v>
-      </c>
-      <c r="L176" s="33" t="s">
-        <v>85</v>
       </c>
       <c r="M176" s="33">
         <v>23131</v>
@@ -6560,21 +6566,21 @@
         <v>0.29570218535110998</v>
       </c>
     </row>
-    <row r="177" spans="8:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="8:20" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H177" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="I177" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="I177" s="33" t="s">
-        <v>119</v>
-      </c>
       <c r="J177" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K177" s="33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L177" s="33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M177" s="33">
         <v>23132</v>
@@ -6601,21 +6607,21 @@
         <v>0.241441912576494</v>
       </c>
     </row>
-    <row r="178" spans="8:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="8:20" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H178" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="I178" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I178" s="20" t="s">
-        <v>119</v>
-      </c>
       <c r="J178" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K178" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L178" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M178" s="20">
         <v>23231</v>
@@ -6642,21 +6648,21 @@
         <v>0.20628490054454399</v>
       </c>
     </row>
-    <row r="179" spans="8:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:20" ht="13.9" x14ac:dyDescent="0.25">
       <c r="H179" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="I179" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I179" s="20" t="s">
-        <v>119</v>
-      </c>
       <c r="J179" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K179" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L179" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M179" s="20">
         <v>23232</v>
@@ -6683,34 +6689,23 @@
         <v>0.164597803992556</v>
       </c>
     </row>
-    <row r="181" spans="8:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="8:20" ht="13.9" x14ac:dyDescent="0.25">
       <c r="S181" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="V123:Z123"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="W119:X119"/>
-    <mergeCell ref="Y119:Z119"/>
-    <mergeCell ref="W120:X120"/>
-    <mergeCell ref="Y120:Z120"/>
-    <mergeCell ref="W121:X121"/>
-    <mergeCell ref="Y121:Z121"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="V116:Z116"/>
-    <mergeCell ref="W117:X117"/>
-    <mergeCell ref="Y117:Z117"/>
-    <mergeCell ref="W122:X122"/>
-    <mergeCell ref="Y122:Z122"/>
-    <mergeCell ref="W118:X118"/>
-    <mergeCell ref="Y118:Z118"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="V106:Z106"/>
-    <mergeCell ref="G28:G38"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="D106:F106"/>
     <mergeCell ref="H106:S106"/>
@@ -6722,16 +6717,27 @@
     <mergeCell ref="H21:K21"/>
     <mergeCell ref="H22:K22"/>
     <mergeCell ref="H23:K23"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="V106:Z106"/>
+    <mergeCell ref="G28:G38"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="V116:Z116"/>
+    <mergeCell ref="W117:X117"/>
+    <mergeCell ref="Y117:Z117"/>
+    <mergeCell ref="W122:X122"/>
+    <mergeCell ref="Y122:Z122"/>
+    <mergeCell ref="W118:X118"/>
+    <mergeCell ref="Y118:Z118"/>
+    <mergeCell ref="V123:Z123"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="W119:X119"/>
+    <mergeCell ref="Y119:Z119"/>
+    <mergeCell ref="W120:X120"/>
+    <mergeCell ref="Y120:Z120"/>
+    <mergeCell ref="W121:X121"/>
+    <mergeCell ref="Y121:Z121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6740,137 +6746,137 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4608C4-66B7-4E2E-8469-0BE055B9F575}">
   <dimension ref="A1:U23"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" customWidth="1"/>
-    <col min="17" max="17" width="19.88671875" customWidth="1"/>
-    <col min="20" max="20" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" customWidth="1"/>
+    <col min="17" max="17" width="19.85546875" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L1" t="s">
         <v>159</v>
       </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="F2" t="s">
         <v>161</v>
       </c>
-      <c r="F2" t="s">
+      <c r="L2" t="s">
         <v>162</v>
       </c>
-      <c r="L2" t="s">
+    </row>
+    <row r="3" spans="1:21" ht="28.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="56" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" ht="28.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="44" t="s">
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+    </row>
+    <row r="4" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="44" t="s">
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="44" t="s">
+      <c r="G4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="44" t="s">
+      <c r="N4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-    </row>
-    <row r="4" spans="1:21" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="S4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="U4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="B5" s="7">
         <v>0.27</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="7">
         <v>0.86</v>
@@ -6879,25 +6885,25 @@
         <v>0.06</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J5" s="8">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M5" s="7">
         <v>1.24</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R5" s="7">
         <v>1.47</v>
@@ -6906,21 +6912,21 @@
         <v>0.03</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="F6" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="F6" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="G6" s="7">
         <v>1.55</v>
@@ -6929,19 +6935,19 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="Q6" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="Q6" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="R6" s="7">
         <v>1.05</v>
@@ -6950,23 +6956,23 @@
         <v>0.01</v>
       </c>
       <c r="T6" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="51">
+        <v>3.29</v>
+      </c>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="F7" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="U6" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="41">
-        <v>3.29</v>
-      </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="F7" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="G7" s="7">
         <v>0.14000000000000001</v>
@@ -6975,21 +6981,21 @@
         <v>0.01</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="41">
+        <v>20</v>
+      </c>
+      <c r="M7" s="51">
         <v>0.59</v>
       </c>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
       <c r="Q7" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R7" s="7">
         <v>0.76</v>
@@ -6998,23 +7004,23 @@
         <v>0.01</v>
       </c>
       <c r="T7" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="51">
+        <v>0.9</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="F8" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="41">
-        <v>0.9</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="F8" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="G8" s="7">
         <v>0.21</v>
@@ -7023,21 +7029,21 @@
         <v>0.01</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="41">
+        <v>23</v>
+      </c>
+      <c r="M8" s="51">
         <v>0.01</v>
       </c>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
       <c r="Q8" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R8" s="7">
         <v>0.79</v>
@@ -7046,23 +7052,23 @@
         <v>0.01</v>
       </c>
       <c r="T8" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="51">
+        <v>0.21</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="F9" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="41">
-        <v>0.21</v>
-      </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="F9" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="G9" s="7">
         <v>0.8</v>
@@ -7071,21 +7077,21 @@
         <v>0.06</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J9" s="8">
         <v>2E-3</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="41">
+        <v>26</v>
+      </c>
+      <c r="M9" s="51">
         <v>0.02</v>
       </c>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
       <c r="Q9" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R9" s="7">
         <v>0.97</v>
@@ -7094,15 +7100,15 @@
         <v>0.02</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="U9" s="7">
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="41.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="41.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="49">
         <v>108</v>
@@ -7110,7 +7116,7 @@
       <c r="C10" s="49"/>
       <c r="D10" s="49"/>
       <c r="F10" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G10" s="7">
         <v>0.76</v>
@@ -7119,13 +7125,13 @@
         <v>0.05</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M10" s="49">
         <v>108</v>
@@ -7133,7 +7139,7 @@
       <c r="N10" s="49"/>
       <c r="O10" s="49"/>
       <c r="Q10" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R10" s="7">
         <v>0.96</v>
@@ -7142,15 +7148,15 @@
         <v>0.02</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U10" s="8">
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="50">
         <v>29653</v>
@@ -7158,7 +7164,7 @@
       <c r="C11" s="50"/>
       <c r="D11" s="50"/>
       <c r="F11" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G11" s="7">
         <v>0.62</v>
@@ -7167,13 +7173,13 @@
         <v>0.05</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M11" s="50">
         <v>29653</v>
@@ -7181,7 +7187,7 @@
       <c r="N11" s="50"/>
       <c r="O11" s="50"/>
       <c r="Q11" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R11" s="7">
         <v>0.94</v>
@@ -7190,23 +7196,23 @@
         <v>0.02</v>
       </c>
       <c r="T11" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="51" t="s">
         <v>186</v>
       </c>
-      <c r="U11" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="41" t="s">
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="F12" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="F12" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="G12" s="7">
         <v>0.57999999999999996</v>
@@ -7215,21 +7221,21 @@
         <v>0.05</v>
       </c>
       <c r="I12" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
       <c r="Q12" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R12" s="7">
         <v>0.93</v>
@@ -7238,21 +7244,21 @@
         <v>0.02</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U12" s="8">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="35">
         <v>21.405159999999999</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G13" s="7">
         <v>0.46</v>
@@ -7261,19 +7267,19 @@
         <v>0.04</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M13" s="35">
         <v>2.307426</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R13" s="7">
         <v>0.91</v>
@@ -7282,15 +7288,15 @@
         <v>0.02</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U13" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F14" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" s="7">
         <v>1.28</v>
@@ -7299,13 +7305,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R14" s="7">
         <v>1.03</v>
@@ -7314,15 +7320,15 @@
         <v>0.02</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U14" s="8">
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G15" s="7">
         <v>1.28</v>
@@ -7331,13 +7337,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R15" s="7">
         <v>1.03</v>
@@ -7346,54 +7352,54 @@
         <v>0.01</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="U15" s="8">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F16" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
+    <row r="16" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
       <c r="Q16" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
       <c r="T16" s="9"/>
       <c r="U16" s="9"/>
     </row>
-    <row r="17" spans="6:21" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="6:21" ht="18" x14ac:dyDescent="0.25">
       <c r="F17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="41">
+        <v>20</v>
+      </c>
+      <c r="G17" s="51">
         <v>3.29</v>
       </c>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
       <c r="Q17" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="6:21" ht="16.2" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="6:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="F18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="41">
+        <v>23</v>
+      </c>
+      <c r="G18" s="51">
         <v>0.02</v>
       </c>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
       <c r="Q18" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R18" s="6">
         <v>0</v>
@@ -7402,18 +7408,18 @@
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
     </row>
-    <row r="19" spans="6:21" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="41">
+        <v>26</v>
+      </c>
+      <c r="G19" s="51">
         <v>0.01</v>
       </c>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
       <c r="Q19" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R19" s="10">
         <v>108</v>
@@ -7422,9 +7428,9 @@
       <c r="T19" s="10"/>
       <c r="U19" s="10"/>
     </row>
-    <row r="20" spans="6:21" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F20" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20" s="49">
         <v>108</v>
@@ -7433,7 +7439,7 @@
       <c r="I20" s="49"/>
       <c r="J20" s="49"/>
       <c r="Q20" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R20" s="11">
         <v>29653</v>
@@ -7442,9 +7448,9 @@
       <c r="T20" s="11"/>
       <c r="U20" s="11"/>
     </row>
-    <row r="21" spans="6:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="6:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F21" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="50">
         <v>29653</v>
@@ -7453,26 +7459,26 @@
       <c r="I21" s="50"/>
       <c r="J21" s="50"/>
       <c r="Q21" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R21" s="36">
         <v>3.6478820000000001E-8</v>
       </c>
     </row>
-    <row r="22" spans="6:21" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="6:21" ht="36" x14ac:dyDescent="0.25">
       <c r="F22" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="41" t="s">
-        <v>199</v>
-      </c>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-    </row>
-    <row r="23" spans="6:21" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="G22" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+    </row>
+    <row r="23" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F23" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G23" s="35">
         <v>0.6992389</v>
@@ -7480,24 +7486,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="M12:O12"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="F16:J16"/>
     <mergeCell ref="G17:J17"/>
@@ -7505,6 +7493,24 @@
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="G21:J21"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="L6:O6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7513,251 +7519,251 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41054B0F-2B87-45B8-8543-78EB4D93A102}">
   <dimension ref="A1:AR25"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" customWidth="1"/>
-    <col min="9" max="9" width="10.88671875" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" customWidth="1"/>
-    <col min="17" max="17" width="18.44140625" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" customWidth="1"/>
-    <col min="35" max="35" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.44140625" customWidth="1"/>
-    <col min="40" max="40" width="19.88671875" customWidth="1"/>
-    <col min="41" max="41" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
+    <col min="35" max="35" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.42578125" customWidth="1"/>
+    <col min="40" max="40" width="19.85546875" customWidth="1"/>
+    <col min="41" max="41" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="X1" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="X1" s="37" t="s">
+    </row>
+    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="L2" s="37" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="F2" s="37" t="s">
+      <c r="Q2" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="X2" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="L2" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q2" s="37" t="s">
+      <c r="AC2" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="AI2" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="X2" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="AC2" s="37" t="s">
+      <c r="AN2" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="AI2" s="37" t="s">
+    </row>
+    <row r="3" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>204</v>
+      </c>
+      <c r="L3" t="s">
+        <v>205</v>
+      </c>
+      <c r="X3" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" ht="28.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="L4" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+      <c r="X4" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="AN2" s="37" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>205</v>
-      </c>
-      <c r="L3" t="s">
-        <v>206</v>
-      </c>
-      <c r="X3" t="s">
-        <v>205</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44" ht="28.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="44" t="s">
+      <c r="Y4" s="56"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="56"/>
+      <c r="AC4" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="56"/>
+      <c r="AF4" s="56"/>
+      <c r="AG4" s="56"/>
+      <c r="AI4" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ4" s="56"/>
+      <c r="AK4" s="56"/>
+      <c r="AL4" s="56"/>
+      <c r="AN4" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="AO4" s="56"/>
+      <c r="AP4" s="56"/>
+      <c r="AQ4" s="56"/>
+      <c r="AR4" s="56"/>
+    </row>
+    <row r="5" spans="1:44" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="44" t="s">
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="L4" s="44" t="s">
+      <c r="G5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="44" t="s">
+      <c r="M5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="X4" s="44" t="s">
+      <c r="R5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y5" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="44"/>
-      <c r="AC4" s="44" t="s">
+      <c r="Z5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD5" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="44"/>
-      <c r="AG4" s="44"/>
-      <c r="AI4" s="44" t="s">
+      <c r="AE5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ5" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="44"/>
-      <c r="AN4" s="44" t="s">
+      <c r="AK5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AN5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO5" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="AO4" s="44"/>
-      <c r="AP4" s="44"/>
-      <c r="AQ4" s="44"/>
-      <c r="AR4" s="44"/>
-    </row>
-    <row r="5" spans="1:44" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="AP5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="AR5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5" t="s">
+    </row>
+    <row r="6" spans="1:44" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD5" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AG5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ5" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="AK5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="AN5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO5" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="AP5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AQ5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AR5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="B6" s="7">
         <v>0.14000000000000001</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" s="7">
         <v>0.09</v>
@@ -7766,25 +7772,25 @@
         <v>0.01</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M6" s="7">
         <v>0.15</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R6" s="7">
         <v>0.11</v>
@@ -7793,25 +7799,25 @@
         <v>0.01</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y6" s="7">
         <v>0.13</v>
       </c>
       <c r="Z6" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD6" s="7">
         <v>0.09</v>
@@ -7820,25 +7826,25 @@
         <v>0.01</v>
       </c>
       <c r="AF6" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ6" s="7">
         <v>0.13</v>
       </c>
       <c r="AK6" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AL6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" s="7">
         <v>0.1</v>
@@ -7847,21 +7853,21 @@
         <v>0.01</v>
       </c>
       <c r="AQ6" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR6" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="F7" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="F7" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="G7" s="7">
         <v>1.93</v>
@@ -7870,19 +7876,19 @@
         <v>0.1</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="Q7" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="Q7" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="R7" s="7">
         <v>1.95</v>
@@ -7891,19 +7897,19 @@
         <v>0.09</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="X7" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
+      <c r="AA7" s="47"/>
+      <c r="AC7" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="Y7" s="45"/>
-      <c r="Z7" s="45"/>
-      <c r="AA7" s="45"/>
-      <c r="AC7" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="AD7" s="7">
         <v>1.76</v>
@@ -7912,19 +7918,19 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AF7" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI7" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI7" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ7" s="47"/>
+      <c r="AK7" s="47"/>
+      <c r="AL7" s="47"/>
+      <c r="AN7" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="AJ7" s="45"/>
-      <c r="AK7" s="45"/>
-      <c r="AL7" s="45"/>
-      <c r="AN7" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="AO7" s="7">
         <v>1.76</v>
@@ -7933,23 +7939,23 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AQ7" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AR7" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="51">
+        <v>3.29</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="F8" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" s="41">
-        <v>3.29</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="F8" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="G8" s="7">
         <v>1.04</v>
@@ -7958,21 +7964,21 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J8" s="7">
         <v>0.54100000000000004</v>
       </c>
       <c r="L8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="51">
+        <v>3.29</v>
+      </c>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
+      <c r="Q8" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="M8" s="41">
-        <v>3.29</v>
-      </c>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="Q8" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="R8" s="7">
         <v>1.04</v>
@@ -7981,21 +7987,21 @@
         <v>0.06</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="U8" s="7">
         <v>0.49399999999999999</v>
       </c>
       <c r="X8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y8" s="51">
+        <v>2.12</v>
+      </c>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="51"/>
+      <c r="AC8" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="Y8" s="41">
-        <v>2.12</v>
-      </c>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="41"/>
-      <c r="AC8" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="AD8" s="7">
         <v>1.04</v>
@@ -8004,21 +8010,21 @@
         <v>0.06</v>
       </c>
       <c r="AF8" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG8" s="7">
         <v>0.45900000000000002</v>
       </c>
       <c r="AI8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ8" s="51">
+        <v>2.11</v>
+      </c>
+      <c r="AK8" s="51"/>
+      <c r="AL8" s="51"/>
+      <c r="AN8" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="AJ8" s="41">
-        <v>2.11</v>
-      </c>
-      <c r="AK8" s="41"/>
-      <c r="AL8" s="41"/>
-      <c r="AN8" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="AO8" s="7">
         <v>1.04</v>
@@ -8027,23 +8033,23 @@
         <v>0.05</v>
       </c>
       <c r="AQ8" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AR8" s="7">
         <v>0.42</v>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="51">
+        <v>0.24</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="F9" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="41">
-        <v>0.24</v>
-      </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="F9" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="G9" s="7">
         <v>1.68</v>
@@ -8052,21 +8058,21 @@
         <v>0.1</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="51">
+        <v>0.26</v>
+      </c>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
+      <c r="Q9" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="M9" s="41">
-        <v>0.26</v>
-      </c>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="Q9" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="R9" s="7">
         <v>1.67</v>
@@ -8075,21 +8081,21 @@
         <v>0.09</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="U9" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y9" s="51">
+        <v>0.17</v>
+      </c>
+      <c r="Z9" s="51"/>
+      <c r="AA9" s="51"/>
+      <c r="AC9" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="Y9" s="41">
-        <v>0.17</v>
-      </c>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="41"/>
-      <c r="AC9" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="AD9" s="7">
         <v>1.55</v>
@@ -8098,21 +8104,21 @@
         <v>0.08</v>
       </c>
       <c r="AF9" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG9" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ9" s="51">
+        <v>0.18</v>
+      </c>
+      <c r="AK9" s="51"/>
+      <c r="AL9" s="51"/>
+      <c r="AN9" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="AJ9" s="41">
-        <v>0.18</v>
-      </c>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="41"/>
-      <c r="AN9" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="AO9" s="7">
         <v>1.54</v>
@@ -8121,23 +8127,23 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AQ9" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="AR9" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="51">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="F10" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="AR9" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="41">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="F10" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="G10" s="7">
         <v>0.78</v>
@@ -8146,21 +8152,21 @@
         <v>0.04</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="41">
+        <v>26</v>
+      </c>
+      <c r="M10" s="51">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
       <c r="Q10" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R10" s="7">
         <v>0.79</v>
@@ -8169,21 +8175,21 @@
         <v>0.06</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="U10" s="8">
         <v>1E-3</v>
       </c>
       <c r="X10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y10" s="41">
+        <v>26</v>
+      </c>
+      <c r="Y10" s="51">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="41"/>
+      <c r="Z10" s="51"/>
+      <c r="AA10" s="51"/>
       <c r="AC10" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AD10" s="7">
         <v>0.81</v>
@@ -8192,21 +8198,21 @@
         <v>0.04</v>
       </c>
       <c r="AF10" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ10" s="41">
+        <v>26</v>
+      </c>
+      <c r="AJ10" s="51">
         <v>0.08</v>
       </c>
-      <c r="AK10" s="41"/>
-      <c r="AL10" s="41"/>
+      <c r="AK10" s="51"/>
+      <c r="AL10" s="51"/>
       <c r="AN10" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AO10" s="7">
         <v>0.82</v>
@@ -8215,15 +8221,15 @@
         <v>0.05</v>
       </c>
       <c r="AQ10" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AR10" s="8">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:44" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:44" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="49">
         <v>54</v>
@@ -8231,7 +8237,7 @@
       <c r="C11" s="49"/>
       <c r="D11" s="49"/>
       <c r="F11" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G11" s="7">
         <v>0.51</v>
@@ -8240,13 +8246,13 @@
         <v>0.04</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M11" s="49">
         <v>108</v>
@@ -8254,7 +8260,7 @@
       <c r="N11" s="49"/>
       <c r="O11" s="49"/>
       <c r="Q11" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R11" s="7">
         <v>0.75</v>
@@ -8263,13 +8269,13 @@
         <v>0.06</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U11" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y11" s="49">
         <v>54</v>
@@ -8277,7 +8283,7 @@
       <c r="Z11" s="49"/>
       <c r="AA11" s="49"/>
       <c r="AC11" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AD11" s="7">
         <v>0.56000000000000005</v>
@@ -8286,13 +8292,13 @@
         <v>0.03</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG11" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ11" s="49">
         <v>108</v>
@@ -8300,7 +8306,7 @@
       <c r="AK11" s="49"/>
       <c r="AL11" s="49"/>
       <c r="AN11" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AO11" s="7">
         <v>0.79</v>
@@ -8309,15 +8315,15 @@
         <v>0.05</v>
       </c>
       <c r="AQ11" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AR11" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:44" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="50">
         <v>19500</v>
@@ -8325,7 +8331,7 @@
       <c r="C12" s="50"/>
       <c r="D12" s="50"/>
       <c r="F12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="7">
         <v>1.34</v>
@@ -8334,13 +8340,13 @@
         <v>0.09</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M12" s="50">
         <v>19500</v>
@@ -8348,7 +8354,7 @@
       <c r="N12" s="50"/>
       <c r="O12" s="50"/>
       <c r="Q12" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R12" s="7">
         <v>0.59</v>
@@ -8357,13 +8363,13 @@
         <v>0.05</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U12" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Y12" s="50">
         <v>19500</v>
@@ -8371,7 +8377,7 @@
       <c r="Z12" s="50"/>
       <c r="AA12" s="50"/>
       <c r="AC12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD12" s="7">
         <v>1.28</v>
@@ -8380,13 +8386,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG12" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI12" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AJ12" s="50">
         <v>19500</v>
@@ -8394,7 +8400,7 @@
       <c r="AK12" s="50"/>
       <c r="AL12" s="50"/>
       <c r="AN12" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AO12" s="7">
         <v>0.65</v>
@@ -8403,23 +8409,23 @@
         <v>0.04</v>
       </c>
       <c r="AQ12" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="AR12" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="51" t="s">
         <v>236</v>
       </c>
-      <c r="AR12" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:44" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>237</v>
-      </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
       <c r="F13" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G13" s="7">
         <v>1.33</v>
@@ -8428,21 +8434,21 @@
         <v>0.09</v>
       </c>
       <c r="I13" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="41" t="s">
-        <v>239</v>
-      </c>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="51"/>
       <c r="Q13" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R13" s="7">
         <v>0.56000000000000005</v>
@@ -8451,21 +8457,21 @@
         <v>0.05</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="U13" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y13" s="41" t="s">
-        <v>239</v>
-      </c>
-      <c r="Z13" s="41"/>
-      <c r="AA13" s="41"/>
+        <v>34</v>
+      </c>
+      <c r="Y13" s="51" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z13" s="51"/>
+      <c r="AA13" s="51"/>
       <c r="AC13" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD13" s="7">
         <v>1.28</v>
@@ -8474,21 +8480,21 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AF13" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG13" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ13" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="AJ13" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK13" s="41"/>
-      <c r="AL13" s="41"/>
+      <c r="AK13" s="51"/>
+      <c r="AL13" s="51"/>
       <c r="AN13" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AO13" s="7">
         <v>0.61</v>
@@ -8497,36 +8503,36 @@
         <v>0.05</v>
       </c>
       <c r="AQ13" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AR13" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="13">
         <v>6.678481E-2</v>
       </c>
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
-      <c r="F14" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
+      <c r="F14" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
       <c r="L14" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M14" s="13">
         <v>7.2955740000000005E-2</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R14" s="7">
         <v>0.34</v>
@@ -8535,34 +8541,34 @@
         <v>0.03</v>
       </c>
       <c r="T14" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="X14" s="12" t="s">
         <v>243</v>
-      </c>
-      <c r="U14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="X14" s="12" t="s">
-        <v>244</v>
       </c>
       <c r="Y14" s="14">
         <v>7.0640750000000002E-2</v>
       </c>
       <c r="Z14" s="14"/>
       <c r="AA14" s="14"/>
-      <c r="AC14" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD14" s="45"/>
-      <c r="AE14" s="45"/>
-      <c r="AF14" s="45"/>
-      <c r="AG14" s="45"/>
+      <c r="AC14" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD14" s="47"/>
+      <c r="AE14" s="47"/>
+      <c r="AF14" s="47"/>
+      <c r="AG14" s="47"/>
       <c r="AI14" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AJ14" s="39">
         <v>7.5683070000000005E-2</v>
       </c>
       <c r="AN14" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AO14" s="7">
         <v>0.4</v>
@@ -8571,27 +8577,27 @@
         <v>0.04</v>
       </c>
       <c r="AQ14" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR14" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:44" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="AR14" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:44" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="42" t="s">
-        <v>246</v>
-      </c>
       <c r="F15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="41">
+        <v>20</v>
+      </c>
+      <c r="G15" s="51">
         <v>3.29</v>
       </c>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
       <c r="Q15" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R15" s="7">
         <v>1.34</v>
@@ -8600,22 +8606,22 @@
         <v>0.09</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="U15" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD15" s="41">
+        <v>20</v>
+      </c>
+      <c r="AD15" s="51">
         <v>2.12</v>
       </c>
-      <c r="AE15" s="41"/>
-      <c r="AF15" s="41"/>
-      <c r="AG15" s="41"/>
+      <c r="AE15" s="51"/>
+      <c r="AF15" s="51"/>
+      <c r="AG15" s="51"/>
       <c r="AN15" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AO15" s="7">
         <v>1.28</v>
@@ -8624,25 +8630,25 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AQ15" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AR15" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="42"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="43"/>
       <c r="F16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="41">
+        <v>23</v>
+      </c>
+      <c r="G16" s="51">
         <v>0.01</v>
       </c>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
       <c r="Q16" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R16" s="7">
         <v>1.36</v>
@@ -8651,22 +8657,22 @@
         <v>0.08</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="U16" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD16" s="41">
+        <v>23</v>
+      </c>
+      <c r="AD16" s="51">
         <v>0</v>
       </c>
-      <c r="AE16" s="41"/>
-      <c r="AF16" s="41"/>
-      <c r="AG16" s="41"/>
+      <c r="AE16" s="51"/>
+      <c r="AF16" s="51"/>
+      <c r="AG16" s="51"/>
       <c r="AN16" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AO16" s="7">
         <v>1.3</v>
@@ -8675,51 +8681,51 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AQ16" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AR16" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="43"/>
       <c r="F17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="41">
+        <v>26</v>
+      </c>
+      <c r="G17" s="51">
         <v>0</v>
       </c>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="Q17" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="45"/>
-      <c r="U17" s="45"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="Q17" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="47"/>
       <c r="AC17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD17" s="41">
+        <v>26</v>
+      </c>
+      <c r="AD17" s="51">
         <v>0</v>
       </c>
-      <c r="AE17" s="41"/>
-      <c r="AF17" s="41"/>
-      <c r="AG17" s="41"/>
-      <c r="AN17" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="AO17" s="45"/>
-      <c r="AP17" s="45"/>
-      <c r="AQ17" s="45"/>
-      <c r="AR17" s="45"/>
-    </row>
-    <row r="18" spans="1:44" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
+      <c r="AE17" s="51"/>
+      <c r="AF17" s="51"/>
+      <c r="AG17" s="51"/>
+      <c r="AN17" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO17" s="47"/>
+      <c r="AP17" s="47"/>
+      <c r="AQ17" s="47"/>
+      <c r="AR17" s="47"/>
+    </row>
+    <row r="18" spans="1:44" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="43"/>
       <c r="F18" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" s="49">
         <v>54</v>
@@ -8728,16 +8734,16 @@
       <c r="I18" s="49"/>
       <c r="J18" s="49"/>
       <c r="Q18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="R18" s="41">
+        <v>20</v>
+      </c>
+      <c r="R18" s="51">
         <v>3.29</v>
       </c>
-      <c r="S18" s="41"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
+      <c r="S18" s="51"/>
+      <c r="T18" s="51"/>
+      <c r="U18" s="51"/>
       <c r="AC18" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD18" s="49">
         <v>54</v>
@@ -8746,18 +8752,18 @@
       <c r="AF18" s="49"/>
       <c r="AG18" s="49"/>
       <c r="AN18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AO18" s="41">
+        <v>20</v>
+      </c>
+      <c r="AO18" s="51">
         <v>2.11</v>
       </c>
-      <c r="AP18" s="41"/>
-      <c r="AQ18" s="41"/>
-      <c r="AR18" s="41"/>
-    </row>
-    <row r="19" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="AP18" s="51"/>
+      <c r="AQ18" s="51"/>
+      <c r="AR18" s="51"/>
+    </row>
+    <row r="19" spans="1:44" ht="30" x14ac:dyDescent="0.25">
       <c r="F19" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" s="50">
         <v>19500</v>
@@ -8766,16 +8772,16 @@
       <c r="I19" s="50"/>
       <c r="J19" s="50"/>
       <c r="Q19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="R19" s="41">
+        <v>23</v>
+      </c>
+      <c r="R19" s="51">
         <v>0.01</v>
       </c>
-      <c r="S19" s="41"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
+      <c r="S19" s="51"/>
+      <c r="T19" s="51"/>
+      <c r="U19" s="51"/>
       <c r="AC19" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AD19" s="50">
         <v>19500</v>
@@ -8784,62 +8790,62 @@
       <c r="AF19" s="50"/>
       <c r="AG19" s="50"/>
       <c r="AN19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="AO19" s="41">
+        <v>23</v>
+      </c>
+      <c r="AO19" s="51">
         <v>0</v>
       </c>
-      <c r="AP19" s="41"/>
-      <c r="AQ19" s="41"/>
-      <c r="AR19" s="41"/>
-    </row>
-    <row r="20" spans="1:44" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="AP19" s="51"/>
+      <c r="AQ19" s="51"/>
+      <c r="AR19" s="51"/>
+    </row>
+    <row r="20" spans="1:44" ht="66" x14ac:dyDescent="0.25">
       <c r="F20" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="51" t="s">
+        <v>248</v>
+      </c>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="Q20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="R20" s="51">
+        <v>0</v>
+      </c>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
+      <c r="AC20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD20" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="Q20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="R20" s="41">
+      <c r="AE20" s="51"/>
+      <c r="AF20" s="51"/>
+      <c r="AG20" s="51"/>
+      <c r="AN20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO20" s="51">
         <v>0</v>
       </c>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="AC20" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD20" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="AE20" s="41"/>
-      <c r="AF20" s="41"/>
-      <c r="AG20" s="41"/>
-      <c r="AN20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="AO20" s="41">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="41"/>
-      <c r="AQ20" s="41"/>
-      <c r="AR20" s="41"/>
-    </row>
-    <row r="21" spans="1:44" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AP20" s="51"/>
+      <c r="AQ20" s="51"/>
+      <c r="AR20" s="51"/>
+    </row>
+    <row r="21" spans="1:44" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F21" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" s="13">
         <v>2.4345920000000002E-3</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R21" s="49">
         <v>108</v>
@@ -8848,13 +8854,13 @@
       <c r="T21" s="49"/>
       <c r="U21" s="49"/>
       <c r="AC21" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AD21" s="14">
         <v>7.2764780000000005E-4</v>
       </c>
       <c r="AN21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO21" s="49">
         <v>108</v>
@@ -8863,15 +8869,15 @@
       <c r="AQ21" s="49"/>
       <c r="AR21" s="49"/>
     </row>
-    <row r="22" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R22" s="50">
         <v>19500</v>
@@ -8880,13 +8886,13 @@
       <c r="T22" s="50"/>
       <c r="U22" s="50"/>
       <c r="AC22" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AD22" s="14">
         <v>98.895399999999995</v>
       </c>
       <c r="AN22" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AO22" s="50">
         <v>19500</v>
@@ -8895,49 +8901,49 @@
       <c r="AQ22" s="50"/>
       <c r="AR22" s="50"/>
     </row>
-    <row r="23" spans="1:44" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:44" ht="36" x14ac:dyDescent="0.25">
       <c r="Q23" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R23" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="R23" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="S23" s="51"/>
+      <c r="T23" s="51"/>
+      <c r="U23" s="51"/>
+      <c r="AN23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO23" s="51" t="s">
         <v>253</v>
       </c>
-      <c r="S23" s="41"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="41"/>
-      <c r="AN23" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO23" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="AP23" s="41"/>
-      <c r="AQ23" s="41"/>
-      <c r="AR23" s="41"/>
-    </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AP23" s="51"/>
+      <c r="AQ23" s="51"/>
+      <c r="AR23" s="51"/>
+    </row>
+    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
       <c r="Q24" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R24" s="39">
         <v>2.1294360000000002E-3</v>
       </c>
       <c r="AN24" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AO24" s="40">
         <v>5.6517609999999998E-9</v>
       </c>
     </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
       <c r="Q25" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R25" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AN25" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AO25" s="40">
         <v>99.999989999999997</v>
@@ -8945,6 +8951,59 @@
     </row>
   </sheetData>
   <mergeCells count="65">
+    <mergeCell ref="R22:U22"/>
+    <mergeCell ref="AO22:AR22"/>
+    <mergeCell ref="R23:U23"/>
+    <mergeCell ref="AO23:AR23"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="R20:U20"/>
+    <mergeCell ref="AD20:AG20"/>
+    <mergeCell ref="AO20:AR20"/>
+    <mergeCell ref="R21:U21"/>
+    <mergeCell ref="AO21:AR21"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="R19:U19"/>
+    <mergeCell ref="AD19:AG19"/>
+    <mergeCell ref="AO19:AR19"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="AC14:AG14"/>
+    <mergeCell ref="AN17:AR17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="R18:U18"/>
+    <mergeCell ref="AD18:AG18"/>
+    <mergeCell ref="AO18:AR18"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="AD15:AG15"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="AD16:AG16"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="Q17:U17"/>
+    <mergeCell ref="AD17:AG17"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AJ12:AL12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AI4:AL4"/>
     <mergeCell ref="AN4:AR4"/>
     <mergeCell ref="A7:D7"/>
@@ -8957,59 +9016,6 @@
     <mergeCell ref="R4:U4"/>
     <mergeCell ref="X4:AA4"/>
     <mergeCell ref="AC4:AG4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="Y8:AA8"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="AJ12:AL12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="Y13:AA13"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="AD15:AG15"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="AD16:AG16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="Q17:U17"/>
-    <mergeCell ref="AD17:AG17"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="R19:U19"/>
-    <mergeCell ref="AD19:AG19"/>
-    <mergeCell ref="AO19:AR19"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="AC14:AG14"/>
-    <mergeCell ref="AN17:AR17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="R18:U18"/>
-    <mergeCell ref="AD18:AG18"/>
-    <mergeCell ref="AO18:AR18"/>
-    <mergeCell ref="R22:U22"/>
-    <mergeCell ref="AO22:AR22"/>
-    <mergeCell ref="R23:U23"/>
-    <mergeCell ref="AO23:AR23"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="R20:U20"/>
-    <mergeCell ref="AD20:AG20"/>
-    <mergeCell ref="AO20:AR20"/>
-    <mergeCell ref="R21:U21"/>
-    <mergeCell ref="AO21:AR21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tables/MAIHDA.xlsx
+++ b/Tables/MAIHDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38b97e870d12de33/Documents/UAH/PhD Documents/INEdatos/Analysis/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="900" documentId="8_{980E5B5A-75EE-4430-85D2-0D88ED2233B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83330719-84BC-4EE1-A966-066E5E2B0349}"/>
+  <xr:revisionPtr revIDLastSave="942" documentId="8_{980E5B5A-75EE-4430-85D2-0D88ED2233B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7073CC24-FECD-460A-87F2-28E3397C72EC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{F53BC189-169C-4D5A-95F0-57F331A1907F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F53BC189-169C-4D5A-95F0-57F331A1907F}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIHDA-0412" sheetId="1" r:id="rId1"/>
@@ -1003,11 +1003,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="0.0000000000000"/>
     <numFmt numFmtId="167" formatCode="0.000000000"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1206,7 +1207,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1330,6 +1331,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1372,17 +1381,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1757,25 +1757,25 @@
     </row>
     <row r="9" spans="1:18" ht="28.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
       <c r="K9"/>
-      <c r="N9" s="53" t="s">
+      <c r="N9" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="O9" s="53"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="53"/>
-      <c r="R9" s="53"/>
+      <c r="O9" s="59"/>
+      <c r="P9" s="59"/>
+      <c r="Q9" s="59"/>
+      <c r="R9" s="59"/>
     </row>
     <row r="10" spans="1:18" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -1860,12 +1860,12 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
       <c r="G12" s="6" t="s">
         <v>75</v>
       </c>
@@ -1894,11 +1894,11 @@
       <c r="A13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="53">
         <v>3.29</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
       <c r="G13" s="6" t="s">
         <v>79</v>
       </c>
@@ -1927,11 +1927,11 @@
       <c r="A14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="53">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
       <c r="G14" s="6" t="s">
         <v>82</v>
       </c>
@@ -1960,11 +1960,11 @@
       <c r="A15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="53">
         <v>0.08</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
       <c r="G15" s="31" t="s">
         <v>252</v>
       </c>
@@ -1993,11 +1993,11 @@
       <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="50">
+      <c r="B16" s="56">
         <v>72</v>
       </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
       <c r="G16" s="31" t="s">
         <v>250</v>
       </c>
@@ -2026,11 +2026,11 @@
       <c r="A17" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="57">
         <v>19503</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
       <c r="G17" s="6" t="s">
         <v>249</v>
       </c>
@@ -2059,11 +2059,11 @@
       <c r="A18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
       <c r="G18" s="6" t="s">
         <v>253</v>
       </c>
@@ -2097,146 +2097,146 @@
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
-      <c r="G19" s="49" t="s">
+      <c r="G19" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="M19" s="49" t="s">
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="M19" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="55"/>
+      <c r="P19" s="55"/>
+      <c r="Q19" s="55"/>
     </row>
     <row r="20" spans="1:17" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="58" t="s">
         <v>29</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="58">
         <v>3.29</v>
       </c>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
       <c r="K20" s="46"/>
       <c r="M20" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N20" s="52">
+      <c r="N20" s="58">
         <v>3.29</v>
       </c>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52">
+      <c r="O20" s="58"/>
+      <c r="P20" s="58">
         <v>3.29</v>
       </c>
-      <c r="Q20" s="52"/>
+      <c r="Q20" s="58"/>
     </row>
     <row r="21" spans="1:17" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="58"/>
       <c r="G21" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="58">
         <v>0.03</v>
       </c>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
       <c r="K21" s="46"/>
       <c r="M21" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="N21" s="52" t="s">
+      <c r="N21" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52" t="s">
+      <c r="O21" s="58"/>
+      <c r="P21" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="Q21" s="52"/>
+      <c r="Q21" s="58"/>
     </row>
     <row r="22" spans="1:17" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
+      <c r="A22" s="58"/>
       <c r="G22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="52">
+      <c r="H22" s="58">
         <v>0.01</v>
       </c>
-      <c r="I22" s="52"/>
-      <c r="J22" s="52"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
       <c r="K22" s="46"/>
       <c r="M22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N22" s="52">
+      <c r="N22" s="58">
         <v>0.08</v>
       </c>
-      <c r="O22" s="52"/>
-      <c r="P22" s="52">
+      <c r="O22" s="58"/>
+      <c r="P22" s="58">
         <v>0.01</v>
       </c>
-      <c r="Q22" s="52"/>
+      <c r="Q22" s="58"/>
     </row>
     <row r="23" spans="1:17" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="52"/>
+      <c r="A23" s="58"/>
       <c r="G23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H23" s="55">
+      <c r="H23" s="61">
         <v>72</v>
       </c>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
       <c r="K23"/>
       <c r="M23" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="N23" s="55" t="s">
+      <c r="N23" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55" t="s">
+      <c r="O23" s="61"/>
+      <c r="P23" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="Q23" s="55"/>
+      <c r="Q23" s="61"/>
     </row>
     <row r="24" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G24" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="54">
+      <c r="H24" s="60">
         <v>19503</v>
       </c>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
       <c r="K24"/>
       <c r="M24" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="N24" s="54">
+      <c r="N24" s="60">
         <v>19500</v>
       </c>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54">
+      <c r="O24" s="60"/>
+      <c r="P24" s="60">
         <v>19500</v>
       </c>
-      <c r="Q24" s="54"/>
+      <c r="Q24" s="60"/>
     </row>
     <row r="25" spans="1:17" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H25" s="52" t="s">
+      <c r="H25" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="I25" s="52"/>
-      <c r="J25" s="52"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
       <c r="K25"/>
       <c r="M25" s="17" t="s">
         <v>112</v>
@@ -2245,7 +2245,7 @@
         <v>7.7580510000000005E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
@@ -2262,10 +2262,10 @@
       <c r="G27" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H27" s="56">
+      <c r="H27" s="62">
         <v>7.9442479999999992E-3</v>
       </c>
-      <c r="I27" s="56"/>
+      <c r="I27" s="62"/>
       <c r="M27" s="17" t="s">
         <v>117</v>
       </c>
@@ -2277,7 +2277,7 @@
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="52" t="s">
+      <c r="G28" s="58" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="1">
@@ -2285,36 +2285,36 @@
       </c>
       <c r="M28" s="17"/>
     </row>
-    <row r="29" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
         <v>33</v>
       </c>
       <c r="C29" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="G29" s="52"/>
-      <c r="M29" s="63" t="s">
+      <c r="G29" s="58"/>
+      <c r="M29" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="N29" s="64">
+      <c r="N29" s="1">
         <v>0.64979770000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>11111</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="52">
         <v>96</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="52">
         <v>4</v>
       </c>
-      <c r="G30" s="52"/>
-      <c r="M30" s="63" t="s">
+      <c r="G30" s="58"/>
+      <c r="M30" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="N30" s="64">
+      <c r="N30" s="1">
         <v>0.5</v>
       </c>
     </row>
@@ -2322,35 +2322,35 @@
       <c r="A31" s="1">
         <v>11112</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="52">
         <v>92.015209125475295</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="52">
         <v>7.9847908745247196</v>
       </c>
-      <c r="G31" s="52"/>
-      <c r="M31" s="63" t="s">
+      <c r="G31" s="58"/>
+      <c r="M31" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="N31" s="64">
+      <c r="N31" s="1">
         <v>0.64516010000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>11121</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="52">
         <v>97.350993377483405</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="52">
         <v>2.64900662251656</v>
       </c>
-      <c r="G32" s="52"/>
-      <c r="M32" s="63" t="s">
+      <c r="G32" s="58"/>
+      <c r="M32" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="N32" s="64">
+      <c r="N32" s="1">
         <v>0.63441369999999997</v>
       </c>
     </row>
@@ -2358,25 +2358,25 @@
       <c r="A33" s="1">
         <v>11122</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="52">
         <v>89.887640449438194</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="52">
         <v>10.1123595505618</v>
       </c>
-      <c r="G33" s="52"/>
+      <c r="G33" s="58"/>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>11131</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="52">
         <v>91.791044776119406</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="52">
         <v>8.2089552238806007</v>
       </c>
-      <c r="G34" s="52"/>
+      <c r="G34" s="58"/>
       <c r="M34" s="1" t="s">
         <v>128</v>
       </c>
@@ -2385,13 +2385,13 @@
       <c r="A35" s="1">
         <v>11132</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="52">
         <v>91.312384473197795</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="52">
         <v>8.6876155268022206</v>
       </c>
-      <c r="G35" s="52"/>
+      <c r="G35" s="58"/>
       <c r="M35" s="1" t="s">
         <v>129</v>
       </c>
@@ -2400,13 +2400,13 @@
       <c r="A36" s="1">
         <v>11211</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="52">
         <v>90.476190476190496</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="52">
         <v>9.5238095238095202</v>
       </c>
-      <c r="G36" s="52"/>
+      <c r="G36" s="58"/>
       <c r="M36" s="1" t="s">
         <v>130</v>
       </c>
@@ -2415,34 +2415,34 @@
       <c r="A37" s="1">
         <v>11212</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="52">
         <v>91.428571428571402</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="52">
         <v>8.5714285714285694</v>
       </c>
-      <c r="G37" s="52"/>
+      <c r="G37" s="58"/>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>11221</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="52">
         <v>91.891891891891902</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="52">
         <v>8.1081081081081106</v>
       </c>
-      <c r="G38" s="52"/>
+      <c r="G38" s="58"/>
     </row>
     <row r="39" spans="1:28" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>11222</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="52">
         <v>85.853658536585399</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="52">
         <v>14.146341463414601</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -2456,10 +2456,10 @@
       <c r="A40" s="1">
         <v>11231</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="52">
         <v>86.046511627906995</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="52">
         <v>13.953488372093</v>
       </c>
     </row>
@@ -2467,10 +2467,10 @@
       <c r="A41" s="1">
         <v>11232</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="52">
         <v>87.678571428571402</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="52">
         <v>12.3214285714286</v>
       </c>
     </row>
@@ -2478,10 +2478,10 @@
       <c r="A42" s="1">
         <v>12111</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="52">
         <v>95.061728395061706</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="52">
         <v>4.9382716049382704</v>
       </c>
     </row>
@@ -2489,10 +2489,10 @@
       <c r="A43" s="1">
         <v>12112</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="52">
         <v>94.240837696335106</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="52">
         <v>5.7591623036649198</v>
       </c>
     </row>
@@ -2500,10 +2500,10 @@
       <c r="A44" s="1">
         <v>12121</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="52">
         <v>91.970802919708007</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="52">
         <v>8.0291970802919703</v>
       </c>
     </row>
@@ -2511,10 +2511,10 @@
       <c r="A45" s="1">
         <v>12122</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="52">
         <v>92.173913043478294</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="52">
         <v>7.8260869565217401</v>
       </c>
       <c r="H45" s="2" t="s">
@@ -2535,13 +2535,13 @@
       <c r="M45" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="N45" s="65" t="s">
+      <c r="N45" s="49" t="s">
         <v>254</v>
       </c>
-      <c r="O45" s="65" t="s">
+      <c r="O45" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="P45" s="65" t="s">
+      <c r="P45" s="49" t="s">
         <v>58</v>
       </c>
       <c r="R45" s="2" t="s">
@@ -2552,10 +2552,10 @@
       <c r="A46" s="1">
         <v>12131</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="52">
         <v>93.625498007968105</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="52">
         <v>6.3745019920318704</v>
       </c>
       <c r="H46" s="2" t="s">
@@ -2564,7 +2564,7 @@
       <c r="R46" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="S46" s="67" t="s">
+      <c r="S46" s="51" t="s">
         <v>255</v>
       </c>
       <c r="T46" s="2" t="s">
@@ -2574,20 +2574,20 @@
         <v>257</v>
       </c>
       <c r="V46" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="W46" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="W46" s="2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>12132</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="52">
         <v>91.902834008097201</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="52">
         <v>8.0971659919028305</v>
       </c>
       <c r="H47" s="1">
@@ -2620,7 +2620,7 @@
       <c r="R47" s="1">
         <v>21132</v>
       </c>
-      <c r="S47" s="2">
+      <c r="S47" s="67">
         <v>-2.4374729598776401</v>
       </c>
       <c r="T47" s="1">
@@ -2629,11 +2629,11 @@
       <c r="U47" s="1">
         <v>1</v>
       </c>
-      <c r="V47" s="1">
+      <c r="V47" s="43">
+        <v>-4.9988772714395697</v>
+      </c>
+      <c r="W47" s="43">
         <v>0.123931351684285</v>
-      </c>
-      <c r="W47" s="1">
-        <v>-4.9988772714395697</v>
       </c>
       <c r="X47" s="1" t="s">
         <v>92</v>
@@ -2655,10 +2655,10 @@
       <c r="A48" s="1">
         <v>12211</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="52">
         <v>91.156462585034006</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="52">
         <v>8.84353741496599</v>
       </c>
       <c r="H48" s="1">
@@ -2691,7 +2691,7 @@
       <c r="R48" s="1">
         <v>13212</v>
       </c>
-      <c r="S48" s="2">
+      <c r="S48" s="67">
         <v>-2.2731123492214298</v>
       </c>
       <c r="T48" s="1">
@@ -2700,21 +2700,21 @@
       <c r="U48" s="1">
         <v>2</v>
       </c>
-      <c r="V48" s="1">
+      <c r="V48" s="43">
+        <v>-5.3218015142079604</v>
+      </c>
+      <c r="W48" s="43">
         <v>0.77557681576510396</v>
-      </c>
-      <c r="W48" s="1">
-        <v>-5.3218015142079604</v>
       </c>
     </row>
     <row r="49" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>12212</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="52">
         <v>89.576547231270396</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="52">
         <v>10.4234527687296</v>
       </c>
       <c r="H49" s="1">
@@ -2747,7 +2747,7 @@
       <c r="R49" s="1">
         <v>12222</v>
       </c>
-      <c r="S49" s="2">
+      <c r="S49" s="67">
         <v>-2.14985285253674</v>
       </c>
       <c r="T49" s="1">
@@ -2756,21 +2756,21 @@
       <c r="U49" s="1">
         <v>3</v>
       </c>
-      <c r="V49" s="1">
+      <c r="V49" s="43">
+        <v>-4.7347344194309304</v>
+      </c>
+      <c r="W49" s="43">
         <v>0.43502871435745599</v>
-      </c>
-      <c r="W49" s="1">
-        <v>-4.7347344194309304</v>
       </c>
     </row>
     <row r="50" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>12221</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="52">
         <v>83.823529411764696</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="52">
         <v>16.176470588235301</v>
       </c>
       <c r="H50" s="1">
@@ -2803,7 +2803,7 @@
       <c r="R50" s="1">
         <v>21222</v>
       </c>
-      <c r="S50" s="2">
+      <c r="S50" s="67">
         <v>-1.7527973928072</v>
       </c>
       <c r="T50" s="1">
@@ -2812,21 +2812,21 @@
       <c r="U50" s="1">
         <v>4</v>
       </c>
-      <c r="V50" s="1">
+      <c r="V50" s="43">
+        <v>-5.8031302758109904</v>
+      </c>
+      <c r="W50" s="43">
         <v>2.2975354901965899</v>
-      </c>
-      <c r="W50" s="1">
-        <v>-5.8031302758109904</v>
       </c>
     </row>
     <row r="51" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>12222</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="52">
         <v>92.582417582417605</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="52">
         <v>7.4175824175824197</v>
       </c>
       <c r="H51" s="1">
@@ -2859,7 +2859,7 @@
       <c r="R51" s="1">
         <v>13232</v>
       </c>
-      <c r="S51" s="2">
+      <c r="S51" s="67">
         <v>-1.38525594745957</v>
       </c>
       <c r="T51" s="1">
@@ -2868,21 +2868,21 @@
       <c r="U51" s="1">
         <v>5</v>
       </c>
-      <c r="V51" s="1">
+      <c r="V51" s="43">
+        <v>-4.5748899580133804</v>
+      </c>
+      <c r="W51" s="43">
         <v>1.8043780630942301</v>
-      </c>
-      <c r="W51" s="1">
-        <v>-4.5748899580133804</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>12231</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="52">
         <v>90.209790209790199</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="52">
         <v>9.79020979020979</v>
       </c>
       <c r="H52" s="1">
@@ -2915,7 +2915,7 @@
       <c r="R52" s="1">
         <v>23131</v>
       </c>
-      <c r="S52" s="2">
+      <c r="S52" s="67">
         <v>-1.3520553758190501</v>
       </c>
       <c r="T52" s="1">
@@ -2924,28 +2924,28 @@
       <c r="U52" s="1">
         <v>6</v>
       </c>
-      <c r="V52" s="1">
+      <c r="V52" s="43">
+        <v>-5.0646734737213901</v>
+      </c>
+      <c r="W52" s="43">
         <v>2.3605627220832899</v>
-      </c>
-      <c r="W52" s="1">
-        <v>-5.0646734737213901</v>
       </c>
     </row>
     <row r="53" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>12232</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="52">
         <v>89.432485322896298</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="52">
         <v>10.5675146771037</v>
       </c>
-      <c r="R53" s="62"/>
-      <c r="S53" s="62"/>
-      <c r="T53" s="62"/>
-      <c r="U53" s="62"/>
-      <c r="V53" s="66"/>
+      <c r="R53" s="48"/>
+      <c r="S53" s="68"/>
+      <c r="T53" s="48"/>
+      <c r="U53" s="48"/>
+      <c r="V53" s="50"/>
       <c r="W53" s="1" t="s">
         <v>261</v>
       </c>
@@ -2954,24 +2954,25 @@
       <c r="A54" s="1">
         <v>13111</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="52">
         <v>96.774193548387103</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="52">
         <v>3.2258064516128999</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="S54" s="43"/>
     </row>
     <row r="55" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>13112</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="52">
         <v>89.552238805970106</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="52">
         <v>10.4477611940298</v>
       </c>
       <c r="H55" s="1">
@@ -3004,7 +3005,7 @@
       <c r="R55" s="1">
         <v>11231</v>
       </c>
-      <c r="S55" s="2">
+      <c r="S55" s="67">
         <v>2.1783763039510702</v>
       </c>
       <c r="T55" s="1">
@@ -3013,21 +3014,21 @@
       <c r="U55" s="1">
         <v>67</v>
       </c>
-      <c r="V55" s="1">
+      <c r="V55" s="43">
+        <v>-0.398000907706553</v>
+      </c>
+      <c r="W55" s="43">
         <v>4.7547535156086997</v>
-      </c>
-      <c r="W55" s="1">
-        <v>-0.398000907706553</v>
       </c>
     </row>
     <row r="56" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>13121</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="52">
         <v>88.785046728972006</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="52">
         <v>11.214953271028</v>
       </c>
       <c r="H56" s="1">
@@ -3060,7 +3061,7 @@
       <c r="R56" s="1">
         <v>12221</v>
       </c>
-      <c r="S56" s="2">
+      <c r="S56" s="67">
         <v>2.2499393965209</v>
       </c>
       <c r="T56" s="1">
@@ -3069,21 +3070,21 @@
       <c r="U56" s="1">
         <v>68</v>
       </c>
-      <c r="V56" s="1">
+      <c r="V56" s="43">
+        <v>-1.0138057120675401</v>
+      </c>
+      <c r="W56" s="43">
         <v>5.5136845051093397</v>
-      </c>
-      <c r="W56" s="1">
-        <v>-1.0138057120675401</v>
       </c>
     </row>
     <row r="57" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>13122</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="52">
         <v>85.714285714285694</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="52">
         <v>14.285714285714301</v>
       </c>
       <c r="H57" s="1">
@@ -3116,7 +3117,7 @@
       <c r="R57" s="1">
         <v>23232</v>
       </c>
-      <c r="S57" s="2">
+      <c r="S57" s="67">
         <v>2.2910895764829902</v>
       </c>
       <c r="T57" s="1">
@@ -3125,21 +3126,21 @@
       <c r="U57" s="1">
         <v>69</v>
       </c>
-      <c r="V57" s="1">
+      <c r="V57" s="43">
+        <v>-2.43975198900733</v>
+      </c>
+      <c r="W57" s="43">
         <v>7.0219311419733099</v>
-      </c>
-      <c r="W57" s="1">
-        <v>-2.43975198900733</v>
       </c>
     </row>
     <row r="58" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>13131</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="52">
         <v>93.3333333333333</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="52">
         <v>6.6666666666666696</v>
       </c>
       <c r="H58" s="1">
@@ -3172,7 +3173,7 @@
       <c r="R58" s="1">
         <v>22231</v>
       </c>
-      <c r="S58" s="2">
+      <c r="S58" s="67">
         <v>2.8995339642012801</v>
       </c>
       <c r="T58" s="1">
@@ -3181,21 +3182,21 @@
       <c r="U58" s="1">
         <v>70</v>
       </c>
-      <c r="V58" s="1">
+      <c r="V58" s="43">
+        <v>-1.2732832474564899</v>
+      </c>
+      <c r="W58" s="43">
         <v>7.0723511758590503</v>
-      </c>
-      <c r="W58" s="1">
-        <v>-1.2732832474564899</v>
       </c>
     </row>
     <row r="59" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>13132</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="52">
         <v>89.5372233400402</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59" s="52">
         <v>10.4627766599598</v>
       </c>
       <c r="H59" s="1">
@@ -3228,7 +3229,7 @@
       <c r="R59" s="1">
         <v>23112</v>
       </c>
-      <c r="S59" s="2">
+      <c r="S59" s="67">
         <v>3.46032451184628</v>
       </c>
       <c r="T59" s="1">
@@ -3237,21 +3238,21 @@
       <c r="U59" s="1">
         <v>71</v>
       </c>
-      <c r="V59" s="1">
+      <c r="V59" s="43">
+        <v>-1.0651811517918699</v>
+      </c>
+      <c r="W59" s="43">
         <v>7.9858301754844296</v>
-      </c>
-      <c r="W59" s="1">
-        <v>-1.0651811517918699</v>
       </c>
     </row>
     <row r="60" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>13211</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="52">
         <v>93.661971830985905</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="52">
         <v>6.3380281690140796</v>
       </c>
       <c r="H60" s="1">
@@ -3284,7 +3285,7 @@
       <c r="R60" s="1">
         <v>23122</v>
       </c>
-      <c r="S60" s="2">
+      <c r="S60" s="67">
         <v>3.73158300769117</v>
       </c>
       <c r="T60" s="1">
@@ -3293,21 +3294,21 @@
       <c r="U60" s="1">
         <v>72</v>
       </c>
-      <c r="V60" s="1">
+      <c r="V60" s="43">
+        <v>-0.95195361033137404</v>
+      </c>
+      <c r="W60" s="43">
         <v>8.4151196257137197</v>
-      </c>
-      <c r="W60" s="1">
-        <v>-0.95195361033137404</v>
       </c>
     </row>
     <row r="61" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>13212</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="52">
         <v>90.7780979827089</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="52">
         <v>9.22190201729107</v>
       </c>
       <c r="W61" s="1" t="s">
@@ -3318,27 +3319,27 @@
       <c r="A62" s="1">
         <v>13221</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="52">
         <v>88.0208333333333</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62" s="52">
         <v>11.9791666666667</v>
       </c>
-      <c r="R62" s="62"/>
-      <c r="S62" s="62"/>
-      <c r="T62" s="62"/>
-      <c r="U62" s="62"/>
-      <c r="V62" s="66"/>
-      <c r="W62" s="62"/>
+      <c r="R62" s="48"/>
+      <c r="S62" s="48"/>
+      <c r="T62" s="48"/>
+      <c r="U62" s="48"/>
+      <c r="V62" s="50"/>
+      <c r="W62" s="48"/>
     </row>
     <row r="63" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>13222</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="52">
         <v>84.084880636604794</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="52">
         <v>15.915119363395201</v>
       </c>
       <c r="J63" s="19"/>
@@ -3347,10 +3348,10 @@
       <c r="A64" s="1">
         <v>13231</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="52">
         <v>87.5555555555556</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="52">
         <v>12.4444444444444</v>
       </c>
       <c r="J64" s="19"/>
@@ -3359,10 +3360,10 @@
       <c r="A65" s="1">
         <v>13232</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="52">
         <v>83.977900552486204</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="52">
         <v>16.022099447513799</v>
       </c>
       <c r="J65" s="19"/>
@@ -3371,10 +3372,10 @@
       <c r="A66" s="1">
         <v>21111</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="52">
         <v>95.522388059701498</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="52">
         <v>4.4776119402985097</v>
       </c>
       <c r="J66" s="19"/>
@@ -3383,10 +3384,10 @@
       <c r="A67" s="1">
         <v>21112</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="52">
         <v>90</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="52">
         <v>10</v>
       </c>
       <c r="J67" s="19"/>
@@ -3395,10 +3396,10 @@
       <c r="A68" s="1">
         <v>21121</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="52">
         <v>93.75</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="52">
         <v>6.25</v>
       </c>
     </row>
@@ -3406,10 +3407,10 @@
       <c r="A69" s="1">
         <v>21122</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="52">
         <v>88.273615635179098</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="52">
         <v>11.726384364820801</v>
       </c>
     </row>
@@ -3417,10 +3418,10 @@
       <c r="A70" s="1">
         <v>21131</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="52">
         <v>90.188679245282998</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="52">
         <v>9.8113207547169807</v>
       </c>
     </row>
@@ -3428,10 +3429,10 @@
       <c r="A71" s="1">
         <v>21132</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="52">
         <v>90.466926070038895</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="52">
         <v>9.5330739299610894</v>
       </c>
     </row>
@@ -3439,10 +3440,10 @@
       <c r="A72" s="1">
         <v>21211</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="52">
         <v>90.579710144927503</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="52">
         <v>9.4202898550724594</v>
       </c>
     </row>
@@ -3450,10 +3451,10 @@
       <c r="A73" s="1">
         <v>21212</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="52">
         <v>82.840236686390497</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73" s="52">
         <v>17.159763313609499</v>
       </c>
     </row>
@@ -3461,10 +3462,10 @@
       <c r="A74" s="1">
         <v>21221</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="52">
         <v>83.710407239819006</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="52">
         <v>16.289592760181002</v>
       </c>
     </row>
@@ -3472,10 +3473,10 @@
       <c r="A75" s="1">
         <v>21222</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="52">
         <v>82.957393483709296</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="52">
         <v>17.0426065162907</v>
       </c>
     </row>
@@ -3483,10 +3484,10 @@
       <c r="A76" s="1">
         <v>21231</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="52">
         <v>82.440476190476204</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="52">
         <v>17.5595238095238</v>
       </c>
     </row>
@@ -3494,10 +3495,10 @@
       <c r="A77" s="1">
         <v>21232</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="52">
         <v>80.882352941176507</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C77" s="52">
         <v>19.117647058823501</v>
       </c>
     </row>
@@ -3505,10 +3506,10 @@
       <c r="A78" s="1">
         <v>22111</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="52">
         <v>97.402597402597394</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="52">
         <v>2.5974025974026</v>
       </c>
     </row>
@@ -3516,10 +3517,10 @@
       <c r="A79" s="1">
         <v>22112</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="52">
         <v>86.263736263736305</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79" s="52">
         <v>13.7362637362637</v>
       </c>
     </row>
@@ -3527,10 +3528,10 @@
       <c r="A80" s="1">
         <v>22121</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="52">
         <v>92.96875</v>
       </c>
-      <c r="C80" s="1">
+      <c r="C80" s="52">
         <v>7.03125</v>
       </c>
       <c r="Y80" s="19"/>
@@ -3539,10 +3540,10 @@
       <c r="A81" s="1">
         <v>22122</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="52">
         <v>86.637931034482804</v>
       </c>
-      <c r="C81" s="1">
+      <c r="C81" s="52">
         <v>13.362068965517199</v>
       </c>
     </row>
@@ -3550,10 +3551,10 @@
       <c r="A82" s="1">
         <v>22131</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="52">
         <v>89.754098360655703</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82" s="52">
         <v>10.2459016393443</v>
       </c>
     </row>
@@ -3561,10 +3562,10 @@
       <c r="A83" s="1">
         <v>22132</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="52">
         <v>86.842105263157904</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C83" s="52">
         <v>13.157894736842101</v>
       </c>
     </row>
@@ -3572,10 +3573,10 @@
       <c r="A84" s="1">
         <v>22211</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="52">
         <v>89.5833333333333</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84" s="52">
         <v>10.4166666666667</v>
       </c>
     </row>
@@ -3583,10 +3584,10 @@
       <c r="A85" s="1">
         <v>22212</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="52">
         <v>84.090909090909093</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C85" s="52">
         <v>15.909090909090899</v>
       </c>
     </row>
@@ -3594,10 +3595,10 @@
       <c r="A86" s="1">
         <v>22221</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="52">
         <v>78.947368421052602</v>
       </c>
-      <c r="C86" s="1">
+      <c r="C86" s="52">
         <v>21.052631578947398</v>
       </c>
     </row>
@@ -3605,10 +3606,10 @@
       <c r="A87" s="1">
         <v>22222</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="52">
         <v>79.464285714285694</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C87" s="52">
         <v>20.535714285714299</v>
       </c>
     </row>
@@ -3616,10 +3617,10 @@
       <c r="A88" s="1">
         <v>22231</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="52">
         <v>77.659574468085097</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88" s="52">
         <v>22.340425531914899</v>
       </c>
     </row>
@@ -3627,10 +3628,10 @@
       <c r="A89" s="1">
         <v>22232</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="52">
         <v>78.813559322033896</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89" s="52">
         <v>21.1864406779661</v>
       </c>
     </row>
@@ -3638,10 +3639,10 @@
       <c r="A90" s="1">
         <v>23111</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="52">
         <v>77.7777777777778</v>
       </c>
-      <c r="C90" s="1">
+      <c r="C90" s="52">
         <v>22.2222222222222</v>
       </c>
     </row>
@@ -3649,10 +3650,10 @@
       <c r="A91" s="1">
         <v>23112</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="52">
         <v>75.897435897435898</v>
       </c>
-      <c r="C91" s="1">
+      <c r="C91" s="52">
         <v>24.102564102564099</v>
       </c>
     </row>
@@ -3660,10 +3661,10 @@
       <c r="A92" s="1">
         <v>23121</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="52">
         <v>87.394957983193294</v>
       </c>
-      <c r="C92" s="1">
+      <c r="C92" s="52">
         <v>12.605042016806699</v>
       </c>
     </row>
@@ -3671,10 +3672,10 @@
       <c r="A93" s="1">
         <v>23122</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="52">
         <v>72.357723577235802</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C93" s="52">
         <v>27.642276422764201</v>
       </c>
     </row>
@@ -3682,10 +3683,10 @@
       <c r="A94" s="1">
         <v>23131</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="52">
         <v>86.936936936936902</v>
       </c>
-      <c r="C94" s="1">
+      <c r="C94" s="52">
         <v>13.063063063063099</v>
       </c>
     </row>
@@ -3693,10 +3694,10 @@
       <c r="A95" s="1">
         <v>23132</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="52">
         <v>76.595744680851098</v>
       </c>
-      <c r="C95" s="1">
+      <c r="C95" s="52">
         <v>23.404255319148898</v>
       </c>
     </row>
@@ -3704,10 +3705,10 @@
       <c r="A96" s="1">
         <v>23211</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="52">
         <v>80.769230769230802</v>
       </c>
-      <c r="C96" s="1">
+      <c r="C96" s="52">
         <v>19.230769230769202</v>
       </c>
     </row>
@@ -3715,10 +3716,10 @@
       <c r="A97" s="1">
         <v>23212</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="52">
         <v>77.707006369426793</v>
       </c>
-      <c r="C97" s="1">
+      <c r="C97" s="52">
         <v>22.2929936305732</v>
       </c>
     </row>
@@ -3726,10 +3727,10 @@
       <c r="A98" s="1">
         <v>23221</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98" s="52">
         <v>77.070063694267503</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C98" s="52">
         <v>22.9299363057325</v>
       </c>
     </row>
@@ -3737,10 +3738,10 @@
       <c r="A99" s="1">
         <v>23222</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99" s="52">
         <v>67.806267806267797</v>
       </c>
-      <c r="C99" s="1">
+      <c r="C99" s="52">
         <v>32.193732193732203</v>
       </c>
     </row>
@@ -3748,10 +3749,10 @@
       <c r="A100" s="1">
         <v>23231</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100" s="52">
         <v>72.289156626505999</v>
       </c>
-      <c r="C100" s="1">
+      <c r="C100" s="52">
         <v>27.710843373494001</v>
       </c>
     </row>
@@ -3759,10 +3760,10 @@
       <c r="A101" s="1">
         <v>23232</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101" s="52">
         <v>67.594433399602394</v>
       </c>
-      <c r="C101" s="1">
+      <c r="C101" s="52">
         <v>32.405566600397599</v>
       </c>
       <c r="M101" s="41"/>
@@ -3792,13 +3793,13 @@
       </c>
     </row>
     <row r="103" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="H103" s="53" t="s">
+      <c r="H103" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="I103" s="53"/>
-      <c r="J103" s="53"/>
-      <c r="K103" s="53"/>
-      <c r="L103" s="53"/>
+      <c r="I103" s="59"/>
+      <c r="J103" s="59"/>
+      <c r="K103" s="59"/>
+      <c r="L103" s="59"/>
       <c r="M103" s="20">
         <v>11111</v>
       </c>
@@ -3914,15 +3915,15 @@
       <c r="AT105" s="2"/>
     </row>
     <row r="106" spans="1:46" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="59" t="s">
+      <c r="A106" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B106" s="59"/>
-      <c r="D106" s="60" t="s">
+      <c r="B106" s="65"/>
+      <c r="D106" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="E106" s="60"/>
-      <c r="F106" s="60"/>
+      <c r="E106" s="66"/>
+      <c r="F106" s="66"/>
       <c r="H106" s="20" t="s">
         <v>62</v>
       </c>
@@ -3966,10 +3967,10 @@
       <c r="AP106" s="20"/>
     </row>
     <row r="107" spans="1:46" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="58" t="s">
+      <c r="A107" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="B107" s="58"/>
+      <c r="B107" s="64"/>
       <c r="D107" s="17" t="s">
         <v>52</v>
       </c>
@@ -5041,10 +5042,10 @@
       <c r="AO128" s="19"/>
     </row>
     <row r="129" spans="1:41" ht="18" x14ac:dyDescent="0.25">
-      <c r="A129" s="57" t="s">
+      <c r="A129" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="B129" s="57"/>
+      <c r="B129" s="63"/>
       <c r="H129" s="20" t="s">
         <v>62</v>
       </c>
@@ -8969,25 +8970,25 @@
       <c r="I1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="J1" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="61" t="s">
+      <c r="K1" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="62" t="s">
+      <c r="L1" s="48" t="s">
         <v>230</v>
       </c>
-      <c r="M1" s="62" t="s">
+      <c r="M1" s="48" t="s">
         <v>232</v>
       </c>
-      <c r="N1" s="62" t="s">
+      <c r="N1" s="48" t="s">
         <v>231</v>
       </c>
-      <c r="O1" s="62" t="s">
+      <c r="O1" s="48" t="s">
         <v>233</v>
       </c>
-      <c r="P1" s="62" t="s">
+      <c r="P1" s="48" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9025,19 +9026,19 @@
       <c r="K2" s="43">
         <v>6.1176389357909802</v>
       </c>
-      <c r="L2" s="62">
+      <c r="L2" s="48">
         <v>-3.0903727354831898</v>
       </c>
-      <c r="M2" s="62">
+      <c r="M2" s="48">
         <v>-3.4497533284219601</v>
       </c>
-      <c r="N2" s="62">
+      <c r="N2" s="48">
         <v>-2.73618359894897</v>
       </c>
-      <c r="O2" s="62">
+      <c r="O2" s="48">
         <v>-3.0729576427763998</v>
       </c>
-      <c r="P2" s="62">
+      <c r="P2" s="48">
         <v>4.4236610543303598</v>
       </c>
     </row>
@@ -9075,19 +9076,19 @@
       <c r="K3" s="43">
         <v>8.5129453133499702</v>
       </c>
-      <c r="L3" s="62">
+      <c r="L3" s="48">
         <v>-2.68315217912052</v>
       </c>
-      <c r="M3" s="62">
+      <c r="M3" s="48">
         <v>-3.0032539738305202</v>
       </c>
-      <c r="N3" s="62">
+      <c r="N3" s="48">
         <v>-2.3717073968684899</v>
       </c>
-      <c r="O3" s="62">
+      <c r="O3" s="48">
         <v>-2.7962904093516898</v>
       </c>
-      <c r="P3" s="62">
+      <c r="P3" s="48">
         <v>5.7524964678276298</v>
       </c>
     </row>
@@ -9125,19 +9126,19 @@
       <c r="K4" s="43">
         <v>10.410484050735599</v>
       </c>
-      <c r="L4" s="62">
+      <c r="L4" s="48">
         <v>-2.49494052722671</v>
       </c>
-      <c r="M4" s="62">
+      <c r="M4" s="48">
         <v>-2.8224687617342799</v>
       </c>
-      <c r="N4" s="62">
+      <c r="N4" s="48">
         <v>-2.1748579128143701</v>
       </c>
-      <c r="O4" s="62">
+      <c r="O4" s="48">
         <v>-2.5931026310838101</v>
       </c>
-      <c r="P4" s="62">
+      <c r="P4" s="48">
         <v>6.9583644633061796</v>
       </c>
     </row>
@@ -9175,19 +9176,19 @@
       <c r="K5" s="43">
         <v>11.5548216540856</v>
       </c>
-      <c r="L5" s="62">
+      <c r="L5" s="48">
         <v>-2.33569427602573</v>
       </c>
-      <c r="M5" s="62">
+      <c r="M5" s="48">
         <v>-2.6227794335486001</v>
       </c>
-      <c r="N5" s="62">
+      <c r="N5" s="48">
         <v>-2.0326177195400699</v>
       </c>
-      <c r="O5" s="62">
+      <c r="O5" s="48">
         <v>-2.3164353976591001</v>
       </c>
-      <c r="P5" s="62">
+      <c r="P5" s="48">
         <v>8.9770904826601701</v>
       </c>
     </row>
@@ -9225,19 +9226,19 @@
       <c r="K6" s="43">
         <v>7.3343198654356296</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="48">
         <v>-2.8780787726618899</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="48">
         <v>-3.2398678763361901</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="48">
         <v>-2.5236291939291902</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="48">
         <v>-2.7813852592693098</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="48">
         <v>5.8338409694455704</v>
       </c>
     </row>
@@ -9275,19 +9276,19 @@
       <c r="K7" s="43">
         <v>10.9998785622053</v>
       </c>
-      <c r="L7" s="62">
+      <c r="L7" s="48">
         <v>-2.3879844350667501</v>
       </c>
-      <c r="M7" s="62">
+      <c r="M7" s="48">
         <v>-2.70456441972622</v>
       </c>
-      <c r="N7" s="62">
+      <c r="N7" s="48">
         <v>-2.0854610202717199</v>
       </c>
-      <c r="O7" s="62">
+      <c r="O7" s="48">
         <v>-2.5047180258445998</v>
       </c>
-      <c r="P7" s="62">
+      <c r="P7" s="48">
         <v>7.5528090034148496</v>
       </c>
     </row>
@@ -9325,19 +9326,19 @@
       <c r="K8" s="43">
         <v>11.711213288173999</v>
       </c>
-      <c r="L8" s="62">
+      <c r="L8" s="48">
         <v>-2.3429452370166999</v>
       </c>
-      <c r="M8" s="62">
+      <c r="M8" s="48">
         <v>-2.6829126910611398</v>
       </c>
-      <c r="N8" s="62">
+      <c r="N8" s="48">
         <v>-2.0341948670485901</v>
       </c>
-      <c r="O8" s="62">
+      <c r="O8" s="48">
         <v>-2.3015302475767201</v>
       </c>
-      <c r="P8" s="62">
+      <c r="P8" s="48">
         <v>9.0996305843878602</v>
       </c>
     </row>
@@ -9375,19 +9376,19 @@
       <c r="K9" s="43">
         <v>16.524219876610701</v>
       </c>
-      <c r="L9" s="62">
+      <c r="L9" s="48">
         <v>-1.9066780226181099</v>
       </c>
-      <c r="M9" s="62">
+      <c r="M9" s="48">
         <v>-2.17333191082411</v>
       </c>
-      <c r="N9" s="62">
+      <c r="N9" s="48">
         <v>-1.6372983977348701</v>
       </c>
-      <c r="O9" s="62">
+      <c r="O9" s="48">
         <v>-2.0248630141520101</v>
       </c>
-      <c r="P9" s="62">
+      <c r="P9" s="48">
         <v>11.6617080364679</v>
       </c>
     </row>
@@ -9425,19 +9426,19 @@
       <c r="K10" s="43">
         <v>8.9193751036164404</v>
       </c>
-      <c r="L10" s="62">
+      <c r="L10" s="48">
         <v>-2.64542893795611</v>
       </c>
-      <c r="M10" s="62">
+      <c r="M10" s="48">
         <v>-2.9850519320062601</v>
       </c>
-      <c r="N10" s="62">
+      <c r="N10" s="48">
         <v>-2.3131113975826301</v>
       </c>
-      <c r="O10" s="62">
+      <c r="O10" s="48">
         <v>-2.7650269337584401</v>
       </c>
-      <c r="P10" s="62">
+      <c r="P10" s="48">
         <v>5.9243574444457696</v>
       </c>
     </row>
@@ -9475,19 +9476,19 @@
       <c r="K11" s="43">
         <v>10.5914693270239</v>
       </c>
-      <c r="L11" s="62">
+      <c r="L11" s="48">
         <v>-2.4169230706482199</v>
       </c>
-      <c r="M11" s="62">
+      <c r="M11" s="48">
         <v>-2.6820764350241202</v>
       </c>
-      <c r="N11" s="62">
+      <c r="N11" s="48">
         <v>-2.1526972308253498</v>
       </c>
-      <c r="O11" s="62">
+      <c r="O11" s="48">
         <v>-2.4883597003337199</v>
       </c>
-      <c r="P11" s="62">
+      <c r="P11" s="48">
         <v>7.6678247817657299</v>
       </c>
     </row>
@@ -9525,19 +9526,19 @@
       <c r="K12" s="43">
         <v>14.7900798851225</v>
       </c>
-      <c r="L12" s="62">
+      <c r="L12" s="48">
         <v>-2.0535115557585399</v>
       </c>
-      <c r="M12" s="62">
+      <c r="M12" s="48">
         <v>-2.3143968703701798</v>
       </c>
-      <c r="N12" s="62">
+      <c r="N12" s="48">
         <v>-1.7560602477031499</v>
       </c>
-      <c r="O12" s="62">
+      <c r="O12" s="48">
         <v>-2.28517192206585</v>
       </c>
-      <c r="P12" s="62">
+      <c r="P12" s="48">
         <v>9.2358484175372197</v>
       </c>
     </row>
@@ -9575,19 +9576,19 @@
       <c r="K13" s="43">
         <v>14.996448435760801</v>
       </c>
-      <c r="L13" s="62">
+      <c r="L13" s="48">
         <v>-1.9855308526962301</v>
       </c>
-      <c r="M13" s="62">
+      <c r="M13" s="48">
         <v>-2.2251068057970498</v>
       </c>
-      <c r="N13" s="62">
+      <c r="N13" s="48">
         <v>-1.7250552482839201</v>
       </c>
-      <c r="O13" s="62">
+      <c r="O13" s="48">
         <v>-2.0085046886411302</v>
       </c>
-      <c r="P13" s="62">
+      <c r="P13" s="48">
         <v>11.8312872114243</v>
       </c>
     </row>
@@ -9625,19 +9626,19 @@
       <c r="K14" s="43">
         <v>6.7823198388138497</v>
       </c>
-      <c r="L14" s="62">
+      <c r="L14" s="48">
         <v>-3.0190562976614901</v>
       </c>
-      <c r="M14" s="62">
+      <c r="M14" s="48">
         <v>-3.3813946125816301</v>
       </c>
-      <c r="N14" s="62">
+      <c r="N14" s="48">
         <v>-2.64205808611645</v>
       </c>
-      <c r="O14" s="62">
+      <c r="O14" s="48">
         <v>-3.0243658494171402</v>
       </c>
-      <c r="P14" s="62">
+      <c r="P14" s="48">
         <v>4.6337164922482899</v>
       </c>
     </row>
@@ -9675,19 +9676,19 @@
       <c r="K15" s="43">
         <v>8.0610449480463195</v>
       </c>
-      <c r="L15" s="62">
+      <c r="L15" s="48">
         <v>-2.75319928727053</v>
       </c>
-      <c r="M15" s="62">
+      <c r="M15" s="48">
         <v>-3.1273141679660901</v>
       </c>
-      <c r="N15" s="62">
+      <c r="N15" s="48">
         <v>-2.41331273059332</v>
       </c>
-      <c r="O15" s="62">
+      <c r="O15" s="48">
         <v>-2.7476986159924301</v>
       </c>
-      <c r="P15" s="62">
+      <c r="P15" s="48">
         <v>6.0216755362552501</v>
       </c>
     </row>
@@ -9725,19 +9726,19 @@
       <c r="K16" s="43">
         <v>10.314508490176999</v>
       </c>
-      <c r="L16" s="62">
+      <c r="L16" s="48">
         <v>-2.5034515714744399</v>
       </c>
-      <c r="M16" s="62">
+      <c r="M16" s="48">
         <v>-2.8238775006698398</v>
       </c>
-      <c r="N16" s="62">
+      <c r="N16" s="48">
         <v>-2.1690197933481201</v>
       </c>
-      <c r="O16" s="62">
+      <c r="O16" s="48">
         <v>-2.54451083772455</v>
       </c>
-      <c r="P16" s="62">
+      <c r="P16" s="48">
         <v>7.2796118775279703</v>
       </c>
     </row>
@@ -9775,19 +9776,19 @@
       <c r="K17" s="43">
         <v>12.8554558558953</v>
       </c>
-      <c r="L17" s="62">
+      <c r="L17" s="48">
         <v>-2.2171169161190298</v>
       </c>
-      <c r="M17" s="62">
+      <c r="M17" s="48">
         <v>-2.4964637960540701</v>
       </c>
-      <c r="N17" s="62">
+      <c r="N17" s="48">
         <v>-1.9012184362318001</v>
       </c>
-      <c r="O17" s="62">
+      <c r="O17" s="48">
         <v>-2.26784360429984</v>
       </c>
-      <c r="P17" s="62">
+      <c r="P17" s="48">
         <v>9.3821386191049392</v>
       </c>
     </row>
@@ -9825,19 +9826,19 @@
       <c r="K18" s="43">
         <v>8.8970613419390592</v>
       </c>
-      <c r="L18" s="62">
+      <c r="L18" s="48">
         <v>-2.6874284273755702</v>
       </c>
-      <c r="M18" s="62">
+      <c r="M18" s="48">
         <v>-3.0200038128694202</v>
       </c>
-      <c r="N18" s="62">
+      <c r="N18" s="48">
         <v>-2.3469955716764099</v>
       </c>
-      <c r="O18" s="62">
+      <c r="O18" s="48">
         <v>-2.7327934659100501</v>
       </c>
-      <c r="P18" s="62">
+      <c r="P18" s="48">
         <v>6.1065797991149999</v>
       </c>
     </row>
@@ -9875,19 +9876,19 @@
       <c r="K19" s="43">
         <v>10.4459222448359</v>
       </c>
-      <c r="L19" s="62">
+      <c r="L19" s="48">
         <v>-2.4583772172877798</v>
       </c>
-      <c r="M19" s="62">
+      <c r="M19" s="48">
         <v>-2.76673409665342</v>
       </c>
-      <c r="N19" s="62">
+      <c r="N19" s="48">
         <v>-2.1385650814326</v>
       </c>
-      <c r="O19" s="62">
+      <c r="O19" s="48">
         <v>-2.4561262324853401</v>
       </c>
-      <c r="P19" s="62">
+      <c r="P19" s="48">
         <v>7.89917023292689</v>
       </c>
     </row>
@@ -9925,19 +9926,19 @@
       <c r="K20" s="43">
         <v>15.3072550549784</v>
       </c>
-      <c r="L20" s="62">
+      <c r="L20" s="48">
         <v>-2.01889385808974</v>
       </c>
-      <c r="M20" s="62">
+      <c r="M20" s="48">
         <v>-2.3368876155603302</v>
       </c>
-      <c r="N20" s="62">
+      <c r="N20" s="48">
         <v>-1.70161457751523</v>
       </c>
-      <c r="O20" s="62">
+      <c r="O20" s="48">
         <v>-2.25293845421746</v>
       </c>
-      <c r="P20" s="62">
+      <c r="P20" s="48">
         <v>9.5096301084327894</v>
       </c>
     </row>
@@ -9975,19 +9976,19 @@
       <c r="K21" s="43">
         <v>12.7177698651962</v>
       </c>
-      <c r="L21" s="62">
+      <c r="L21" s="48">
         <v>-2.2074679861695801</v>
       </c>
-      <c r="M21" s="62">
+      <c r="M21" s="48">
         <v>-2.49446031365621</v>
       </c>
-      <c r="N21" s="62">
+      <c r="N21" s="48">
         <v>-1.93449056089705</v>
       </c>
-      <c r="O21" s="62">
+      <c r="O21" s="48">
         <v>-1.97627122079274</v>
       </c>
-      <c r="P21" s="62">
+      <c r="P21" s="48">
         <v>12.1716889503482</v>
       </c>
     </row>
@@ -10025,19 +10026,19 @@
       <c r="K22" s="43">
         <v>8.3036702166475198</v>
       </c>
-      <c r="L22" s="62">
+      <c r="L22" s="48">
         <v>-2.6928928984349798</v>
       </c>
-      <c r="M22" s="62">
+      <c r="M22" s="48">
         <v>-3.0330866111642498</v>
       </c>
-      <c r="N22" s="62">
+      <c r="N22" s="48">
         <v>-2.3798402722386198</v>
       </c>
-      <c r="O22" s="62">
+      <c r="O22" s="48">
         <v>-2.7164351403991698</v>
       </c>
-      <c r="P22" s="62">
+      <c r="P22" s="48">
         <v>6.2010493541898501</v>
       </c>
     </row>
@@ -10075,19 +10076,19 @@
       <c r="K23" s="43">
         <v>10.4007522719353</v>
       </c>
-      <c r="L23" s="62">
+      <c r="L23" s="48">
         <v>-2.4296915843963101</v>
       </c>
-      <c r="M23" s="62">
+      <c r="M23" s="48">
         <v>-2.7094424775049499</v>
       </c>
-      <c r="N23" s="62">
+      <c r="N23" s="48">
         <v>-2.1576095656586598</v>
       </c>
-      <c r="O23" s="62">
+      <c r="O23" s="48">
         <v>-2.4397679069744602</v>
       </c>
-      <c r="P23" s="62">
+      <c r="P23" s="48">
         <v>8.0190029591014795</v>
       </c>
     </row>
@@ -10125,19 +10126,19 @@
       <c r="K24" s="43">
         <v>12.5524471966608</v>
       </c>
-      <c r="L24" s="62">
+      <c r="L24" s="48">
         <v>-2.2375758683971201</v>
       </c>
-      <c r="M24" s="62">
+      <c r="M24" s="48">
         <v>-2.53091341964176</v>
       </c>
-      <c r="N24" s="62">
+      <c r="N24" s="48">
         <v>-1.95183785337891</v>
       </c>
-      <c r="O24" s="62">
+      <c r="O24" s="48">
         <v>-2.2365801287065801</v>
       </c>
-      <c r="P24" s="62">
+      <c r="P24" s="48">
         <v>9.6513338193271903</v>
       </c>
     </row>
@@ -10175,19 +10176,19 @@
       <c r="K25" s="43">
         <v>14.1161697442234</v>
       </c>
-      <c r="L25" s="62">
+      <c r="L25" s="48">
         <v>-2.0656114272353299</v>
       </c>
-      <c r="M25" s="62">
+      <c r="M25" s="48">
         <v>-2.3237667603525201</v>
       </c>
-      <c r="N25" s="62">
+      <c r="N25" s="48">
         <v>-1.7910111806587801</v>
       </c>
-      <c r="O25" s="62">
+      <c r="O25" s="48">
         <v>-1.9599128952818701</v>
       </c>
-      <c r="P25" s="62">
+      <c r="P25" s="48">
         <v>12.347647460271601</v>
       </c>
     </row>
@@ -10225,19 +10226,19 @@
       <c r="K26" s="43">
         <v>9.2948153710372008</v>
       </c>
-      <c r="L26" s="62">
+      <c r="L26" s="48">
         <v>-2.6373411829112601</v>
       </c>
-      <c r="M26" s="62">
+      <c r="M26" s="48">
         <v>-2.9920919458040198</v>
       </c>
-      <c r="N26" s="62">
+      <c r="N26" s="48">
         <v>-2.2517161026539698</v>
       </c>
-      <c r="O26" s="62">
+      <c r="O26" s="48">
         <v>-2.57708677412709</v>
       </c>
-      <c r="P26" s="62">
+      <c r="P26" s="48">
         <v>7.0627714380323496</v>
       </c>
     </row>
@@ -10275,19 +10276,19 @@
       <c r="K27" s="43">
         <v>12.530999611576</v>
       </c>
-      <c r="L27" s="62">
+      <c r="L27" s="48">
         <v>-2.2560294475139</v>
       </c>
-      <c r="M27" s="62">
+      <c r="M27" s="48">
         <v>-2.5690870238330699</v>
       </c>
-      <c r="N27" s="62">
+      <c r="N27" s="48">
         <v>-1.94880501570592</v>
       </c>
-      <c r="O27" s="62">
+      <c r="O27" s="48">
         <v>-2.3004195407023702</v>
       </c>
-      <c r="P27" s="62">
+      <c r="P27" s="48">
         <v>9.1088220795416799</v>
       </c>
     </row>
@@ -10325,19 +10326,19 @@
       <c r="K28" s="43">
         <v>12.966141309088</v>
       </c>
-      <c r="L28" s="62">
+      <c r="L28" s="48">
         <v>-2.22419580302159</v>
       </c>
-      <c r="M28" s="62">
+      <c r="M28" s="48">
         <v>-2.5632029839548198</v>
       </c>
-      <c r="N28" s="62">
+      <c r="N28" s="48">
         <v>-1.9145067046295099</v>
       </c>
-      <c r="O28" s="62">
+      <c r="O28" s="48">
         <v>-2.0972317624344901</v>
       </c>
-      <c r="P28" s="62">
+      <c r="P28" s="48">
         <v>10.9366170522977</v>
       </c>
     </row>
@@ -10375,19 +10376,19 @@
       <c r="K29" s="43">
         <v>14.6560160189639</v>
       </c>
-      <c r="L29" s="62">
+      <c r="L29" s="48">
         <v>-2.0353697392291901</v>
       </c>
-      <c r="M29" s="62">
+      <c r="M29" s="48">
         <v>-2.3244418381115102</v>
       </c>
-      <c r="N29" s="62">
+      <c r="N29" s="48">
         <v>-1.76494875621347</v>
       </c>
-      <c r="O29" s="62">
+      <c r="O29" s="48">
         <v>-1.8205645290097801</v>
       </c>
-      <c r="P29" s="62">
+      <c r="P29" s="48">
         <v>13.9366147745571</v>
       </c>
     </row>
@@ -10425,19 +10426,19 @@
       <c r="K30" s="43">
         <v>12.8433775939563</v>
       </c>
-      <c r="L30" s="62">
+      <c r="L30" s="48">
         <v>-2.2401008886745499</v>
       </c>
-      <c r="M30" s="62">
+      <c r="M30" s="48">
         <v>-2.5714199678860101</v>
       </c>
-      <c r="N30" s="62">
+      <c r="N30" s="48">
         <v>-1.88557339524247</v>
       </c>
-      <c r="O30" s="62">
+      <c r="O30" s="48">
         <v>-2.2855143906199902</v>
       </c>
-      <c r="P30" s="62">
+      <c r="P30" s="48">
         <v>9.2329779593851597</v>
       </c>
     </row>
@@ -10475,19 +10476,19 @@
       <c r="K31" s="43">
         <v>16.563173422756101</v>
       </c>
-      <c r="L31" s="62">
+      <c r="L31" s="48">
         <v>-1.90998602527318</v>
       </c>
-      <c r="M31" s="62">
+      <c r="M31" s="48">
         <v>-2.17985051222982</v>
       </c>
-      <c r="N31" s="62">
+      <c r="N31" s="48">
         <v>-1.6069606255098801</v>
       </c>
-      <c r="O31" s="62">
+      <c r="O31" s="48">
         <v>-2.0088471571952802</v>
       </c>
-      <c r="P31" s="62">
+      <c r="P31" s="48">
         <v>11.827715219830401</v>
       </c>
     </row>
@@ -10525,19 +10526,19 @@
       <c r="K32" s="43">
         <v>17.1179756779302</v>
       </c>
-      <c r="L32" s="62">
+      <c r="L32" s="48">
         <v>-1.871086899389</v>
       </c>
-      <c r="M32" s="62">
+      <c r="M32" s="48">
         <v>-2.18953566006086</v>
       </c>
-      <c r="N32" s="62">
+      <c r="N32" s="48">
         <v>-1.5630614072256801</v>
       </c>
-      <c r="O32" s="62">
+      <c r="O32" s="48">
         <v>-1.8056593789274</v>
       </c>
-      <c r="P32" s="62">
+      <c r="P32" s="48">
         <v>14.1163547801013</v>
       </c>
     </row>
@@ -10575,19 +10576,19 @@
       <c r="K33" s="43">
         <v>20.439348825167599</v>
       </c>
-      <c r="L33" s="62">
+      <c r="L33" s="48">
         <v>-1.60697319822823</v>
       </c>
-      <c r="M33" s="62">
+      <c r="M33" s="48">
         <v>-1.8712808814508199</v>
       </c>
-      <c r="N33" s="62">
+      <c r="N33" s="48">
         <v>-1.3578375266932801</v>
       </c>
-      <c r="O33" s="62">
+      <c r="O33" s="48">
         <v>-1.52899214550269</v>
       </c>
-      <c r="P33" s="62">
+      <c r="P33" s="48">
         <v>17.8141194785964</v>
       </c>
     </row>
@@ -10625,19 +10626,19 @@
       <c r="K34" s="43">
         <v>11.2622091993706</v>
       </c>
-      <c r="L34" s="62">
+      <c r="L34" s="48">
         <v>-2.39170829333617</v>
       </c>
-      <c r="M34" s="62">
+      <c r="M34" s="48">
         <v>-2.69603967735158</v>
       </c>
-      <c r="N34" s="62">
+      <c r="N34" s="48">
         <v>-2.0646337156279202</v>
       </c>
-      <c r="O34" s="62">
+      <c r="O34" s="48">
         <v>-2.26915606510912</v>
       </c>
-      <c r="P34" s="62">
+      <c r="P34" s="48">
         <v>9.3709861641564505</v>
       </c>
     </row>
@@ -10675,19 +10676,19 @@
       <c r="K35" s="43">
         <v>14.0704766210629</v>
       </c>
-      <c r="L35" s="62">
+      <c r="L35" s="48">
         <v>-2.08709016029418</v>
       </c>
-      <c r="M35" s="62">
+      <c r="M35" s="48">
         <v>-2.33600054694196</v>
       </c>
-      <c r="N35" s="62">
+      <c r="N35" s="48">
         <v>-1.82799387752217</v>
       </c>
-      <c r="O35" s="62">
+      <c r="O35" s="48">
         <v>-1.99248883168441</v>
       </c>
-      <c r="P35" s="62">
+      <c r="P35" s="48">
         <v>11.999380490352401</v>
       </c>
     </row>
@@ -10725,19 +10726,19 @@
       <c r="K36" s="43">
         <v>17.458282647952299</v>
       </c>
-      <c r="L36" s="62">
+      <c r="L36" s="48">
         <v>-1.8544030913596601</v>
       </c>
-      <c r="M36" s="62">
+      <c r="M36" s="48">
         <v>-2.1350017591824502</v>
       </c>
-      <c r="N36" s="62">
+      <c r="N36" s="48">
         <v>-1.57089114151078</v>
       </c>
-      <c r="O36" s="62">
+      <c r="O36" s="48">
         <v>-1.7893010534165299</v>
       </c>
-      <c r="P36" s="62">
+      <c r="P36" s="48">
         <v>14.3158437751548</v>
       </c>
     </row>
@@ -10775,19 +10776,19 @@
       <c r="K37" s="43">
         <v>19.950369827787299</v>
       </c>
-      <c r="L37" s="62">
+      <c r="L37" s="48">
         <v>-1.61185928581113</v>
       </c>
-      <c r="M37" s="62">
+      <c r="M37" s="48">
         <v>-1.8467724829239001</v>
       </c>
-      <c r="N37" s="62">
+      <c r="N37" s="48">
         <v>-1.3933882718233199</v>
       </c>
-      <c r="O37" s="62">
+      <c r="O37" s="48">
         <v>-1.5126338199918199</v>
       </c>
-      <c r="P37" s="62">
+      <c r="P37" s="48">
         <v>18.054878913607698</v>
       </c>
     </row>
@@ -10825,19 +10826,19 @@
       <c r="K38" s="43">
         <v>10.4836544886462</v>
       </c>
-      <c r="L38" s="62">
+      <c r="L38" s="48">
         <v>-2.4860936803154599</v>
       </c>
-      <c r="M38" s="62">
+      <c r="M38" s="48">
         <v>-2.8381115125919401</v>
       </c>
-      <c r="N38" s="62">
+      <c r="N38" s="48">
         <v>-2.1290402697719899</v>
       </c>
-      <c r="O38" s="62">
+      <c r="O38" s="48">
         <v>-2.4283501756426298</v>
       </c>
-      <c r="P38" s="62">
+      <c r="P38" s="48">
         <v>8.1036243704474504</v>
       </c>
     </row>
@@ -10875,19 +10876,19 @@
       <c r="K39" s="43">
         <v>13.526240308945001</v>
       </c>
-      <c r="L39" s="62">
+      <c r="L39" s="48">
         <v>-2.1642772086909301</v>
       </c>
-      <c r="M39" s="62">
+      <c r="M39" s="48">
         <v>-2.47687156844384</v>
       </c>
-      <c r="N39" s="62">
+      <c r="N39" s="48">
         <v>-1.8689765132542899</v>
       </c>
-      <c r="O39" s="62">
+      <c r="O39" s="48">
         <v>-2.1516829422179198</v>
       </c>
-      <c r="P39" s="62">
+      <c r="P39" s="48">
         <v>10.417406321987499</v>
       </c>
     </row>
@@ -10925,19 +10926,19 @@
       <c r="K40" s="43">
         <v>15.5555749961385</v>
       </c>
-      <c r="L40" s="62">
+      <c r="L40" s="48">
         <v>-2.0204161648797698</v>
       </c>
-      <c r="M40" s="62">
+      <c r="M40" s="48">
         <v>-2.3266028258550202</v>
       </c>
-      <c r="N40" s="62">
+      <c r="N40" s="48">
         <v>-1.7006708011453899</v>
       </c>
-      <c r="O40" s="62">
+      <c r="O40" s="48">
         <v>-1.9484951639500401</v>
       </c>
-      <c r="P40" s="62">
+      <c r="P40" s="48">
         <v>12.4717537966392</v>
       </c>
     </row>
@@ -10975,19 +10976,19 @@
       <c r="K41" s="43">
         <v>20.725345888952901</v>
       </c>
-      <c r="L41" s="62">
+      <c r="L41" s="48">
         <v>-1.6079301622506199</v>
       </c>
-      <c r="M41" s="62">
+      <c r="M41" s="48">
         <v>-1.8976048883173799</v>
       </c>
-      <c r="N41" s="62">
+      <c r="N41" s="48">
         <v>-1.3542924871309701</v>
       </c>
-      <c r="O41" s="62">
+      <c r="O41" s="48">
         <v>-1.6718279305253301</v>
       </c>
-      <c r="P41" s="62">
+      <c r="P41" s="48">
         <v>15.818062039585399</v>
       </c>
     </row>
@@ -11025,19 +11026,19 @@
       <c r="K42" s="43">
         <v>12.8213482789008</v>
       </c>
-      <c r="L42" s="62">
+      <c r="L42" s="48">
         <v>-2.2426252278914398</v>
       </c>
-      <c r="M42" s="62">
+      <c r="M42" s="48">
         <v>-2.5837350503463798</v>
       </c>
-      <c r="N42" s="62">
+      <c r="N42" s="48">
         <v>-1.9234723236726301</v>
       </c>
-      <c r="O42" s="62">
+      <c r="O42" s="48">
         <v>-2.1367777921355402</v>
       </c>
-      <c r="P42" s="62">
+      <c r="P42" s="48">
         <v>10.557326825735499</v>
       </c>
     </row>
@@ -11075,19 +11076,19 @@
       <c r="K43" s="43">
         <v>16.031792096092602</v>
       </c>
-      <c r="L43" s="62">
+      <c r="L43" s="48">
         <v>-1.93522830325913</v>
       </c>
-      <c r="M43" s="62">
+      <c r="M43" s="48">
         <v>-2.2198719484824898</v>
       </c>
-      <c r="N43" s="62">
+      <c r="N43" s="48">
         <v>-1.63150729543174</v>
       </c>
-      <c r="O43" s="62">
+      <c r="O43" s="48">
         <v>-1.86011055871082</v>
       </c>
-      <c r="P43" s="62">
+      <c r="P43" s="48">
         <v>13.4690165954798</v>
       </c>
     </row>
@@ -11125,19 +11126,19 @@
       <c r="K44" s="43">
         <v>20.396649548154901</v>
       </c>
-      <c r="L44" s="62">
+      <c r="L44" s="48">
         <v>-1.6470490084126801</v>
       </c>
-      <c r="M44" s="62">
+      <c r="M44" s="48">
         <v>-1.9431993377363499</v>
       </c>
-      <c r="N44" s="62">
+      <c r="N44" s="48">
         <v>-1.3340647970500901</v>
       </c>
-      <c r="O44" s="62">
+      <c r="O44" s="48">
         <v>-1.65692278044295</v>
       </c>
-      <c r="P44" s="62">
+      <c r="P44" s="48">
         <v>16.0175509670377</v>
       </c>
     </row>
@@ -11175,19 +11176,19 @@
       <c r="K45" s="43">
         <v>22.5225740192305</v>
       </c>
-      <c r="L45" s="62">
+      <c r="L45" s="48">
         <v>-1.50242897933589</v>
       </c>
-      <c r="M45" s="62">
+      <c r="M45" s="48">
         <v>-1.76984075314222</v>
       </c>
-      <c r="N45" s="62">
+      <c r="N45" s="48">
         <v>-1.24246698739892</v>
       </c>
-      <c r="O45" s="62">
+      <c r="O45" s="48">
         <v>-1.3802555470182301</v>
       </c>
-      <c r="P45" s="62">
+      <c r="P45" s="48">
         <v>20.096796091550001</v>
       </c>
     </row>
@@ -11225,19 +11226,19 @@
       <c r="K46" s="43">
         <v>13.7150744105131</v>
       </c>
-      <c r="L46" s="62">
+      <c r="L46" s="48">
         <v>-2.1588875637402598</v>
       </c>
-      <c r="M46" s="62">
+      <c r="M46" s="48">
         <v>-2.4698669780685001</v>
       </c>
-      <c r="N46" s="62">
+      <c r="N46" s="48">
         <v>-1.8460640523613701</v>
       </c>
-      <c r="O46" s="62">
+      <c r="O46" s="48">
         <v>-2.1204194666246599</v>
       </c>
-      <c r="P46" s="62">
+      <c r="P46" s="48">
         <v>10.712794124303599</v>
       </c>
     </row>
@@ -11275,19 +11276,19 @@
       <c r="K47" s="43">
         <v>13.947563057128001</v>
       </c>
-      <c r="L47" s="62">
+      <c r="L47" s="48">
         <v>-2.0707376655346801</v>
       </c>
-      <c r="M47" s="62">
+      <c r="M47" s="48">
         <v>-2.33091833567592</v>
       </c>
-      <c r="N47" s="62">
+      <c r="N47" s="48">
         <v>-1.8251865181534499</v>
       </c>
-      <c r="O47" s="62">
+      <c r="O47" s="48">
         <v>-1.8437522331999501</v>
       </c>
-      <c r="P47" s="62">
+      <c r="P47" s="48">
         <v>13.660812662823099</v>
       </c>
     </row>
@@ -11325,19 +11326,19 @@
       <c r="K48" s="43">
         <v>20.880781913257302</v>
       </c>
-      <c r="L48" s="62">
+      <c r="L48" s="48">
         <v>-1.58627236593804</v>
       </c>
-      <c r="M48" s="62">
+      <c r="M48" s="48">
         <v>-1.8389201044424499</v>
       </c>
-      <c r="N48" s="62">
+      <c r="N48" s="48">
         <v>-1.31748901139191</v>
       </c>
-      <c r="O48" s="62">
+      <c r="O48" s="48">
         <v>-1.6405644549320699</v>
       </c>
-      <c r="P48" s="62">
+      <c r="P48" s="48">
         <v>16.238827173685799</v>
       </c>
     </row>
@@ -11375,19 +11376,19 @@
       <c r="K49" s="43">
         <v>23.619903833864299</v>
       </c>
-      <c r="L49" s="62">
+      <c r="L49" s="48">
         <v>-1.4203639247183599</v>
       </c>
-      <c r="M49" s="62">
+      <c r="M49" s="48">
         <v>-1.65116774279641</v>
       </c>
-      <c r="N49" s="62">
+      <c r="N49" s="48">
         <v>-1.16954550983226</v>
       </c>
-      <c r="O49" s="62">
+      <c r="O49" s="48">
         <v>-1.3638972215073599</v>
       </c>
-      <c r="P49" s="62">
+      <c r="P49" s="48">
         <v>20.3607631720072</v>
       </c>
     </row>
@@ -11425,19 +11426,19 @@
       <c r="K50" s="43">
         <v>10.602202473045301</v>
       </c>
-      <c r="L50" s="62">
+      <c r="L50" s="48">
         <v>-2.4889259956614902</v>
       </c>
-      <c r="M50" s="62">
+      <c r="M50" s="48">
         <v>-2.8472195987828401</v>
       </c>
-      <c r="N50" s="62">
+      <c r="N50" s="48">
         <v>-2.1327986837606798</v>
       </c>
-      <c r="O50" s="62">
+      <c r="O50" s="48">
         <v>-2.3797583822833701</v>
       </c>
-      <c r="P50" s="62">
+      <c r="P50" s="48">
         <v>8.4729301364341403</v>
       </c>
     </row>
@@ -11475,19 +11476,19 @@
       <c r="K51" s="43">
         <v>15.426349246714899</v>
       </c>
-      <c r="L51" s="62">
+      <c r="L51" s="48">
         <v>-2.0104222826895399</v>
       </c>
-      <c r="M51" s="62">
+      <c r="M51" s="48">
         <v>-2.3248387259040499</v>
       </c>
-      <c r="N51" s="62">
+      <c r="N51" s="48">
         <v>-1.7104955619323099</v>
       </c>
-      <c r="O51" s="62">
+      <c r="O51" s="48">
         <v>-2.1030911488586499</v>
       </c>
-      <c r="P51" s="62">
+      <c r="P51" s="48">
         <v>10.8796740732946</v>
       </c>
     </row>
@@ -11525,19 +11526,19 @@
       <c r="K52" s="43">
         <v>16.285474495934</v>
       </c>
-      <c r="L52" s="62">
+      <c r="L52" s="48">
         <v>-1.9610430401563701</v>
       </c>
-      <c r="M52" s="62">
+      <c r="M52" s="48">
         <v>-2.2841227147295702</v>
       </c>
-      <c r="N52" s="62">
+      <c r="N52" s="48">
         <v>-1.64060277144776</v>
       </c>
-      <c r="O52" s="62">
+      <c r="O52" s="48">
         <v>-1.89990337059077</v>
       </c>
-      <c r="P52" s="62">
+      <c r="P52" s="48">
         <v>13.011941129548999</v>
       </c>
     </row>
@@ -11575,19 +11576,19 @@
       <c r="K53" s="43">
         <v>20.421700095814199</v>
       </c>
-      <c r="L53" s="62">
+      <c r="L53" s="48">
         <v>-1.6409770220656901</v>
       </c>
-      <c r="M53" s="62">
+      <c r="M53" s="48">
         <v>-1.90933876319978</v>
       </c>
-      <c r="N53" s="62">
+      <c r="N53" s="48">
         <v>-1.3791028399171099</v>
       </c>
-      <c r="O53" s="62">
+      <c r="O53" s="48">
         <v>-1.62323613716606</v>
       </c>
-      <c r="P53" s="62">
+      <c r="P53" s="48">
         <v>16.475905073542599</v>
       </c>
     </row>
@@ -11625,19 +11626,19 @@
       <c r="K54" s="43">
         <v>13.5386678436489</v>
       </c>
-      <c r="L54" s="62">
+      <c r="L54" s="48">
         <v>-2.1810523424731501</v>
       </c>
-      <c r="M54" s="62">
+      <c r="M54" s="48">
         <v>-2.5247747930561202</v>
       </c>
-      <c r="N54" s="62">
+      <c r="N54" s="48">
         <v>-1.87549913473182</v>
       </c>
-      <c r="O54" s="62">
+      <c r="O54" s="48">
         <v>-2.0881859987762699</v>
       </c>
-      <c r="P54" s="62">
+      <c r="P54" s="48">
         <v>11.025039348757</v>
       </c>
     </row>
@@ -11675,19 +11676,19 @@
       <c r="K55" s="43">
         <v>17.4358167231232</v>
       </c>
-      <c r="L55" s="62">
+      <c r="L55" s="48">
         <v>-1.8360849182646499</v>
       </c>
-      <c r="M55" s="62">
+      <c r="M55" s="48">
         <v>-2.1432413997211501</v>
       </c>
-      <c r="N55" s="62">
+      <c r="N55" s="48">
         <v>-1.5514433155681</v>
       </c>
-      <c r="O55" s="62">
+      <c r="O55" s="48">
         <v>-1.8115187653515601</v>
       </c>
-      <c r="P55" s="62">
+      <c r="P55" s="48">
         <v>14.0454669369957</v>
       </c>
     </row>
@@ -11725,19 +11726,19 @@
       <c r="K56" s="43">
         <v>23.8557865687781</v>
       </c>
-      <c r="L56" s="62">
+      <c r="L56" s="48">
         <v>-1.4883892404381001</v>
       </c>
-      <c r="M56" s="62">
+      <c r="M56" s="48">
         <v>-1.7841714081473701</v>
       </c>
-      <c r="N56" s="62">
+      <c r="N56" s="48">
         <v>-1.19337387546475</v>
       </c>
-      <c r="O56" s="62">
+      <c r="O56" s="48">
         <v>-1.6083309870836799</v>
       </c>
-      <c r="P56" s="62">
+      <c r="P56" s="48">
         <v>16.682046302999701</v>
       </c>
     </row>
@@ -11775,19 +11776,19 @@
       <c r="K57" s="43">
         <v>25.152314674356699</v>
       </c>
-      <c r="L57" s="62">
+      <c r="L57" s="48">
         <v>-1.3454478204425699</v>
       </c>
-      <c r="M57" s="62">
+      <c r="M57" s="48">
         <v>-1.6185678781564401</v>
       </c>
-      <c r="N57" s="62">
+      <c r="N57" s="48">
         <v>-1.08623131807948</v>
       </c>
-      <c r="O57" s="62">
+      <c r="O57" s="48">
         <v>-1.3316637536589699</v>
       </c>
-      <c r="P57" s="62">
+      <c r="P57" s="48">
         <v>20.888429401697099</v>
       </c>
     </row>
@@ -11825,19 +11826,19 @@
       <c r="K58" s="43">
         <v>14.1065283253274</v>
       </c>
-      <c r="L58" s="62">
+      <c r="L58" s="48">
         <v>-2.1107192272316899</v>
       </c>
-      <c r="M58" s="62">
+      <c r="M58" s="48">
         <v>-2.40371680829529</v>
       </c>
-      <c r="N58" s="62">
+      <c r="N58" s="48">
         <v>-1.8297558278767401</v>
       </c>
-      <c r="O58" s="62">
+      <c r="O58" s="48">
         <v>-2.0718276732654002</v>
       </c>
-      <c r="P58" s="62">
+      <c r="P58" s="48">
         <v>11.1865327668083</v>
       </c>
     </row>
@@ -11875,19 +11876,19 @@
       <c r="K59" s="43">
         <v>17.051403914375101</v>
       </c>
-      <c r="L59" s="62">
+      <c r="L59" s="48">
         <v>-1.8362679444404999</v>
       </c>
-      <c r="M59" s="62">
+      <c r="M59" s="48">
         <v>-2.1081388367249798</v>
       </c>
-      <c r="N59" s="62">
+      <c r="N59" s="48">
         <v>-1.58939409294987</v>
       </c>
-      <c r="O59" s="62">
+      <c r="O59" s="48">
         <v>-1.79516043984069</v>
       </c>
-      <c r="P59" s="62">
+      <c r="P59" s="48">
         <v>14.2441203090822</v>
       </c>
     </row>
@@ -11925,19 +11926,19 @@
       <c r="K60" s="43">
         <v>24.045383462595002</v>
       </c>
-      <c r="L60" s="62">
+      <c r="L60" s="48">
         <v>-1.4045778008438701</v>
       </c>
-      <c r="M60" s="62">
+      <c r="M60" s="48">
         <v>-1.6680705768765201</v>
       </c>
-      <c r="N60" s="62">
+      <c r="N60" s="48">
         <v>-1.13341434773953</v>
       </c>
-      <c r="O60" s="62">
+      <c r="O60" s="48">
         <v>-1.59197266157281</v>
       </c>
-      <c r="P60" s="62">
+      <c r="P60" s="48">
         <v>16.910653825588099</v>
       </c>
     </row>
@@ -11975,19 +11976,19 @@
       <c r="K61" s="43">
         <v>25.0904829238753</v>
       </c>
-      <c r="L61" s="62">
+      <c r="L61" s="48">
         <v>-1.3113169383307099</v>
       </c>
-      <c r="M61" s="62">
+      <c r="M61" s="48">
         <v>-1.5392985795162699</v>
       </c>
-      <c r="N61" s="62">
+      <c r="N61" s="48">
         <v>-1.09070486392903</v>
       </c>
-      <c r="O61" s="62">
+      <c r="O61" s="48">
         <v>-1.3153054281481</v>
       </c>
-      <c r="P61" s="62">
+      <c r="P61" s="48">
         <v>21.160040824654999</v>
       </c>
     </row>
@@ -12025,19 +12026,19 @@
       <c r="K62" s="43">
         <v>19.087364385916601</v>
       </c>
-      <c r="L62" s="62">
+      <c r="L62" s="48">
         <v>-1.7948020831985001</v>
       </c>
-      <c r="M62" s="62">
+      <c r="M62" s="48">
         <v>-2.13648145379315</v>
       </c>
-      <c r="N62" s="62">
+      <c r="N62" s="48">
         <v>-1.47218952317611</v>
       </c>
-      <c r="O62" s="62">
+      <c r="O62" s="48">
         <v>-1.9324793069933099</v>
       </c>
-      <c r="P62" s="62">
+      <c r="P62" s="48">
         <v>12.647641220391</v>
       </c>
     </row>
@@ -12075,19 +12076,19 @@
       <c r="K63" s="43">
         <v>24.3185077382165</v>
       </c>
-      <c r="L63" s="62">
+      <c r="L63" s="48">
         <v>-1.4204165600122001</v>
       </c>
-      <c r="M63" s="62">
+      <c r="M63" s="48">
         <v>-1.7124353063128199</v>
       </c>
-      <c r="N63" s="62">
+      <c r="N63" s="48">
         <v>-1.15194955382963</v>
       </c>
-      <c r="O63" s="62">
+      <c r="O63" s="48">
         <v>-1.6558120735685999</v>
       </c>
-      <c r="P63" s="62">
+      <c r="P63" s="48">
         <v>16.0324977599753</v>
       </c>
     </row>
@@ -12125,19 +12126,19 @@
       <c r="K64" s="43">
         <v>24.1740084370836</v>
       </c>
-      <c r="L64" s="62">
+      <c r="L64" s="48">
         <v>-1.4433765750380001</v>
       </c>
-      <c r="M64" s="62">
+      <c r="M64" s="48">
         <v>-1.75184084113048</v>
       </c>
-      <c r="N64" s="62">
+      <c r="N64" s="48">
         <v>-1.1259029372917699</v>
       </c>
-      <c r="O64" s="62">
+      <c r="O64" s="48">
         <v>-1.45262429530072</v>
       </c>
-      <c r="P64" s="62">
+      <c r="P64" s="48">
         <v>18.959801295362301</v>
       </c>
     </row>
@@ -12175,19 +12176,19 @@
       <c r="K65" s="43">
         <v>27.569040273267099</v>
       </c>
-      <c r="L65" s="62">
+      <c r="L65" s="48">
         <v>-1.2216824944376501</v>
       </c>
-      <c r="M65" s="62">
+      <c r="M65" s="48">
         <v>-1.46089872621804</v>
       </c>
-      <c r="N65" s="62">
+      <c r="N65" s="48">
         <v>-0.96699963563570701</v>
       </c>
-      <c r="O65" s="62">
+      <c r="O65" s="48">
         <v>-1.17595706187601</v>
       </c>
-      <c r="P65" s="62">
+      <c r="P65" s="48">
         <v>23.577990577796701</v>
       </c>
     </row>
@@ -12225,19 +12226,19 @@
       <c r="K66" s="43">
         <v>19.636048441945398</v>
       </c>
-      <c r="L66" s="62">
+      <c r="L66" s="48">
         <v>-1.7161866992102</v>
       </c>
-      <c r="M66" s="62">
+      <c r="M66" s="48">
         <v>-2.04027802751959</v>
       </c>
-      <c r="N66" s="62">
+      <c r="N66" s="48">
         <v>-1.40587128252992</v>
       </c>
-      <c r="O66" s="62">
+      <c r="O66" s="48">
         <v>-1.6409069234862199</v>
       </c>
-      <c r="P66" s="62">
+      <c r="P66" s="48">
         <v>16.2341695124857</v>
       </c>
     </row>
@@ -12275,19 +12276,19 @@
       <c r="K67" s="43">
         <v>29.405664740668399</v>
       </c>
-      <c r="L67" s="62">
+      <c r="L67" s="48">
         <v>-1.15009178143339</v>
       </c>
-      <c r="M67" s="62">
+      <c r="M67" s="48">
         <v>-1.4158808546045301</v>
       </c>
-      <c r="N67" s="62">
+      <c r="N67" s="48">
         <v>-0.87955391944462902</v>
       </c>
-      <c r="O67" s="62">
+      <c r="O67" s="48">
         <v>-1.3642396900615099</v>
       </c>
-      <c r="P67" s="62">
+      <c r="P67" s="48">
         <v>20.3552105545118</v>
       </c>
     </row>
@@ -12325,19 +12326,19 @@
       <c r="K68" s="43">
         <v>29.0540518591352</v>
       </c>
-      <c r="L68" s="62">
+      <c r="L68" s="48">
         <v>-1.1832647652062001</v>
       </c>
-      <c r="M68" s="62">
+      <c r="M68" s="48">
         <v>-1.4671839727037199</v>
       </c>
-      <c r="N68" s="62">
+      <c r="N68" s="48">
         <v>-0.90723716601539794</v>
       </c>
-      <c r="O68" s="62">
+      <c r="O68" s="48">
         <v>-1.16105191179363</v>
       </c>
-      <c r="P68" s="62">
+      <c r="P68" s="48">
         <v>23.847619984823599</v>
       </c>
     </row>
@@ -12375,19 +12376,19 @@
       <c r="K69" s="43">
         <v>36.686825927248996</v>
       </c>
-      <c r="L69" s="62">
+      <c r="L69" s="48">
         <v>-0.79870427428052404</v>
       </c>
-      <c r="M69" s="62">
+      <c r="M69" s="48">
         <v>-1.0376945324696201</v>
       </c>
-      <c r="N69" s="62">
+      <c r="N69" s="48">
         <v>-0.54463216130230796</v>
       </c>
-      <c r="O69" s="62">
+      <c r="O69" s="48">
         <v>-0.88438467836891699</v>
       </c>
-      <c r="P69" s="62">
+      <c r="P69" s="48">
         <v>29.226999050315001</v>
       </c>
     </row>
@@ -12425,19 +12426,19 @@
       <c r="K70" s="43">
         <v>18.9091406215211</v>
       </c>
-      <c r="L70" s="62">
+      <c r="L70" s="48">
         <v>-1.7317177164639299</v>
       </c>
-      <c r="M70" s="62">
+      <c r="M70" s="48">
         <v>-2.0286274490738299</v>
       </c>
-      <c r="N70" s="62">
+      <c r="N70" s="48">
         <v>-1.44445447415225</v>
       </c>
-      <c r="O70" s="62">
+      <c r="O70" s="48">
         <v>-1.62454859797535</v>
       </c>
-      <c r="P70" s="62">
+      <c r="P70" s="48">
         <v>16.457851786074102</v>
       </c>
     </row>
@@ -12475,19 +12476,19 @@
       <c r="K71" s="43">
         <v>27.0298363888575</v>
       </c>
-      <c r="L71" s="62">
+      <c r="L71" s="48">
         <v>-1.24054041793325</v>
       </c>
-      <c r="M71" s="62">
+      <c r="M71" s="48">
         <v>-1.46604253590471</v>
       </c>
-      <c r="N71" s="62">
+      <c r="N71" s="48">
         <v>-1.0016399920041701</v>
       </c>
-      <c r="O71" s="62">
+      <c r="O71" s="48">
         <v>-1.34788136455063</v>
       </c>
-      <c r="P71" s="62">
+      <c r="P71" s="48">
         <v>20.621695861579799</v>
       </c>
     </row>
@@ -12525,19 +12526,19 @@
       <c r="K72" s="43">
         <v>31.160939932302899</v>
       </c>
-      <c r="L72" s="62">
+      <c r="L72" s="48">
         <v>-1.04214570331485</v>
       </c>
-      <c r="M72" s="62">
+      <c r="M72" s="48">
         <v>-1.3116549511767699</v>
       </c>
-      <c r="N72" s="62">
+      <c r="N72" s="48">
         <v>-0.76770941555124195</v>
       </c>
-      <c r="O72" s="62">
+      <c r="O72" s="48">
         <v>-1.1446935862827601</v>
       </c>
-      <c r="P72" s="62">
+      <c r="P72" s="48">
         <v>24.145965545857202</v>
       </c>
     </row>
@@ -12575,19 +12576,19 @@
       <c r="K73" s="43">
         <v>36.5803487772191</v>
       </c>
-      <c r="L73" s="62">
+      <c r="L73" s="48">
         <v>-0.76746401317275703</v>
       </c>
-      <c r="M73" s="62">
+      <c r="M73" s="48">
         <v>-0.99326438350858903</v>
       </c>
-      <c r="N73" s="62">
+      <c r="N73" s="48">
         <v>-0.537464163745764</v>
       </c>
-      <c r="O73" s="62">
+      <c r="O73" s="48">
         <v>-0.86802635285804297</v>
       </c>
-      <c r="P73" s="62">
+      <c r="P73" s="48">
         <v>29.566514280427999</v>
       </c>
     </row>
@@ -15209,31 +15210,31 @@
     </row>
     <row r="3" spans="1:21" ht="28.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
       <c r="L3" s="3"/>
-      <c r="M3" s="48" t="s">
+      <c r="M3" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
       <c r="Q3" s="3"/>
-      <c r="R3" s="48" t="s">
+      <c r="R3" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
     </row>
     <row r="4" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -15348,12 +15349,12 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
       <c r="F6" s="6" t="s">
         <v>16</v>
       </c>
@@ -15369,12 +15370,12 @@
       <c r="J6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="49" t="s">
+      <c r="L6" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
       <c r="Q6" s="6" t="s">
         <v>16</v>
       </c>
@@ -15395,11 +15396,11 @@
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="53">
         <v>3.29</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
       <c r="F7" s="6" t="s">
         <v>145</v>
       </c>
@@ -15418,11 +15419,11 @@
       <c r="L7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="47">
+      <c r="M7" s="53">
         <v>0.59</v>
       </c>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="53"/>
       <c r="Q7" s="6" t="s">
         <v>145</v>
       </c>
@@ -15443,11 +15444,11 @@
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="53">
         <v>0.9</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
       <c r="F8" s="6" t="s">
         <v>148</v>
       </c>
@@ -15466,11 +15467,11 @@
       <c r="L8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M8" s="47">
+      <c r="M8" s="53">
         <v>0.01</v>
       </c>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="53"/>
       <c r="Q8" s="6" t="s">
         <v>148</v>
       </c>
@@ -15491,11 +15492,11 @@
       <c r="A9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="53">
         <v>0.21</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
       <c r="F9" s="6" t="s">
         <v>151</v>
       </c>
@@ -15514,11 +15515,11 @@
       <c r="L9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="47">
+      <c r="M9" s="53">
         <v>0.02</v>
       </c>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="53"/>
       <c r="Q9" s="6" t="s">
         <v>151</v>
       </c>
@@ -15539,11 +15540,11 @@
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="50">
+      <c r="B10" s="56">
         <v>108</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
       <c r="F10" s="6" t="s">
         <v>154</v>
       </c>
@@ -15562,11 +15563,11 @@
       <c r="L10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="50">
+      <c r="M10" s="56">
         <v>108</v>
       </c>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
       <c r="Q10" s="6" t="s">
         <v>154</v>
       </c>
@@ -15587,11 +15588,11 @@
       <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="51">
+      <c r="B11" s="57">
         <v>29653</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
       <c r="F11" s="6" t="s">
         <v>157</v>
       </c>
@@ -15610,11 +15611,11 @@
       <c r="L11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="51">
+      <c r="M11" s="57">
         <v>29653</v>
       </c>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="57"/>
       <c r="Q11" s="6" t="s">
         <v>157</v>
       </c>
@@ -15635,11 +15636,11 @@
       <c r="A12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
       <c r="F12" s="6" t="s">
         <v>161</v>
       </c>
@@ -15658,11 +15659,11 @@
       <c r="L12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M12" s="47" t="s">
+      <c r="M12" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
       <c r="Q12" s="6" t="s">
         <v>161</v>
       </c>
@@ -15788,13 +15789,13 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F16" s="49" t="s">
+      <c r="F16" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
       <c r="Q16" s="9" t="s">
         <v>15</v>
       </c>
@@ -15807,12 +15808,12 @@
       <c r="F17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="53">
         <v>3.29</v>
       </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
       <c r="Q17" s="6" t="s">
         <v>17</v>
       </c>
@@ -15821,12 +15822,12 @@
       <c r="F18" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="47">
+      <c r="G18" s="53">
         <v>0.02</v>
       </c>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
       <c r="Q18" s="6" t="s">
         <v>19</v>
       </c>
@@ -15841,12 +15842,12 @@
       <c r="F19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="47">
+      <c r="G19" s="53">
         <v>0.01</v>
       </c>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
       <c r="Q19" s="6" t="s">
         <v>22</v>
       </c>
@@ -15861,12 +15862,12 @@
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="50">
+      <c r="G20" s="56">
         <v>108</v>
       </c>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
       <c r="Q20" s="11" t="s">
         <v>23</v>
       </c>
@@ -15881,12 +15882,12 @@
       <c r="F21" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="57">
         <v>29653</v>
       </c>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
       <c r="Q21" s="14" t="s">
         <v>28</v>
       </c>
@@ -15898,12 +15899,12 @@
       <c r="F22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="47" t="s">
+      <c r="G22" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F23" s="14" t="s">
@@ -16016,57 +16017,57 @@
     </row>
     <row r="4" spans="1:44" ht="28.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="L4" s="48" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="L4" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="X4" s="48" t="s">
+      <c r="S4" s="54"/>
+      <c r="T4" s="54"/>
+      <c r="U4" s="54"/>
+      <c r="X4" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="48"/>
-      <c r="AC4" s="48" t="s">
+      <c r="Y4" s="54"/>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="54"/>
+      <c r="AC4" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="AD4" s="48"/>
-      <c r="AE4" s="48"/>
-      <c r="AF4" s="48"/>
-      <c r="AG4" s="48"/>
-      <c r="AI4" s="48" t="s">
+      <c r="AD4" s="54"/>
+      <c r="AE4" s="54"/>
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="54"/>
+      <c r="AI4" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="AJ4" s="48"/>
-      <c r="AK4" s="48"/>
-      <c r="AL4" s="48"/>
-      <c r="AN4" s="48" t="s">
+      <c r="AJ4" s="54"/>
+      <c r="AK4" s="54"/>
+      <c r="AL4" s="54"/>
+      <c r="AN4" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="AO4" s="48"/>
-      <c r="AP4" s="48"/>
-      <c r="AQ4" s="48"/>
-      <c r="AR4" s="48"/>
+      <c r="AO4" s="54"/>
+      <c r="AP4" s="54"/>
+      <c r="AQ4" s="54"/>
+      <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -16289,12 +16290,12 @@
       </c>
     </row>
     <row r="7" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
       <c r="F7" s="6" t="s">
         <v>16</v>
       </c>
@@ -16310,12 +16311,12 @@
       <c r="J7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="49" t="s">
+      <c r="L7" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
       <c r="Q7" s="6" t="s">
         <v>16</v>
       </c>
@@ -16331,12 +16332,12 @@
       <c r="U7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="X7" s="49" t="s">
+      <c r="X7" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="49"/>
+      <c r="Y7" s="55"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="55"/>
       <c r="AC7" s="6" t="s">
         <v>16</v>
       </c>
@@ -16352,12 +16353,12 @@
       <c r="AG7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AI7" s="49" t="s">
+      <c r="AI7" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="AJ7" s="49"/>
-      <c r="AK7" s="49"/>
-      <c r="AL7" s="49"/>
+      <c r="AJ7" s="55"/>
+      <c r="AK7" s="55"/>
+      <c r="AL7" s="55"/>
       <c r="AN7" s="6" t="s">
         <v>16</v>
       </c>
@@ -16378,11 +16379,11 @@
       <c r="A8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="53">
         <v>3.29</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
       <c r="F8" s="6" t="s">
         <v>18</v>
       </c>
@@ -16401,11 +16402,11 @@
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="47">
+      <c r="M8" s="53">
         <v>3.29</v>
       </c>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="53"/>
       <c r="Q8" s="6" t="s">
         <v>18</v>
       </c>
@@ -16424,11 +16425,11 @@
       <c r="X8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="Y8" s="47">
+      <c r="Y8" s="53">
         <v>2.12</v>
       </c>
-      <c r="Z8" s="47"/>
-      <c r="AA8" s="47"/>
+      <c r="Z8" s="53"/>
+      <c r="AA8" s="53"/>
       <c r="AC8" s="6" t="s">
         <v>18</v>
       </c>
@@ -16447,11 +16448,11 @@
       <c r="AI8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AJ8" s="47">
+      <c r="AJ8" s="53">
         <v>2.11</v>
       </c>
-      <c r="AK8" s="47"/>
-      <c r="AL8" s="47"/>
+      <c r="AK8" s="53"/>
+      <c r="AL8" s="53"/>
       <c r="AN8" s="6" t="s">
         <v>18</v>
       </c>
@@ -16472,11 +16473,11 @@
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="53">
         <v>0.24</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
       <c r="F9" s="6" t="s">
         <v>20</v>
       </c>
@@ -16495,11 +16496,11 @@
       <c r="L9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="47">
+      <c r="M9" s="53">
         <v>0.26</v>
       </c>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="53"/>
       <c r="Q9" s="6" t="s">
         <v>20</v>
       </c>
@@ -16518,11 +16519,11 @@
       <c r="X9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="Y9" s="47">
+      <c r="Y9" s="53">
         <v>0.17</v>
       </c>
-      <c r="Z9" s="47"/>
-      <c r="AA9" s="47"/>
+      <c r="Z9" s="53"/>
+      <c r="AA9" s="53"/>
       <c r="AC9" s="6" t="s">
         <v>20</v>
       </c>
@@ -16541,11 +16542,11 @@
       <c r="AI9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AJ9" s="47">
+      <c r="AJ9" s="53">
         <v>0.18</v>
       </c>
-      <c r="AK9" s="47"/>
-      <c r="AL9" s="47"/>
+      <c r="AK9" s="53"/>
+      <c r="AL9" s="53"/>
       <c r="AN9" s="6" t="s">
         <v>20</v>
       </c>
@@ -16566,11 +16567,11 @@
       <c r="A10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="53">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
       <c r="F10" s="6" t="s">
         <v>197</v>
       </c>
@@ -16589,11 +16590,11 @@
       <c r="L10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="53">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
       <c r="Q10" s="6" t="s">
         <v>151</v>
       </c>
@@ -16612,11 +16613,11 @@
       <c r="X10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Y10" s="47">
+      <c r="Y10" s="53">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Z10" s="47"/>
-      <c r="AA10" s="47"/>
+      <c r="Z10" s="53"/>
+      <c r="AA10" s="53"/>
       <c r="AC10" s="6" t="s">
         <v>197</v>
       </c>
@@ -16635,11 +16636,11 @@
       <c r="AI10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AJ10" s="47">
+      <c r="AJ10" s="53">
         <v>0.08</v>
       </c>
-      <c r="AK10" s="47"/>
-      <c r="AL10" s="47"/>
+      <c r="AK10" s="53"/>
+      <c r="AL10" s="53"/>
       <c r="AN10" s="6" t="s">
         <v>151</v>
       </c>
@@ -16660,11 +16661,11 @@
       <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="50">
+      <c r="B11" s="56">
         <v>54</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
       <c r="F11" s="6" t="s">
         <v>202</v>
       </c>
@@ -16683,11 +16684,11 @@
       <c r="L11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="50">
+      <c r="M11" s="56">
         <v>108</v>
       </c>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
       <c r="Q11" s="6" t="s">
         <v>154</v>
       </c>
@@ -16706,11 +16707,11 @@
       <c r="X11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y11" s="50">
+      <c r="Y11" s="56">
         <v>54</v>
       </c>
-      <c r="Z11" s="50"/>
-      <c r="AA11" s="50"/>
+      <c r="Z11" s="56"/>
+      <c r="AA11" s="56"/>
       <c r="AC11" s="6" t="s">
         <v>202</v>
       </c>
@@ -16729,11 +16730,11 @@
       <c r="AI11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AJ11" s="50">
+      <c r="AJ11" s="56">
         <v>108</v>
       </c>
-      <c r="AK11" s="50"/>
-      <c r="AL11" s="50"/>
+      <c r="AK11" s="56"/>
+      <c r="AL11" s="56"/>
       <c r="AN11" s="6" t="s">
         <v>154</v>
       </c>
@@ -16754,11 +16755,11 @@
       <c r="A12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="57">
         <v>19500</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
       <c r="F12" s="6" t="s">
         <v>24</v>
       </c>
@@ -16777,11 +16778,11 @@
       <c r="L12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="51">
+      <c r="M12" s="57">
         <v>19500</v>
       </c>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="57"/>
       <c r="Q12" s="6" t="s">
         <v>157</v>
       </c>
@@ -16800,11 +16801,11 @@
       <c r="X12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Y12" s="51">
+      <c r="Y12" s="57">
         <v>19500</v>
       </c>
-      <c r="Z12" s="51"/>
-      <c r="AA12" s="51"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
       <c r="AC12" s="6" t="s">
         <v>24</v>
       </c>
@@ -16823,11 +16824,11 @@
       <c r="AI12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="AJ12" s="51">
+      <c r="AJ12" s="57">
         <v>19500</v>
       </c>
-      <c r="AK12" s="51"/>
-      <c r="AL12" s="51"/>
+      <c r="AK12" s="57"/>
+      <c r="AL12" s="57"/>
       <c r="AN12" s="6" t="s">
         <v>157</v>
       </c>
@@ -16848,11 +16849,11 @@
       <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="53" t="s">
         <v>210</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
       <c r="F13" s="6" t="s">
         <v>27</v>
       </c>
@@ -16871,11 +16872,11 @@
       <c r="L13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="47" t="s">
+      <c r="M13" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="53"/>
       <c r="Q13" s="6" t="s">
         <v>161</v>
       </c>
@@ -16894,11 +16895,11 @@
       <c r="X13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="Y13" s="47" t="s">
+      <c r="Y13" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="Z13" s="47"/>
-      <c r="AA13" s="47"/>
+      <c r="Z13" s="53"/>
+      <c r="AA13" s="53"/>
       <c r="AC13" s="6" t="s">
         <v>27</v>
       </c>
@@ -16917,11 +16918,11 @@
       <c r="AI13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AJ13" s="47" t="s">
+      <c r="AJ13" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="AK13" s="47"/>
-      <c r="AL13" s="47"/>
+      <c r="AK13" s="53"/>
+      <c r="AL13" s="53"/>
       <c r="AN13" s="6" t="s">
         <v>161</v>
       </c>
@@ -16947,13 +16948,13 @@
       </c>
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
       <c r="L14" s="12" t="s">
         <v>28</v>
       </c>
@@ -16983,13 +16984,13 @@
       </c>
       <c r="Z14" s="14"/>
       <c r="AA14" s="14"/>
-      <c r="AC14" s="49" t="s">
+      <c r="AC14" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="AD14" s="49"/>
-      <c r="AE14" s="49"/>
-      <c r="AF14" s="49"/>
-      <c r="AG14" s="49"/>
+      <c r="AD14" s="55"/>
+      <c r="AE14" s="55"/>
+      <c r="AF14" s="55"/>
+      <c r="AG14" s="55"/>
       <c r="AI14" s="14" t="s">
         <v>28</v>
       </c>
@@ -17013,18 +17014,18 @@
       </c>
     </row>
     <row r="15" spans="1:44" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="58" t="s">
         <v>219</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="53">
         <v>3.29</v>
       </c>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
       <c r="Q15" s="6" t="s">
         <v>24</v>
       </c>
@@ -17043,12 +17044,12 @@
       <c r="AC15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AD15" s="47">
+      <c r="AD15" s="53">
         <v>2.12</v>
       </c>
-      <c r="AE15" s="47"/>
-      <c r="AF15" s="47"/>
-      <c r="AG15" s="47"/>
+      <c r="AE15" s="53"/>
+      <c r="AF15" s="53"/>
+      <c r="AG15" s="53"/>
       <c r="AN15" s="6" t="s">
         <v>24</v>
       </c>
@@ -17066,16 +17067,16 @@
       </c>
     </row>
     <row r="16" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
+      <c r="A16" s="58"/>
       <c r="F16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="53">
         <v>0.01</v>
       </c>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
       <c r="Q16" s="6" t="s">
         <v>27</v>
       </c>
@@ -17094,12 +17095,12 @@
       <c r="AC16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AD16" s="47">
+      <c r="AD16" s="53">
         <v>0</v>
       </c>
-      <c r="AE16" s="47"/>
-      <c r="AF16" s="47"/>
-      <c r="AG16" s="47"/>
+      <c r="AE16" s="53"/>
+      <c r="AF16" s="53"/>
+      <c r="AG16" s="53"/>
       <c r="AN16" s="6" t="s">
         <v>27</v>
       </c>
@@ -17117,154 +17118,154 @@
       </c>
     </row>
     <row r="17" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
+      <c r="A17" s="58"/>
       <c r="F17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="53">
         <v>0</v>
       </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="Q17" s="49" t="s">
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="Q17" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="R17" s="49"/>
-      <c r="S17" s="49"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="49"/>
+      <c r="R17" s="55"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="55"/>
+      <c r="U17" s="55"/>
       <c r="AC17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AD17" s="47">
+      <c r="AD17" s="53">
         <v>0</v>
       </c>
-      <c r="AE17" s="47"/>
-      <c r="AF17" s="47"/>
-      <c r="AG17" s="47"/>
-      <c r="AN17" s="49" t="s">
+      <c r="AE17" s="53"/>
+      <c r="AF17" s="53"/>
+      <c r="AG17" s="53"/>
+      <c r="AN17" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="AO17" s="49"/>
-      <c r="AP17" s="49"/>
-      <c r="AQ17" s="49"/>
-      <c r="AR17" s="49"/>
+      <c r="AO17" s="55"/>
+      <c r="AP17" s="55"/>
+      <c r="AQ17" s="55"/>
+      <c r="AR17" s="55"/>
     </row>
     <row r="18" spans="1:44" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="52"/>
+      <c r="A18" s="58"/>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="56">
         <v>54</v>
       </c>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
       <c r="Q18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="R18" s="47">
+      <c r="R18" s="53">
         <v>3.29</v>
       </c>
-      <c r="S18" s="47"/>
-      <c r="T18" s="47"/>
-      <c r="U18" s="47"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="53"/>
+      <c r="U18" s="53"/>
       <c r="AC18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AD18" s="50">
+      <c r="AD18" s="56">
         <v>54</v>
       </c>
-      <c r="AE18" s="50"/>
-      <c r="AF18" s="50"/>
-      <c r="AG18" s="50"/>
+      <c r="AE18" s="56"/>
+      <c r="AF18" s="56"/>
+      <c r="AG18" s="56"/>
       <c r="AN18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AO18" s="47">
+      <c r="AO18" s="53">
         <v>2.11</v>
       </c>
-      <c r="AP18" s="47"/>
-      <c r="AQ18" s="47"/>
-      <c r="AR18" s="47"/>
+      <c r="AP18" s="53"/>
+      <c r="AQ18" s="53"/>
+      <c r="AR18" s="53"/>
     </row>
     <row r="19" spans="1:44" ht="30" x14ac:dyDescent="0.25">
       <c r="F19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="57">
         <v>19500</v>
       </c>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
       <c r="Q19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="R19" s="47">
+      <c r="R19" s="53">
         <v>0.01</v>
       </c>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
+      <c r="S19" s="53"/>
+      <c r="T19" s="53"/>
+      <c r="U19" s="53"/>
       <c r="AC19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="AD19" s="51">
+      <c r="AD19" s="57">
         <v>19500</v>
       </c>
-      <c r="AE19" s="51"/>
-      <c r="AF19" s="51"/>
-      <c r="AG19" s="51"/>
+      <c r="AE19" s="57"/>
+      <c r="AF19" s="57"/>
+      <c r="AG19" s="57"/>
       <c r="AN19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AO19" s="47">
+      <c r="AO19" s="53">
         <v>0</v>
       </c>
-      <c r="AP19" s="47"/>
-      <c r="AQ19" s="47"/>
-      <c r="AR19" s="47"/>
+      <c r="AP19" s="53"/>
+      <c r="AQ19" s="53"/>
+      <c r="AR19" s="53"/>
     </row>
     <row r="20" spans="1:44" ht="66" x14ac:dyDescent="0.25">
       <c r="F20" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G20" s="47" t="s">
+      <c r="G20" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
       <c r="Q20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="R20" s="47">
+      <c r="R20" s="53">
         <v>0</v>
       </c>
-      <c r="S20" s="47"/>
-      <c r="T20" s="47"/>
-      <c r="U20" s="47"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="53"/>
+      <c r="U20" s="53"/>
       <c r="AC20" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AD20" s="47" t="s">
+      <c r="AD20" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="AE20" s="47"/>
-      <c r="AF20" s="47"/>
-      <c r="AG20" s="47"/>
+      <c r="AE20" s="53"/>
+      <c r="AF20" s="53"/>
+      <c r="AG20" s="53"/>
       <c r="AN20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AO20" s="47">
+      <c r="AO20" s="53">
         <v>0</v>
       </c>
-      <c r="AP20" s="47"/>
-      <c r="AQ20" s="47"/>
-      <c r="AR20" s="47"/>
+      <c r="AP20" s="53"/>
+      <c r="AQ20" s="53"/>
+      <c r="AR20" s="53"/>
     </row>
     <row r="21" spans="1:44" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F21" s="12" t="s">
@@ -17276,12 +17277,12 @@
       <c r="Q21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="R21" s="50">
+      <c r="R21" s="56">
         <v>108</v>
       </c>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="50"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="56"/>
+      <c r="U21" s="56"/>
       <c r="AC21" s="12" t="s">
         <v>217</v>
       </c>
@@ -17291,12 +17292,12 @@
       <c r="AN21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AO21" s="50">
+      <c r="AO21" s="56">
         <v>108</v>
       </c>
-      <c r="AP21" s="50"/>
-      <c r="AQ21" s="50"/>
-      <c r="AR21" s="50"/>
+      <c r="AP21" s="56"/>
+      <c r="AQ21" s="56"/>
+      <c r="AR21" s="56"/>
     </row>
     <row r="22" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" s="12" t="s">
@@ -17308,12 +17309,12 @@
       <c r="Q22" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="R22" s="51">
+      <c r="R22" s="57">
         <v>19500</v>
       </c>
-      <c r="S22" s="51"/>
-      <c r="T22" s="51"/>
-      <c r="U22" s="51"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="57"/>
       <c r="AC22" s="12" t="s">
         <v>225</v>
       </c>
@@ -17323,32 +17324,32 @@
       <c r="AN22" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="AO22" s="51">
+      <c r="AO22" s="57">
         <v>19500</v>
       </c>
-      <c r="AP22" s="51"/>
-      <c r="AQ22" s="51"/>
-      <c r="AR22" s="51"/>
+      <c r="AP22" s="57"/>
+      <c r="AQ22" s="57"/>
+      <c r="AR22" s="57"/>
     </row>
     <row r="23" spans="1:44" ht="36" x14ac:dyDescent="0.25">
       <c r="Q23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R23" s="47" t="s">
+      <c r="R23" s="53" t="s">
         <v>226</v>
       </c>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
-      <c r="U23" s="47"/>
+      <c r="S23" s="53"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
       <c r="AN23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AO23" s="47" t="s">
+      <c r="AO23" s="53" t="s">
         <v>227</v>
       </c>
-      <c r="AP23" s="47"/>
-      <c r="AQ23" s="47"/>
-      <c r="AR23" s="47"/>
+      <c r="AP23" s="53"/>
+      <c r="AQ23" s="53"/>
+      <c r="AR23" s="53"/>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.25">
       <c r="Q24" s="14" t="s">
